--- a/research/traditional_assets/database/data/sweden/sweden_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_farming_agriculture.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0275</v>
+        <v>0.16525</v>
       </c>
       <c r="E2">
         <v>-0.0645</v>
@@ -599,40 +599,40 @@
         <v>-0.081</v>
       </c>
       <c r="G2">
-        <v>0.1908267625959467</v>
+        <v>0.1886260067990815</v>
       </c>
       <c r="H2">
-        <v>0.1389580239683768</v>
+        <v>0.1369746377188727</v>
       </c>
       <c r="I2">
-        <v>0.07577437098697007</v>
+        <v>0.07335555282611547</v>
       </c>
       <c r="J2">
-        <v>0.05656001222426035</v>
+        <v>0.06870530007284531</v>
       </c>
       <c r="K2">
-        <v>140.8</v>
+        <v>125.9</v>
       </c>
       <c r="L2">
-        <v>0.02944805805952356</v>
+        <v>0.02620956409685256</v>
       </c>
       <c r="M2">
         <v>169</v>
       </c>
       <c r="N2">
-        <v>0.0565955594253374</v>
+        <v>0.05615550755939525</v>
       </c>
       <c r="O2">
-        <v>1.200284090909091</v>
+        <v>1.342335186656076</v>
       </c>
       <c r="P2">
         <v>169</v>
       </c>
       <c r="Q2">
-        <v>0.0565955594253374</v>
+        <v>0.05615550755939525</v>
       </c>
       <c r="R2">
-        <v>1.200284090909091</v>
+        <v>1.342335186656076</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -641,73 +641,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>338</v>
+        <v>339.617</v>
       </c>
       <c r="V2">
-        <v>0.1131911188506748</v>
+        <v>0.1128483136733677</v>
       </c>
       <c r="W2">
-        <v>0.05872784150156413</v>
+        <v>-0.8034875551987154</v>
       </c>
       <c r="X2">
-        <v>0.08068301614864803</v>
+        <v>0.08022039308462078</v>
       </c>
       <c r="Y2">
-        <v>-0.0219551746470839</v>
+        <v>-0.8837079482833362</v>
       </c>
       <c r="Z2">
-        <v>1.760938420742487</v>
+        <v>1.761826499560056</v>
       </c>
       <c r="AA2">
-        <v>0.09959869860336477</v>
+        <v>-0.8290588014685533</v>
       </c>
       <c r="AB2">
-        <v>0.07017691083267968</v>
+        <v>0.06972846745742212</v>
       </c>
       <c r="AC2">
-        <v>0.02942178777068509</v>
+        <v>-0.8982967787206421</v>
       </c>
       <c r="AD2">
-        <v>1382.3</v>
+        <v>1387.14</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1382.3</v>
+        <v>1387.14</v>
       </c>
       <c r="AG2">
-        <v>1044.3</v>
+        <v>1047.523</v>
       </c>
       <c r="AH2">
-        <v>0.3164316454537131</v>
+        <v>0.3155000181957131</v>
       </c>
       <c r="AI2">
-        <v>0.3620576756855863</v>
+        <v>0.3618827482572943</v>
       </c>
       <c r="AJ2">
-        <v>0.2591057959507742</v>
+        <v>0.2581999165397879</v>
       </c>
       <c r="AK2">
-        <v>0.3000948303112159</v>
+        <v>0.2998488909269578</v>
       </c>
       <c r="AL2">
-        <v>42.6</v>
+        <v>43.417</v>
       </c>
       <c r="AM2">
-        <v>36.19</v>
+        <v>36.971</v>
       </c>
       <c r="AN2">
-        <v>2.515101892285298</v>
+        <v>2.557552962000111</v>
       </c>
       <c r="AO2">
-        <v>8.504694835680752</v>
+        <v>8.115945367022134</v>
       </c>
       <c r="AP2">
-        <v>1.900109170305677</v>
+        <v>1.931380791710456</v>
       </c>
       <c r="AQ2">
-        <v>10.01105277701022</v>
+        <v>9.530983744015579</v>
       </c>
     </row>
     <row r="3">
@@ -787,10 +787,10 @@
         <v>0.05872784150156413</v>
       </c>
       <c r="X3">
-        <v>0.08068301614864803</v>
+        <v>0.08066058947073194</v>
       </c>
       <c r="Y3">
-        <v>-0.0219551746470839</v>
+        <v>-0.02193274796916781</v>
       </c>
       <c r="Z3">
         <v>1.760938420742487</v>
@@ -799,10 +799,10 @@
         <v>0.09959869860336477</v>
       </c>
       <c r="AB3">
-        <v>0.07017691083267968</v>
+        <v>0.07016158066535863</v>
       </c>
       <c r="AC3">
-        <v>0.02942178777068509</v>
+        <v>0.02943711793800614</v>
       </c>
       <c r="AD3">
         <v>1382.3</v>
@@ -845,6 +845,381 @@
       </c>
       <c r="AQ3">
         <v>10.01105277701022</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Agtira AB (OM:AGTIRA B)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Farming/Agriculture</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.303</v>
+      </c>
+      <c r="G4">
+        <v>-0.9791666666666666</v>
+      </c>
+      <c r="H4">
+        <v>-0.9791666666666666</v>
+      </c>
+      <c r="I4">
+        <v>-1.479166666666667</v>
+      </c>
+      <c r="J4">
+        <v>-1.479166666666667</v>
+      </c>
+      <c r="K4">
+        <v>-4.69</v>
+      </c>
+      <c r="L4">
+        <v>-1.628472222222222</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.029</v>
+      </c>
+      <c r="V4">
+        <v>0.007178217821782179</v>
+      </c>
+      <c r="W4">
+        <v>-1.184343434343434</v>
+      </c>
+      <c r="X4">
+        <v>0.0840665159663639</v>
+      </c>
+      <c r="Y4">
+        <v>-1.268409950309798</v>
+      </c>
+      <c r="Z4">
+        <v>0.5585725368502714</v>
+      </c>
+      <c r="AA4">
+        <v>-0.8262218774243598</v>
+      </c>
+      <c r="AB4">
+        <v>0.06929535424948562</v>
+      </c>
+      <c r="AC4">
+        <v>-0.8955172316738454</v>
+      </c>
+      <c r="AD4">
+        <v>2.55</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>2.55</v>
+      </c>
+      <c r="AG4">
+        <v>2.521</v>
+      </c>
+      <c r="AH4">
+        <v>0.3869499241274658</v>
+      </c>
+      <c r="AI4">
+        <v>0.3281853281853282</v>
+      </c>
+      <c r="AJ4">
+        <v>0.3842402072854748</v>
+      </c>
+      <c r="AK4">
+        <v>0.3256685182792921</v>
+      </c>
+      <c r="AL4">
+        <v>0.432</v>
+      </c>
+      <c r="AM4">
+        <v>0.429</v>
+      </c>
+      <c r="AN4">
+        <v>-0.7223796033994334</v>
+      </c>
+      <c r="AO4">
+        <v>-9.861111111111111</v>
+      </c>
+      <c r="AP4">
+        <v>-0.7141643059490085</v>
+      </c>
+      <c r="AQ4">
+        <v>-9.93006993006993</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Lyckegård Group AB (publ) (OM:LYGRD)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Farming/Agriculture</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>-0.1077272727272727</v>
+      </c>
+      <c r="H5">
+        <v>-0.1085227272727273</v>
+      </c>
+      <c r="I5">
+        <v>-0.2465909090909091</v>
+      </c>
+      <c r="J5">
+        <v>-0.2465909090909091</v>
+      </c>
+      <c r="K5">
+        <v>-8.9</v>
+      </c>
+      <c r="L5">
+        <v>-0.5056818181818181</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="V5">
+        <v>0.01611721611721612</v>
+      </c>
+      <c r="W5">
+        <v>-1.049528301886792</v>
+      </c>
+      <c r="X5">
+        <v>0.07978019669850964</v>
+      </c>
+      <c r="Y5">
+        <v>-1.129308498585302</v>
+      </c>
+      <c r="Z5">
+        <v>3.373586352309756</v>
+      </c>
+      <c r="AA5">
+        <v>-0.8318957255127467</v>
+      </c>
+      <c r="AB5">
+        <v>0.06918060025469196</v>
+      </c>
+      <c r="AC5">
+        <v>-0.9010763257674387</v>
+      </c>
+      <c r="AD5">
+        <v>2.29</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>2.29</v>
+      </c>
+      <c r="AG5">
+        <v>2.202</v>
+      </c>
+      <c r="AH5">
+        <v>0.2954838709677419</v>
+      </c>
+      <c r="AI5">
+        <v>0.4914163090128755</v>
+      </c>
+      <c r="AJ5">
+        <v>0.2873923257635082</v>
+      </c>
+      <c r="AK5">
+        <v>0.4816272965879265</v>
+      </c>
+      <c r="AL5">
+        <v>0.385</v>
+      </c>
+      <c r="AM5">
+        <v>0.373</v>
+      </c>
+      <c r="AN5">
+        <v>-0.9196787148594376</v>
+      </c>
+      <c r="AO5">
+        <v>-11.27272727272727</v>
+      </c>
+      <c r="AP5">
+        <v>-0.8843373493975902</v>
+      </c>
+      <c r="AQ5">
+        <v>-11.63538873994638</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BoMill AB (publ) (OM:BOMILL)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Farming/Agriculture</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>-0.8850828729281767</v>
+      </c>
+      <c r="H6">
+        <v>-0.9392265193370165</v>
+      </c>
+      <c r="I6">
+        <v>-0.7348066298342542</v>
+      </c>
+      <c r="J6">
+        <v>-0.7348066298342542</v>
+      </c>
+      <c r="K6">
+        <v>-1.31</v>
+      </c>
+      <c r="L6">
+        <v>-0.7237569060773481</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1.5</v>
+      </c>
+      <c r="V6">
+        <v>0.1079136690647482</v>
+      </c>
+      <c r="W6">
+        <v>-0.5574468085106383</v>
+      </c>
+      <c r="X6">
+        <v>0.07129124021041604</v>
+      </c>
+      <c r="Y6">
+        <v>-0.6287380487210543</v>
+      </c>
+      <c r="Z6">
+        <v>1.989010989010989</v>
+      </c>
+      <c r="AA6">
+        <v>-1</v>
+      </c>
+      <c r="AB6">
+        <v>0.07129124021041604</v>
+      </c>
+      <c r="AC6">
+        <v>-1.071291240210416</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>-1.5</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.1209677419354839</v>
+      </c>
+      <c r="AK6">
+        <v>-1.162790697674419</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>-0.021</v>
+      </c>
+      <c r="AN6">
+        <v>-0</v>
+      </c>
+      <c r="AP6">
+        <v>1.239669421487603</v>
+      </c>
+      <c r="AQ6">
+        <v>63.33333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -1139,49 +1514,49 @@
         <v>8.50469483568075</v>
       </c>
       <c r="F2">
-        <v>4.62067771310394</v>
+        <v>4.54471720491548</v>
       </c>
       <c r="G2">
         <v>2.5151018922853</v>
       </c>
       <c r="H2">
-        <v>2.46398107714702</v>
+        <v>2.62294759825327</v>
       </c>
       <c r="I2">
         <v>0.316431645453713</v>
       </c>
       <c r="J2">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="K2">
         <v>2986.1</v>
       </c>
       <c r="L2">
-        <v>3064.60805797893</v>
+        <v>3069.1236641504</v>
       </c>
       <c r="M2">
         <v>4030.4</v>
       </c>
       <c r="N2">
-        <v>4080.81205797893</v>
+        <v>4172.6956641504</v>
       </c>
       <c r="O2">
         <v>1382.3</v>
       </c>
       <c r="P2">
-        <v>1354.204</v>
+        <v>1441.572</v>
       </c>
       <c r="Q2">
-        <v>0.0701769108326797</v>
+        <v>0.0701615806653586</v>
       </c>
       <c r="R2">
-        <v>0.06973222750543701</v>
+        <v>0.06893405170091189</v>
       </c>
       <c r="S2">
         <v>0.0474812</v>
       </c>
       <c r="T2">
-        <v>0.0459726</v>
+        <v>0.0439082</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1569,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.08068301614864801</v>
+        <v>0.0806605894707319</v>
       </c>
       <c r="X2">
-        <v>0.08040684276150301</v>
+        <v>0.0812602174640477</v>
       </c>
       <c r="Y2">
         <v>0.805094445051546</v>
       </c>
       <c r="Z2">
-        <v>0.798720407356122</v>
+        <v>0.818942666606182</v>
       </c>
       <c r="AA2">
         <v>1382.3</v>
@@ -1236,7 +1611,7 @@
         <v>2986.1</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999999</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1799,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07130763935462331</v>
+        <v>0.07129124021041604</v>
       </c>
       <c r="C2">
-        <v>4245.652879778112</v>
+        <v>4245.763689196644</v>
       </c>
       <c r="D2">
-        <v>3907.652879778112</v>
+        <v>3907.763689196644</v>
       </c>
       <c r="E2">
         <v>-1382.3</v>
@@ -1475,19 +1850,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07130763935462331</v>
+        <v>0.07129124021041604</v>
       </c>
       <c r="T2">
         <v>0.5887122450442503</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.206</v>
       </c>
       <c r="W2">
-        <v>0.0410498</v>
+        <v>0.0399382</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1881,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07120759161755277</v>
+        <v>0.07118011025558257</v>
       </c>
       <c r="C3">
-        <v>4212.52732424584</v>
+        <v>4213.812031294751</v>
       </c>
       <c r="D3">
-        <v>3918.211324245839</v>
+        <v>3919.496031294751</v>
       </c>
       <c r="E3">
         <v>-1338.616</v>
@@ -1539,37 +1914,37 @@
         <v>362.3</v>
       </c>
       <c r="M3">
-        <v>2.2584628</v>
+        <v>2.1973052</v>
       </c>
       <c r="N3">
-        <v>360.0415372</v>
+        <v>360.1026948</v>
       </c>
       <c r="O3">
-        <v>74.16855666320001</v>
+        <v>74.1811551288</v>
       </c>
       <c r="P3">
-        <v>285.8729805368</v>
+        <v>285.9215396712</v>
       </c>
       <c r="Q3">
-        <v>473.1729805368</v>
+        <v>473.2215396712</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07151221577530584</v>
+        <v>0.07149568510664907</v>
       </c>
       <c r="T3">
         <v>0.5934338361812719</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.206</v>
       </c>
       <c r="W3">
-        <v>0.0410498</v>
+        <v>0.0399382</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1952,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>160.418847722442</v>
+        <v>164.8837858300249</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1963,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07110754388048225</v>
+        <v>0.07106898030074911</v>
       </c>
       <c r="C4">
-        <v>4179.458980952801</v>
+        <v>4181.931033938858</v>
       </c>
       <c r="D4">
-        <v>3928.826980952801</v>
+        <v>3931.299033938858</v>
       </c>
       <c r="E4">
         <v>-1294.932</v>
@@ -1621,37 +1996,37 @@
         <v>362.3</v>
       </c>
       <c r="M4">
-        <v>4.5169256</v>
+        <v>4.394610399999999</v>
       </c>
       <c r="N4">
-        <v>357.7830744</v>
+        <v>357.9053896</v>
       </c>
       <c r="O4">
-        <v>73.70331332640001</v>
+        <v>73.72851025760001</v>
       </c>
       <c r="P4">
-        <v>284.0797610736</v>
+        <v>284.1768793424</v>
       </c>
       <c r="Q4">
-        <v>471.3797610736</v>
+        <v>471.4768793424</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07172096722498189</v>
+        <v>0.07170430234770318</v>
       </c>
       <c r="T4">
         <v>0.5982517863210898</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.206</v>
       </c>
       <c r="W4">
-        <v>0.0410498</v>
+        <v>0.0399382</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +2034,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>80.209423861221</v>
+        <v>82.44189291501246</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +2045,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07100749614341173</v>
+        <v>0.07095785034591566</v>
       </c>
       <c r="C5">
-        <v>4146.448316179705</v>
+        <v>4150.12133740951</v>
       </c>
       <c r="D5">
-        <v>3939.500316179705</v>
+        <v>3943.173337409509</v>
       </c>
       <c r="E5">
         <v>-1251.248</v>
@@ -1703,37 +2078,37 @@
         <v>362.3</v>
       </c>
       <c r="M5">
-        <v>6.7753884</v>
+        <v>6.591915599999999</v>
       </c>
       <c r="N5">
-        <v>355.5246116</v>
+        <v>355.7080844</v>
       </c>
       <c r="O5">
-        <v>73.23806998960001</v>
+        <v>73.27586538640001</v>
       </c>
       <c r="P5">
-        <v>282.2865416104</v>
+        <v>282.4322190136</v>
       </c>
       <c r="Q5">
-        <v>469.5865416104</v>
+        <v>469.7322190136</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07193402282825952</v>
+        <v>0.07191722097517078</v>
       </c>
       <c r="T5">
         <v>0.6031690756390483</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.206</v>
       </c>
       <c r="W5">
-        <v>0.0410498</v>
+        <v>0.0399382</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +2116,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>53.472949240814</v>
+        <v>54.96126194334164</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +2127,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07090744840634119</v>
+        <v>0.07084672039108221</v>
       </c>
       <c r="C6">
-        <v>4113.495801287993</v>
+        <v>4118.383589746441</v>
       </c>
       <c r="D6">
-        <v>3950.231801287993</v>
+        <v>3955.11958974644</v>
       </c>
       <c r="E6">
         <v>-1207.564</v>
@@ -1785,37 +2160,37 @@
         <v>362.3</v>
       </c>
       <c r="M6">
-        <v>9.033851200000001</v>
+        <v>8.789220799999999</v>
       </c>
       <c r="N6">
-        <v>353.2661488</v>
+        <v>353.5107792</v>
       </c>
       <c r="O6">
-        <v>72.77282665280001</v>
+        <v>72.82322051520001</v>
       </c>
       <c r="P6">
-        <v>280.4933221472</v>
+        <v>280.6875586848</v>
       </c>
       <c r="Q6">
-        <v>467.7933221472</v>
+        <v>467.9875586848</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07215151708993875</v>
+        <v>0.0721345754073773</v>
       </c>
       <c r="T6">
         <v>0.6081888084844643</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.206</v>
       </c>
       <c r="W6">
-        <v>0.0410498</v>
+        <v>0.0399382</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +2198,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.1047119306105</v>
+        <v>41.22094645750623</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +2209,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07080740066927069</v>
+        <v>0.07073559043624875</v>
       </c>
       <c r="C7">
-        <v>4080.601912789217</v>
+        <v>4086.718446866464</v>
       </c>
       <c r="D7">
-        <v>3961.021912789217</v>
+        <v>3967.138446866464</v>
       </c>
       <c r="E7">
         <v>-1163.88</v>
@@ -1867,37 +2242,37 @@
         <v>362.3</v>
       </c>
       <c r="M7">
-        <v>11.292314</v>
+        <v>10.986526</v>
       </c>
       <c r="N7">
-        <v>351.007686</v>
+        <v>351.313474</v>
       </c>
       <c r="O7">
-        <v>72.30758331600002</v>
+        <v>72.370575644</v>
       </c>
       <c r="P7">
-        <v>278.700102684</v>
+        <v>278.942898356</v>
       </c>
       <c r="Q7">
-        <v>466.000102684</v>
+        <v>466.242898356</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07237359017817967</v>
+        <v>0.0723565057223671</v>
       </c>
       <c r="T7">
         <v>0.6133142199160996</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.206</v>
       </c>
       <c r="W7">
-        <v>0.0410498</v>
+        <v>0.0399382</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +2280,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.0837695444884</v>
+        <v>32.97675716600497</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +2291,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07070735293220015</v>
+        <v>0.07062446048141528</v>
       </c>
       <c r="C8">
-        <v>4047.767132415593</v>
+        <v>4055.126572683519</v>
       </c>
       <c r="D8">
-        <v>3971.871132415593</v>
+        <v>3979.230572683519</v>
       </c>
       <c r="E8">
         <v>-1120.196</v>
@@ -1949,37 +2324,37 @@
         <v>362.3</v>
       </c>
       <c r="M8">
-        <v>13.5507768</v>
+        <v>13.1838312</v>
       </c>
       <c r="N8">
-        <v>348.7492232</v>
+        <v>349.1161688</v>
       </c>
       <c r="O8">
-        <v>71.84233997920001</v>
+        <v>71.91793077280001</v>
       </c>
       <c r="P8">
-        <v>276.9068832208</v>
+        <v>277.1982380272</v>
       </c>
       <c r="Q8">
-        <v>464.2068832208</v>
+        <v>464.4982380272</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07260038822574484</v>
+        <v>0.07258315795895244</v>
       </c>
       <c r="T8">
         <v>0.6185486826547908</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.206</v>
       </c>
       <c r="W8">
-        <v>0.0410498</v>
+        <v>0.0399382</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +2362,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.73647462040701</v>
+        <v>27.48063097167082</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +2373,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07060730519512962</v>
+        <v>0.07051333052658182</v>
       </c>
       <c r="C9">
-        <v>4014.991947191672</v>
+        <v>4023.608639230927</v>
       </c>
       <c r="D9">
-        <v>3982.779947191672</v>
+        <v>3991.396639230926</v>
       </c>
       <c r="E9">
         <v>-1076.512</v>
@@ -2031,37 +2406,37 @@
         <v>362.3</v>
       </c>
       <c r="M9">
-        <v>15.8092396</v>
+        <v>15.3811364</v>
       </c>
       <c r="N9">
-        <v>346.4907604</v>
+        <v>346.9188636</v>
       </c>
       <c r="O9">
-        <v>71.37709664240001</v>
+        <v>71.46528590160001</v>
       </c>
       <c r="P9">
-        <v>275.1136637576</v>
+        <v>275.4535776984</v>
       </c>
       <c r="Q9">
-        <v>462.4136637576</v>
+        <v>462.7535776984</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07283206365067701</v>
+        <v>0.07281468443718477</v>
       </c>
       <c r="T9">
         <v>0.6238957144846368</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.206</v>
       </c>
       <c r="W9">
-        <v>0.0410498</v>
+        <v>0.0399382</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2444,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.91697824606314</v>
+        <v>23.55482654714642</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2455,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07050725745805912</v>
+        <v>0.07040220057174838</v>
       </c>
       <c r="C10">
-        <v>3982.276849507227</v>
+        <v>3992.165326785882</v>
       </c>
       <c r="D10">
-        <v>3993.748849507226</v>
+        <v>4003.637326785882</v>
       </c>
       <c r="E10">
         <v>-1032.828</v>
@@ -2113,37 +2488,37 @@
         <v>362.3</v>
       </c>
       <c r="M10">
-        <v>18.0677024</v>
+        <v>17.5784416</v>
       </c>
       <c r="N10">
-        <v>344.2322976</v>
+        <v>344.7215584</v>
       </c>
       <c r="O10">
-        <v>70.91185330560002</v>
+        <v>71.0126410304</v>
       </c>
       <c r="P10">
-        <v>273.3204442944</v>
+        <v>273.7089173696</v>
       </c>
       <c r="Q10">
-        <v>460.6204442944</v>
+        <v>461.0089173696</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07306877549789034</v>
+        <v>0.07305124409972649</v>
       </c>
       <c r="T10">
         <v>0.6293589861368708</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.206</v>
       </c>
       <c r="W10">
-        <v>0.0410498</v>
+        <v>0.0399382</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2526,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.05235596530525</v>
+        <v>20.61047322875311</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2537,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07040720972098859</v>
+        <v>0.07029107061691492</v>
       </c>
       <c r="C11">
-        <v>3949.622337191348</v>
+        <v>3960.797323996274</v>
       </c>
       <c r="D11">
-        <v>4004.778337191348</v>
+        <v>4015.953323996274</v>
       </c>
       <c r="E11">
         <v>-989.144</v>
@@ -2195,37 +2570,37 @@
         <v>362.3</v>
       </c>
       <c r="M11">
-        <v>20.3261652</v>
+        <v>19.7757468</v>
       </c>
       <c r="N11">
-        <v>341.9738348</v>
+        <v>342.5242532</v>
       </c>
       <c r="O11">
-        <v>70.4466099688</v>
+        <v>70.55999615920001</v>
       </c>
       <c r="P11">
-        <v>271.5272248312</v>
+        <v>271.9642570408</v>
       </c>
       <c r="Q11">
-        <v>458.8272248312</v>
+        <v>459.2642570408</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07331068980328416</v>
+        <v>0.07329300287573068</v>
       </c>
       <c r="T11">
         <v>0.6349423296935494</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.206</v>
       </c>
       <c r="W11">
-        <v>0.0410498</v>
+        <v>0.0399382</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2608,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.82431641360467</v>
+        <v>18.32042064778055</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2619,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07030716198391805</v>
+        <v>0.07017994066208147</v>
       </c>
       <c r="C12">
-        <v>3917.02891358774</v>
+        <v>3929.505328009805</v>
       </c>
       <c r="D12">
-        <v>4015.86891358774</v>
+        <v>4028.345328009806</v>
       </c>
       <c r="E12">
         <v>-945.46</v>
@@ -2277,37 +2652,37 @@
         <v>362.3</v>
       </c>
       <c r="M12">
-        <v>22.584628</v>
+        <v>21.973052</v>
       </c>
       <c r="N12">
-        <v>339.715372</v>
+        <v>340.326948</v>
       </c>
       <c r="O12">
-        <v>69.981366632</v>
+        <v>70.107351288</v>
       </c>
       <c r="P12">
-        <v>269.734005368</v>
+        <v>270.219596712</v>
       </c>
       <c r="Q12">
-        <v>457.034005368</v>
+        <v>457.519596712</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07355797998213118</v>
+        <v>0.07354013406897941</v>
       </c>
       <c r="T12">
         <v>0.6406497475514875</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.206</v>
       </c>
       <c r="W12">
-        <v>0.0410498</v>
+        <v>0.0399382</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2690,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.0418847722442</v>
+        <v>16.48837858300249</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2701,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07020711424684756</v>
+        <v>0.07006881070724802</v>
       </c>
       <c r="C13">
-        <v>3884.4970876313</v>
+        <v>3898.290044605561</v>
       </c>
       <c r="D13">
-        <v>4027.0210876313</v>
+        <v>4040.814044605561</v>
       </c>
       <c r="E13">
         <v>-901.7760000000001</v>
@@ -2359,37 +2734,37 @@
         <v>362.3</v>
       </c>
       <c r="M13">
-        <v>24.8430908</v>
+        <v>24.17035719999999</v>
       </c>
       <c r="N13">
-        <v>337.4569092</v>
+        <v>338.1296428</v>
       </c>
       <c r="O13">
-        <v>69.51612329520002</v>
+        <v>69.65470641680001</v>
       </c>
       <c r="P13">
-        <v>267.9407859048</v>
+        <v>268.4749363832</v>
       </c>
       <c r="Q13">
-        <v>455.2407859048</v>
+        <v>455.7749363832</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07381082724364893</v>
+        <v>0.07379281877218878</v>
       </c>
       <c r="T13">
         <v>0.6464854219905031</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.206</v>
       </c>
       <c r="W13">
-        <v>0.0410498</v>
+        <v>0.0399382</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2772,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.58353161113109</v>
+        <v>14.98943507545681</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2783,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07010706650977701</v>
+        <v>0.06995768075241456</v>
       </c>
       <c r="C14">
-        <v>3852.027373925988</v>
+        <v>3867.15218832799</v>
       </c>
       <c r="D14">
-        <v>4038.235373925988</v>
+        <v>4053.360188327989</v>
       </c>
       <c r="E14">
         <v>-858.092</v>
@@ -2441,37 +2816,37 @@
         <v>362.3</v>
       </c>
       <c r="M14">
-        <v>27.1015536</v>
+        <v>26.3676624</v>
       </c>
       <c r="N14">
-        <v>335.1984464</v>
+        <v>335.9323376</v>
       </c>
       <c r="O14">
-        <v>69.05087995840002</v>
+        <v>69.20206154560002</v>
       </c>
       <c r="P14">
-        <v>266.1475664416</v>
+        <v>266.7302760544</v>
       </c>
       <c r="Q14">
-        <v>453.4475664416</v>
+        <v>454.0302760544</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07406942103383751</v>
+        <v>0.07405124630956199</v>
       </c>
       <c r="T14">
         <v>0.6524537253940415</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.206</v>
       </c>
       <c r="W14">
-        <v>0.0410498</v>
+        <v>0.0399382</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2854,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>13.3682373102035</v>
+        <v>13.74031548583541</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2865,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07012056077270649</v>
+        <v>0.07000138079758109</v>
       </c>
       <c r="C15">
-        <v>3806.827168068112</v>
+        <v>3818.525338483809</v>
       </c>
       <c r="D15">
-        <v>4036.719168068112</v>
+        <v>4048.417338483809</v>
       </c>
       <c r="E15">
         <v>-814.408</v>
@@ -2523,37 +2898,37 @@
         <v>362.3</v>
       </c>
       <c r="M15">
-        <v>29.9846976</v>
+        <v>29.4168056</v>
       </c>
       <c r="N15">
-        <v>332.3153024</v>
+        <v>332.8831944</v>
       </c>
       <c r="O15">
-        <v>68.45695229440001</v>
+        <v>68.57393804640002</v>
       </c>
       <c r="P15">
-        <v>263.8583501056</v>
+        <v>264.3092563536</v>
       </c>
       <c r="Q15">
-        <v>451.1583501056</v>
+        <v>451.6092563536</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07433395950885803</v>
+        <v>0.07431561470986332</v>
       </c>
       <c r="T15">
         <v>0.6585592311746727</v>
       </c>
       <c r="U15">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.206</v>
       </c>
       <c r="W15">
-        <v>0.0419232</v>
+        <v>0.0411292</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2936,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.08282987653009</v>
+        <v>12.31608914055577</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2947,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07002924703563596</v>
+        <v>0.06990216084274764</v>
       </c>
       <c r="C16">
-        <v>3773.425386926358</v>
+        <v>3786.081401437429</v>
       </c>
       <c r="D16">
-        <v>4047.001386926358</v>
+        <v>4059.65740143743</v>
       </c>
       <c r="E16">
         <v>-770.7239999999999</v>
@@ -2605,37 +2980,37 @@
         <v>362.3</v>
       </c>
       <c r="M16">
-        <v>32.2912128</v>
+        <v>31.6796368</v>
       </c>
       <c r="N16">
-        <v>330.0087872</v>
+        <v>330.6203632</v>
       </c>
       <c r="O16">
-        <v>67.98181016320001</v>
+        <v>68.10779481920001</v>
       </c>
       <c r="P16">
-        <v>262.0269770368</v>
+        <v>262.5125683808</v>
       </c>
       <c r="Q16">
-        <v>449.3269770368</v>
+        <v>449.8125683808</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07460465004143717</v>
+        <v>0.07458613121249726</v>
       </c>
       <c r="T16">
         <v>0.6648067254618304</v>
       </c>
       <c r="U16">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.206</v>
       </c>
       <c r="W16">
-        <v>0.0419232</v>
+        <v>0.0411292</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +3018,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.21977059963508</v>
+        <v>11.43636848765892</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +3029,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.06993793329856544</v>
+        <v>0.06980294088791417</v>
       </c>
       <c r="C17">
-        <v>3740.0761207133</v>
+        <v>3753.700052187713</v>
       </c>
       <c r="D17">
-        <v>4057.3361207133</v>
+        <v>4070.960052187713</v>
       </c>
       <c r="E17">
         <v>-727.0400000000001</v>
@@ -2687,37 +3062,37 @@
         <v>362.3</v>
       </c>
       <c r="M17">
-        <v>34.597728</v>
+        <v>33.94246799999999</v>
       </c>
       <c r="N17">
-        <v>327.702272</v>
+        <v>328.357532</v>
       </c>
       <c r="O17">
-        <v>67.50666803200001</v>
+        <v>67.641651592</v>
       </c>
       <c r="P17">
-        <v>260.195603968</v>
+        <v>260.715880408</v>
       </c>
       <c r="Q17">
-        <v>447.495603968</v>
+        <v>448.015880408</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07488170976301817</v>
+        <v>0.07486301280931079</v>
       </c>
       <c r="T17">
         <v>0.6712012196145682</v>
       </c>
       <c r="U17">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.206</v>
       </c>
       <c r="W17">
-        <v>0.0419232</v>
+        <v>0.0411292</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +3100,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.47178589299274</v>
+        <v>10.673943921815</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +3111,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07012610756149493</v>
+        <v>0.06970372093308072</v>
       </c>
       <c r="C18">
-        <v>3675.15226493029</v>
+        <v>3721.381814953541</v>
       </c>
       <c r="D18">
-        <v>4036.09626493029</v>
+        <v>4082.325814953542</v>
       </c>
       <c r="E18">
         <v>-683.356</v>
@@ -2769,45 +3144,45 @@
         <v>362.3</v>
       </c>
       <c r="M18">
-        <v>38.44192</v>
+        <v>36.2052992</v>
       </c>
       <c r="N18">
-        <v>323.85808</v>
+        <v>326.0947008</v>
       </c>
       <c r="O18">
-        <v>66.71476448000001</v>
+        <v>67.17550836480001</v>
       </c>
       <c r="P18">
-        <v>257.14331552</v>
+        <v>258.9191924352</v>
       </c>
       <c r="Q18">
-        <v>444.44331552</v>
+        <v>446.2191924352</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07516536614463681</v>
+        <v>0.0751464868250961</v>
       </c>
       <c r="T18">
         <v>0.6777479636280855</v>
       </c>
       <c r="U18">
-        <v>0.055</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.206</v>
       </c>
       <c r="W18">
-        <v>0.04367</v>
+        <v>0.0411292</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.42460730369347</v>
+        <v>10.00682242670156</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +3193,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07005226182442439</v>
+        <v>0.06983396697824726</v>
       </c>
       <c r="C19">
-        <v>3639.776913914275</v>
+        <v>3662.790954894001</v>
       </c>
       <c r="D19">
-        <v>4044.404913914275</v>
+        <v>4067.418954894002</v>
       </c>
       <c r="E19">
         <v>-639.6719999999999</v>
@@ -2851,37 +3226,37 @@
         <v>362.3</v>
       </c>
       <c r="M19">
-        <v>40.84454</v>
+        <v>39.730598</v>
       </c>
       <c r="N19">
-        <v>321.45546</v>
+        <v>322.569402</v>
       </c>
       <c r="O19">
-        <v>66.21982476000001</v>
+        <v>66.44929681200001</v>
       </c>
       <c r="P19">
-        <v>255.23563524</v>
+        <v>256.120105188</v>
       </c>
       <c r="Q19">
-        <v>442.53563524</v>
+        <v>443.420105188</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07545585761978843</v>
+        <v>0.07543679154005695</v>
       </c>
       <c r="T19">
         <v>0.6844524605093985</v>
       </c>
       <c r="U19">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.206</v>
       </c>
       <c r="W19">
-        <v>0.04367</v>
+        <v>0.042479</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +3264,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.870218638770321</v>
+        <v>9.118916357614351</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +3275,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.06997841608735386</v>
+        <v>0.06974824502341381</v>
       </c>
       <c r="C20">
-        <v>3604.435841591438</v>
+        <v>3628.905688074597</v>
       </c>
       <c r="D20">
-        <v>4052.747841591438</v>
+        <v>4077.217688074597</v>
       </c>
       <c r="E20">
         <v>-595.9880000000001</v>
@@ -2933,37 +3308,37 @@
         <v>362.3</v>
       </c>
       <c r="M20">
-        <v>43.24715999999999</v>
+        <v>42.06769199999999</v>
       </c>
       <c r="N20">
-        <v>319.05284</v>
+        <v>320.232308</v>
       </c>
       <c r="O20">
-        <v>65.72488504</v>
+        <v>65.96785544800001</v>
       </c>
       <c r="P20">
-        <v>253.32795496</v>
+        <v>254.264452552</v>
       </c>
       <c r="Q20">
-        <v>440.62795496</v>
+        <v>441.564452552</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07575343425287057</v>
+        <v>0.07573417685782172</v>
       </c>
       <c r="T20">
         <v>0.6913204817048897</v>
       </c>
       <c r="U20">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.206</v>
       </c>
       <c r="W20">
-        <v>0.04367</v>
+        <v>0.042479</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +3346,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.377428714394195</v>
+        <v>8.612309893302443</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +3357,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06990457035028336</v>
+        <v>0.06966252306858035</v>
       </c>
       <c r="C21">
-        <v>3569.12926053383</v>
+        <v>3595.067747109611</v>
       </c>
       <c r="D21">
-        <v>4061.12526053383</v>
+        <v>4087.063747109612</v>
       </c>
       <c r="E21">
         <v>-552.304</v>
@@ -3015,37 +3390,37 @@
         <v>362.3</v>
       </c>
       <c r="M21">
-        <v>45.64978</v>
+        <v>44.404786</v>
       </c>
       <c r="N21">
-        <v>316.65022</v>
+        <v>317.895214</v>
       </c>
       <c r="O21">
-        <v>65.22994532</v>
+        <v>65.486414084</v>
       </c>
       <c r="P21">
-        <v>251.42027468</v>
+        <v>252.408799916</v>
       </c>
       <c r="Q21">
-        <v>438.72027468</v>
+        <v>439.708799916</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07605835845713993</v>
+        <v>0.07603890502293871</v>
       </c>
       <c r="T21">
         <v>0.69835808367064</v>
       </c>
       <c r="U21">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.206</v>
       </c>
       <c r="W21">
-        <v>0.04367</v>
+        <v>0.042479</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3428,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.936511413636604</v>
+        <v>8.159030425233894</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3439,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07006892461321283</v>
+        <v>0.06957680111374691</v>
       </c>
       <c r="C22">
-        <v>3506.847136551015</v>
+        <v>3561.27747569015</v>
       </c>
       <c r="D22">
-        <v>4042.527136551015</v>
+        <v>4096.95747569015</v>
       </c>
       <c r="E22">
         <v>-508.62</v>
@@ -3097,45 +3472,45 @@
         <v>362.3</v>
       </c>
       <c r="M22">
-        <v>49.36292</v>
+        <v>46.74187999999999</v>
       </c>
       <c r="N22">
-        <v>312.93708</v>
+        <v>315.55812</v>
       </c>
       <c r="O22">
-        <v>64.46503848000002</v>
+        <v>65.00497272000001</v>
       </c>
       <c r="P22">
-        <v>248.47204152</v>
+        <v>250.55314728</v>
       </c>
       <c r="Q22">
-        <v>435.77204152</v>
+        <v>437.85314728</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07637090576651603</v>
+        <v>0.07635125139218363</v>
       </c>
       <c r="T22">
         <v>0.7055716256855341</v>
       </c>
       <c r="U22">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.206</v>
       </c>
       <c r="W22">
-        <v>0.04486100000000001</v>
+        <v>0.042479</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.339517192256861</v>
+        <v>7.751078903972199</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3521,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07000698887614229</v>
+        <v>0.06962447115891343</v>
       </c>
       <c r="C23">
-        <v>3470.151672039712</v>
+        <v>3512.085661383654</v>
       </c>
       <c r="D23">
-        <v>4049.515672039712</v>
+        <v>4091.449661383654</v>
       </c>
       <c r="E23">
         <v>-464.936</v>
@@ -3179,37 +3554,37 @@
         <v>362.3</v>
       </c>
       <c r="M23">
-        <v>51.831066</v>
+        <v>49.8128652</v>
       </c>
       <c r="N23">
-        <v>310.468934</v>
+        <v>312.4871348</v>
       </c>
       <c r="O23">
-        <v>63.956600404</v>
+        <v>64.37234976880001</v>
       </c>
       <c r="P23">
-        <v>246.512333596</v>
+        <v>248.1147850312</v>
       </c>
       <c r="Q23">
-        <v>433.812333596</v>
+        <v>435.4147850312</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.0766913656660029</v>
+        <v>0.07667150526444738</v>
       </c>
       <c r="T23">
         <v>0.7129677890172609</v>
       </c>
       <c r="U23">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.206</v>
       </c>
       <c r="W23">
-        <v>0.04486100000000001</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3592,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.990016373577962</v>
+        <v>7.273221456853681</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3603,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06994505313907178</v>
+        <v>0.06954510120407999</v>
       </c>
       <c r="C24">
-        <v>3433.480412291688</v>
+        <v>3477.580311372068</v>
       </c>
       <c r="D24">
-        <v>4056.528412291687</v>
+        <v>4100.628311372067</v>
       </c>
       <c r="E24">
         <v>-421.2520000000001</v>
@@ -3261,37 +3636,37 @@
         <v>362.3</v>
       </c>
       <c r="M24">
-        <v>54.299212</v>
+        <v>52.1849064</v>
       </c>
       <c r="N24">
-        <v>308.000788</v>
+        <v>310.1150936</v>
       </c>
       <c r="O24">
-        <v>63.448162328</v>
+        <v>63.88370928160001</v>
       </c>
       <c r="P24">
-        <v>244.552625672</v>
+        <v>246.2313843184</v>
       </c>
       <c r="Q24">
-        <v>431.852625672</v>
+        <v>433.5313843184</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07702004248598945</v>
+        <v>0.07699997077446151</v>
       </c>
       <c r="T24">
         <v>0.7205535975626216</v>
       </c>
       <c r="U24">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.206</v>
       </c>
       <c r="W24">
-        <v>0.04486100000000001</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3674,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.672288356597146</v>
+        <v>6.942620481542151</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3685,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06988311740200125</v>
+        <v>0.06946573124924653</v>
       </c>
       <c r="C25">
-        <v>3396.833483274735</v>
+        <v>3443.11623623683</v>
       </c>
       <c r="D25">
-        <v>4063.565483274735</v>
+        <v>4109.84823623683</v>
       </c>
       <c r="E25">
         <v>-377.568</v>
@@ -3343,37 +3718,37 @@
         <v>362.3</v>
       </c>
       <c r="M25">
-        <v>56.767358</v>
+        <v>54.5569476</v>
       </c>
       <c r="N25">
-        <v>305.532642</v>
+        <v>307.7430524</v>
       </c>
       <c r="O25">
-        <v>62.939724252</v>
+        <v>63.3950687944</v>
       </c>
       <c r="P25">
-        <v>242.592917748</v>
+        <v>244.3479836056</v>
       </c>
       <c r="Q25">
-        <v>429.892917748</v>
+        <v>431.6479836056</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07735725636623539</v>
+        <v>0.07733696785616431</v>
       </c>
       <c r="T25">
         <v>0.7283364400961737</v>
       </c>
       <c r="U25">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.206</v>
       </c>
       <c r="W25">
-        <v>0.04486100000000001</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3756,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.382188862832052</v>
+        <v>6.640767417127273</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3767,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07008796566493072</v>
+        <v>0.06938636129441307</v>
       </c>
       <c r="C26">
-        <v>3329.967479534244</v>
+        <v>3408.69371501481</v>
       </c>
       <c r="D26">
-        <v>4040.383479534245</v>
+        <v>4119.10971501481</v>
       </c>
       <c r="E26">
         <v>-333.884</v>
@@ -3425,45 +3800,45 @@
         <v>362.3</v>
       </c>
       <c r="M26">
-        <v>60.7032864</v>
+        <v>56.9289888</v>
       </c>
       <c r="N26">
-        <v>301.5967136</v>
+        <v>305.3710112</v>
       </c>
       <c r="O26">
-        <v>62.12892300160001</v>
+        <v>62.9064283072</v>
       </c>
       <c r="P26">
-        <v>239.4677905984</v>
+        <v>242.4645828928</v>
       </c>
       <c r="Q26">
-        <v>426.7677905984</v>
+        <v>429.7645828928</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07770334429596149</v>
+        <v>0.07768283328212246</v>
       </c>
       <c r="T26">
         <v>0.7363240942753455</v>
       </c>
       <c r="U26">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.206</v>
       </c>
       <c r="W26">
-        <v>0.0459726</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>5.968375379425916</v>
+        <v>6.36406877474697</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3849,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.0700371459278602</v>
+        <v>0.06950549133957962</v>
       </c>
       <c r="C27">
-        <v>3292.00987727235</v>
+        <v>3351.124371682802</v>
       </c>
       <c r="D27">
-        <v>4046.10987727235</v>
+        <v>4105.224371682802</v>
       </c>
       <c r="E27">
         <v>-290.2</v>
@@ -3507,37 +3882,37 @@
         <v>362.3</v>
       </c>
       <c r="M27">
-        <v>63.23258999999999</v>
+        <v>60.39313</v>
       </c>
       <c r="N27">
-        <v>299.06741</v>
+        <v>301.90687</v>
       </c>
       <c r="O27">
-        <v>61.60788646</v>
+        <v>62.19281522000001</v>
       </c>
       <c r="P27">
-        <v>237.45952354</v>
+        <v>239.71405478</v>
       </c>
       <c r="Q27">
-        <v>424.75952354</v>
+        <v>427.01405478</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07805866123714694</v>
+        <v>0.07803792178610615</v>
       </c>
       <c r="T27">
         <v>0.744524752565962</v>
       </c>
       <c r="U27">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.206</v>
       </c>
       <c r="W27">
-        <v>0.0459726</v>
+        <v>0.0439082</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3920,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.729640364248879</v>
+        <v>5.999026710488429</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3931,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06998632619078968</v>
+        <v>0.06943406138474616</v>
       </c>
       <c r="C28">
-        <v>3254.068529988459</v>
+        <v>3315.754714376753</v>
       </c>
       <c r="D28">
-        <v>4051.852529988458</v>
+        <v>4113.538714376753</v>
       </c>
       <c r="E28">
         <v>-246.5160000000001</v>
@@ -3589,37 +3964,37 @@
         <v>362.3</v>
       </c>
       <c r="M28">
-        <v>65.76189359999999</v>
+        <v>62.8088552</v>
       </c>
       <c r="N28">
-        <v>296.5381064</v>
+        <v>299.4911448</v>
       </c>
       <c r="O28">
-        <v>61.08684991840001</v>
+        <v>61.69517582880001</v>
       </c>
       <c r="P28">
-        <v>235.4512564816</v>
+        <v>237.7959689712</v>
       </c>
       <c r="Q28">
-        <v>422.7512564816</v>
+        <v>425.0959689712</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07842358133890498</v>
+        <v>0.07840260727668399</v>
       </c>
       <c r="T28">
         <v>0.7529470502698383</v>
       </c>
       <c r="U28">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.206</v>
       </c>
       <c r="W28">
-        <v>0.0459726</v>
+        <v>0.0439082</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +4002,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.509269581008538</v>
+        <v>5.768294913931181</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +4013,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.06993550645371915</v>
+        <v>0.0693626314299127</v>
       </c>
       <c r="C29">
-        <v>3216.143506993119</v>
+        <v>3280.41880362308</v>
       </c>
       <c r="D29">
-        <v>4057.611506993119</v>
+        <v>4121.88680362308</v>
       </c>
       <c r="E29">
         <v>-202.8319999999999</v>
@@ -3671,37 +4046,37 @@
         <v>362.3</v>
       </c>
       <c r="M29">
-        <v>68.2911972</v>
+        <v>65.22458040000001</v>
       </c>
       <c r="N29">
-        <v>294.0088028</v>
+        <v>297.0754196</v>
       </c>
       <c r="O29">
-        <v>60.56581337680001</v>
+        <v>61.19753643760001</v>
       </c>
       <c r="P29">
-        <v>233.4429894232</v>
+        <v>235.8778831624</v>
       </c>
       <c r="Q29">
-        <v>420.7429894232</v>
+        <v>423.1778831624</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07879849925167007</v>
+        <v>0.07877728415056534</v>
       </c>
       <c r="T29">
         <v>0.7616000958560125</v>
       </c>
       <c r="U29">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.206</v>
       </c>
       <c r="W29">
-        <v>0.0459726</v>
+        <v>0.0439082</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +4084,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.305222559489702</v>
+        <v>5.554654361563359</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +4095,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.06988468671664863</v>
+        <v>0.06929120147507925</v>
       </c>
       <c r="C30">
-        <v>3178.234877991496</v>
+        <v>3245.116845297161</v>
       </c>
       <c r="D30">
-        <v>4063.386877991496</v>
+        <v>4130.268845297162</v>
       </c>
       <c r="E30">
         <v>-159.1479999999999</v>
@@ -3753,37 +4128,37 @@
         <v>362.3</v>
       </c>
       <c r="M30">
-        <v>70.8205008</v>
+        <v>67.6403056</v>
       </c>
       <c r="N30">
-        <v>291.4794992</v>
+        <v>294.6596944</v>
       </c>
       <c r="O30">
-        <v>60.04477683520001</v>
+        <v>60.69989704640001</v>
       </c>
       <c r="P30">
-        <v>231.4347223648</v>
+        <v>233.9597973536</v>
       </c>
       <c r="Q30">
-        <v>418.7347223648</v>
+        <v>421.2597973536</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07918383155090088</v>
+        <v>0.07916236871538784</v>
       </c>
       <c r="T30">
         <v>0.7704935038195806</v>
       </c>
       <c r="U30">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.206</v>
       </c>
       <c r="W30">
-        <v>0.0459726</v>
+        <v>0.0439082</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +4166,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.115750325222213</v>
+        <v>5.356273848650383</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +4177,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.06983386697957811</v>
+        <v>0.06921977152024578</v>
       </c>
       <c r="C31">
-        <v>3140.342713086174</v>
+        <v>3209.849046952427</v>
       </c>
       <c r="D31">
-        <v>4069.178713086174</v>
+        <v>4138.685046952427</v>
       </c>
       <c r="E31">
         <v>-115.4640000000002</v>
@@ -3835,37 +4210,37 @@
         <v>362.3</v>
       </c>
       <c r="M31">
-        <v>73.34980439999998</v>
+        <v>70.05603079999999</v>
       </c>
       <c r="N31">
-        <v>288.9501956</v>
+        <v>292.2439692</v>
       </c>
       <c r="O31">
-        <v>59.52374029360001</v>
+        <v>60.20225765520001</v>
       </c>
       <c r="P31">
-        <v>229.4264553064</v>
+        <v>232.0417115448</v>
       </c>
       <c r="Q31">
-        <v>416.7264553064</v>
+        <v>419.3417115448</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07958001828109593</v>
+        <v>0.07955830073274053</v>
       </c>
       <c r="T31">
         <v>0.7796374303173336</v>
       </c>
       <c r="U31">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.206</v>
       </c>
       <c r="W31">
-        <v>0.0459726</v>
+        <v>0.0439082</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +4248,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.939345141593862</v>
+        <v>5.17157475042106</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +4259,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.06978304724250758</v>
+        <v>0.06914834156541232</v>
       </c>
       <c r="C32">
-        <v>3102.467082779998</v>
+        <v>3174.615617837465</v>
       </c>
       <c r="D32">
-        <v>4074.987082779998</v>
+        <v>4147.135617837464</v>
       </c>
       <c r="E32">
         <v>-71.7800000000002</v>
@@ -3917,37 +4292,37 @@
         <v>362.3</v>
       </c>
       <c r="M32">
-        <v>75.87910799999999</v>
+        <v>72.47175599999998</v>
       </c>
       <c r="N32">
-        <v>286.420892</v>
+        <v>289.828244</v>
       </c>
       <c r="O32">
-        <v>59.00270375200001</v>
+        <v>59.70461826400001</v>
       </c>
       <c r="P32">
-        <v>227.418188248</v>
+        <v>230.123625736</v>
       </c>
       <c r="Q32">
-        <v>414.718188248</v>
+        <v>417.4236257360001</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07998752463215369</v>
+        <v>0.07996554509344617</v>
       </c>
       <c r="T32">
         <v>0.7890426118578795</v>
       </c>
       <c r="U32">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.206</v>
       </c>
       <c r="W32">
-        <v>0.0459726</v>
+        <v>0.0439082</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +4330,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.774700303540733</v>
+        <v>4.999188925407025</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +4341,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.06973222750543705</v>
+        <v>0.06907691161057887</v>
       </c>
       <c r="C33">
-        <v>3064.608057978932</v>
+        <v>3139.416768913382</v>
       </c>
       <c r="D33">
-        <v>4080.812057978932</v>
+        <v>4155.620768913382</v>
       </c>
       <c r="E33">
         <v>-28.096</v>
@@ -3999,37 +4374,37 @@
         <v>362.3</v>
       </c>
       <c r="M33">
-        <v>78.40841159999999</v>
+        <v>74.8874812</v>
       </c>
       <c r="N33">
-        <v>283.8915884</v>
+        <v>287.4125188</v>
       </c>
       <c r="O33">
-        <v>58.48166721040001</v>
+        <v>59.20697887280001</v>
       </c>
       <c r="P33">
-        <v>225.4099211896</v>
+        <v>228.2055399272</v>
       </c>
       <c r="Q33">
-        <v>412.7099211896</v>
+        <v>415.5055399272001</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08040684276150298</v>
+        <v>0.0803845936385201</v>
       </c>
       <c r="T33">
         <v>0.7987204073561225</v>
       </c>
       <c r="U33">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.206</v>
       </c>
       <c r="W33">
-        <v>0.0459726</v>
+        <v>0.0439082</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4412,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.620677713103936</v>
+        <v>4.837924766522926</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4423,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07034201576836653</v>
+        <v>0.06900548165574541</v>
       </c>
       <c r="C34">
-        <v>2952.110306863401</v>
+        <v>3104.252712871356</v>
       </c>
       <c r="D34">
-        <v>4011.998306863401</v>
+        <v>4164.140712871356</v>
       </c>
       <c r="E34">
         <v>15.58799999999997</v>
@@ -4081,45 +4456,45 @@
         <v>362.3</v>
       </c>
       <c r="M34">
-        <v>84.57222399999999</v>
+        <v>77.30320639999999</v>
       </c>
       <c r="N34">
-        <v>277.727776</v>
+        <v>284.9967936</v>
       </c>
       <c r="O34">
-        <v>57.211921856</v>
+        <v>58.70933948160001</v>
       </c>
       <c r="P34">
-        <v>220.515854144</v>
+        <v>226.2874541184</v>
       </c>
       <c r="Q34">
-        <v>407.815854144</v>
+        <v>413.5874541184</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08083849377700961</v>
+        <v>0.08081596714080208</v>
       </c>
       <c r="T34">
         <v>0.8086828438984315</v>
       </c>
       <c r="U34">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.206</v>
       </c>
       <c r="W34">
-        <v>0.048037</v>
+        <v>0.0439082</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.283912410769759</v>
+        <v>4.686739617569085</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4505,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07031184003129601</v>
+        <v>0.06893405170091195</v>
       </c>
       <c r="C35">
-        <v>2911.776969940886</v>
+        <v>3069.123664150402</v>
       </c>
       <c r="D35">
-        <v>4015.348969940886</v>
+        <v>4172.695664150402</v>
       </c>
       <c r="E35">
         <v>59.27199999999993</v>
@@ -4163,45 +4538,45 @@
         <v>362.3</v>
       </c>
       <c r="M35">
-        <v>87.21510599999999</v>
+        <v>79.71893159999999</v>
       </c>
       <c r="N35">
-        <v>275.084894</v>
+        <v>282.5810684</v>
       </c>
       <c r="O35">
-        <v>56.66748816400001</v>
+        <v>58.21170009040002</v>
       </c>
       <c r="P35">
-        <v>218.417405836</v>
+        <v>224.3693683096</v>
       </c>
       <c r="Q35">
-        <v>405.717405836</v>
+        <v>411.6693683096</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08128302989745673</v>
+        <v>0.08126021746404768</v>
       </c>
       <c r="T35">
         <v>0.8189426666061824</v>
       </c>
       <c r="U35">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.206</v>
       </c>
       <c r="W35">
-        <v>0.048037</v>
+        <v>0.0439082</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.154096883170675</v>
+        <v>4.544717204915477</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4587,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07028166429422548</v>
+        <v>0.0695375217460785</v>
       </c>
       <c r="C36">
-        <v>2871.449234380257</v>
+        <v>2954.250983943923</v>
       </c>
       <c r="D36">
-        <v>4018.705234380257</v>
+        <v>4101.506983943923</v>
       </c>
       <c r="E36">
         <v>102.9560000000001</v>
@@ -4245,37 +4620,37 @@
         <v>362.3</v>
       </c>
       <c r="M36">
-        <v>89.85798800000001</v>
+        <v>85.84779680000001</v>
       </c>
       <c r="N36">
-        <v>272.442012</v>
+        <v>276.4522032</v>
       </c>
       <c r="O36">
-        <v>56.123054472</v>
+        <v>56.9491538592</v>
       </c>
       <c r="P36">
-        <v>216.318957528</v>
+        <v>219.5030493408</v>
       </c>
       <c r="Q36">
-        <v>403.618957528</v>
+        <v>406.8030493408</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08174103680943255</v>
+        <v>0.08171792991830075</v>
       </c>
       <c r="T36">
         <v>0.8295133930323501</v>
       </c>
       <c r="U36">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.206</v>
       </c>
       <c r="W36">
-        <v>0.048037</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4658,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.031917563077419</v>
+        <v>4.22025973297896</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4669,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07100181855715496</v>
+        <v>0.06948594179124505</v>
       </c>
       <c r="C37">
-        <v>2749.167753983016</v>
+        <v>2916.556568220581</v>
       </c>
       <c r="D37">
-        <v>3940.107753983016</v>
+        <v>4107.496568220581</v>
       </c>
       <c r="E37">
         <v>146.6400000000001</v>
@@ -4327,45 +4702,45 @@
         <v>362.3</v>
       </c>
       <c r="M37">
-        <v>96.62900800000001</v>
+        <v>88.37273200000001</v>
       </c>
       <c r="N37">
-        <v>265.670992</v>
+        <v>273.927268</v>
       </c>
       <c r="O37">
-        <v>54.72822435200001</v>
+        <v>56.42901720800001</v>
       </c>
       <c r="P37">
-        <v>210.942767648</v>
+        <v>217.498250792</v>
       </c>
       <c r="Q37">
-        <v>398.242767648</v>
+        <v>404.798250792</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08221313624177687</v>
+        <v>0.08218972583268469</v>
       </c>
       <c r="T37">
         <v>0.840409372579323</v>
       </c>
       <c r="U37">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.206</v>
       </c>
       <c r="W37">
-        <v>0.0501808</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.749391694055267</v>
+        <v>4.099680883465275</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4751,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07099308082008443</v>
+        <v>0.07043480183641158</v>
       </c>
       <c r="C38">
-        <v>2706.418959535687</v>
+        <v>2765.414603801488</v>
       </c>
       <c r="D38">
-        <v>3941.042959535687</v>
+        <v>4000.038603801488</v>
       </c>
       <c r="E38">
         <v>190.3239999999998</v>
@@ -4409,37 +4784,37 @@
         <v>362.3</v>
       </c>
       <c r="M38">
-        <v>99.3898368</v>
+        <v>96.40185119999998</v>
       </c>
       <c r="N38">
-        <v>262.9101632</v>
+        <v>265.8981488000001</v>
       </c>
       <c r="O38">
-        <v>54.15949361920001</v>
+        <v>54.77501865280001</v>
       </c>
       <c r="P38">
-        <v>208.7506695808</v>
+        <v>211.1231301472</v>
       </c>
       <c r="Q38">
-        <v>396.0506695808</v>
+        <v>398.4231301472</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08269998878138193</v>
+        <v>0.0826762653693931</v>
       </c>
       <c r="T38">
         <v>0.8516458514871387</v>
       </c>
       <c r="U38">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.206</v>
       </c>
       <c r="W38">
-        <v>0.0501808</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4822,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.645241924775954</v>
+        <v>3.758226584760855</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4833,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07098434308301392</v>
+        <v>0.07041101188157814</v>
       </c>
       <c r="C39">
-        <v>2663.670609145791</v>
+        <v>2724.3560431985</v>
       </c>
       <c r="D39">
-        <v>3941.978609145791</v>
+        <v>4002.6640431985</v>
       </c>
       <c r="E39">
         <v>234.0079999999998</v>
@@ -4491,37 +4866,37 @@
         <v>362.3</v>
       </c>
       <c r="M39">
-        <v>102.1506656</v>
+        <v>99.07968039999999</v>
       </c>
       <c r="N39">
-        <v>260.1493344</v>
+        <v>263.2203196</v>
       </c>
       <c r="O39">
-        <v>53.59076288640001</v>
+        <v>54.22338583760001</v>
       </c>
       <c r="P39">
-        <v>206.5585715136</v>
+        <v>208.9969337624</v>
       </c>
       <c r="Q39">
-        <v>393.8585715136001</v>
+        <v>396.2969337624</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08320229695716494</v>
+        <v>0.08317825060567957</v>
       </c>
       <c r="T39">
         <v>0.8632390440110755</v>
       </c>
       <c r="U39">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0.206</v>
       </c>
       <c r="W39">
-        <v>0.0501808</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4904,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.546721872754983</v>
+        <v>3.656652893280831</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4915,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.0723936893459434</v>
+        <v>0.07038722192674468</v>
       </c>
       <c r="C40">
-        <v>2474.603118138675</v>
+        <v>2683.300931291829</v>
       </c>
       <c r="D40">
-        <v>3796.595118138675</v>
+        <v>4005.29293129183</v>
       </c>
       <c r="E40">
         <v>277.692</v>
@@ -4573,45 +4948,45 @@
         <v>362.3</v>
       </c>
       <c r="M40">
-        <v>112.7134568</v>
+        <v>101.7575096</v>
       </c>
       <c r="N40">
-        <v>249.5865432</v>
+        <v>260.5424904</v>
       </c>
       <c r="O40">
-        <v>51.41482789920001</v>
+        <v>53.67175302240001</v>
       </c>
       <c r="P40">
-        <v>198.1717153008</v>
+        <v>206.8707373776</v>
       </c>
       <c r="Q40">
-        <v>385.4717153008</v>
+        <v>394.1707373776</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08372080862248935</v>
+        <v>0.08369642891410431</v>
       </c>
       <c r="T40">
         <v>0.8752062104873976</v>
       </c>
       <c r="U40">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V40">
         <v>0.206</v>
       </c>
       <c r="W40">
-        <v>0.0539126</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.214345565169464</v>
+        <v>3.560425185562914</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4997,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07242226960887287</v>
+        <v>0.07123047997191122</v>
       </c>
       <c r="C41">
-        <v>2428.081728786606</v>
+        <v>2548.493623245473</v>
       </c>
       <c r="D41">
-        <v>3793.757728786606</v>
+        <v>3914.169623245473</v>
       </c>
       <c r="E41">
         <v>321.376</v>
@@ -4655,37 +5030,37 @@
         <v>362.3</v>
       </c>
       <c r="M41">
-        <v>115.6796004</v>
+        <v>109.2056316</v>
       </c>
       <c r="N41">
-        <v>246.6203996</v>
+        <v>253.0943684</v>
       </c>
       <c r="O41">
-        <v>50.80380231760001</v>
+        <v>52.1374398904</v>
       </c>
       <c r="P41">
-        <v>195.8165972824</v>
+        <v>200.9569285096</v>
       </c>
       <c r="Q41">
-        <v>383.1165972824</v>
+        <v>388.2569285096</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08425632067028339</v>
+        <v>0.08423159667526428</v>
       </c>
       <c r="T41">
         <v>0.8875657430776973</v>
       </c>
       <c r="U41">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.206</v>
       </c>
       <c r="W41">
-        <v>0.0539126</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +5068,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.131926448113837</v>
+        <v>3.317594474679088</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +5079,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07245084987180235</v>
+        <v>0.07122892201707776</v>
       </c>
       <c r="C42">
-        <v>2381.564577319176</v>
+        <v>2504.974154140503</v>
       </c>
       <c r="D42">
-        <v>3790.924577319176</v>
+        <v>3914.334154140503</v>
       </c>
       <c r="E42">
         <v>365.0599999999999</v>
@@ -4737,37 +5112,37 @@
         <v>362.3</v>
       </c>
       <c r="M42">
-        <v>118.645744</v>
+        <v>112.005776</v>
       </c>
       <c r="N42">
-        <v>243.654256</v>
+        <v>250.294224</v>
       </c>
       <c r="O42">
-        <v>50.19277673600001</v>
+        <v>51.56061014400001</v>
       </c>
       <c r="P42">
-        <v>193.461479264</v>
+        <v>198.733613856</v>
       </c>
       <c r="Q42">
-        <v>380.7614792640001</v>
+        <v>386.033613856</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08480968311967058</v>
+        <v>0.08478460336179626</v>
       </c>
       <c r="T42">
         <v>0.9003372600876736</v>
       </c>
       <c r="U42">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.206</v>
       </c>
       <c r="W42">
-        <v>0.0539126</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +5150,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.053628286910992</v>
+        <v>3.234654612812111</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +5161,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07550695213473181</v>
+        <v>0.07122736406224431</v>
       </c>
       <c r="C43">
-        <v>2057.542828157302</v>
+        <v>2461.454698868123</v>
       </c>
       <c r="D43">
-        <v>3510.586828157303</v>
+        <v>3914.498698868123</v>
       </c>
       <c r="E43">
         <v>408.7440000000001</v>
@@ -4819,45 +5194,45 @@
         <v>362.3</v>
       </c>
       <c r="M43">
-        <v>138.2685968</v>
+        <v>114.8059204</v>
       </c>
       <c r="N43">
-        <v>224.0314032</v>
+        <v>247.4940796</v>
       </c>
       <c r="O43">
-        <v>46.15046905920001</v>
+        <v>50.9837803976</v>
       </c>
       <c r="P43">
-        <v>177.8809341408</v>
+        <v>196.5102992024</v>
       </c>
       <c r="Q43">
-        <v>365.1809341408</v>
+        <v>383.8102992024</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08538180361818952</v>
+        <v>0.0853563560377022</v>
       </c>
       <c r="T43">
         <v>0.9135417098776492</v>
       </c>
       <c r="U43">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V43">
         <v>0.206</v>
       </c>
       <c r="W43">
-        <v>0.0612968</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.620262361699183</v>
+        <v>3.155760597865473</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +5243,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.0756093743976613</v>
+        <v>0.07122580610741085</v>
       </c>
       <c r="C44">
-        <v>2005.179869117309</v>
+        <v>2417.935257430078</v>
       </c>
       <c r="D44">
-        <v>3501.907869117309</v>
+        <v>3914.663257430078</v>
       </c>
       <c r="E44">
         <v>452.4279999999999</v>
@@ -4901,45 +5276,45 @@
         <v>362.3</v>
       </c>
       <c r="M44">
-        <v>141.6410016</v>
+        <v>117.6060648</v>
       </c>
       <c r="N44">
-        <v>220.6589984</v>
+        <v>244.6939352</v>
       </c>
       <c r="O44">
-        <v>45.45575367040001</v>
+        <v>50.40695065120001</v>
       </c>
       <c r="P44">
-        <v>175.2032447296</v>
+        <v>194.2869845488</v>
       </c>
       <c r="Q44">
-        <v>362.5032447296001</v>
+        <v>381.5869845488</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08597365240976085</v>
+        <v>0.08594782432312213</v>
       </c>
       <c r="T44">
         <v>0.9272014855224513</v>
       </c>
       <c r="U44">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0.206</v>
       </c>
       <c r="W44">
-        <v>0.0612968</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.557875162611107</v>
+        <v>3.080623440773439</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +5325,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07731647066059077</v>
+        <v>0.07122424815257739</v>
       </c>
       <c r="C45">
-        <v>1822.90967430902</v>
+        <v>2374.415829828115</v>
       </c>
       <c r="D45">
-        <v>3363.32167430902</v>
+        <v>3914.827829828114</v>
       </c>
       <c r="E45">
         <v>496.1119999999999</v>
@@ -4983,45 +5358,45 @@
         <v>362.3</v>
       </c>
       <c r="M45">
-        <v>153.8419428</v>
+        <v>120.4062092</v>
       </c>
       <c r="N45">
-        <v>208.4580572</v>
+        <v>241.8937908</v>
       </c>
       <c r="O45">
-        <v>42.9423597832</v>
+        <v>49.83012090480001</v>
       </c>
       <c r="P45">
-        <v>165.5156974168</v>
+        <v>192.0636698952</v>
       </c>
       <c r="Q45">
-        <v>352.8156974168</v>
+        <v>379.3636698952</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08658626782559783</v>
+        <v>0.0865600458817147</v>
       </c>
       <c r="T45">
         <v>0.9413405515407555</v>
       </c>
       <c r="U45">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.206</v>
       </c>
       <c r="W45">
-        <v>0.06502860000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.355014460984823</v>
+        <v>3.008981035174057</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5407,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07745621092352026</v>
+        <v>0.07394769819774394</v>
       </c>
       <c r="C46">
-        <v>1768.365355381685</v>
+        <v>2062.727458171347</v>
       </c>
       <c r="D46">
-        <v>3352.461355381684</v>
+        <v>3646.823458171347</v>
       </c>
       <c r="E46">
         <v>539.7959999999998</v>
@@ -5065,45 +5440,45 @@
         <v>362.3</v>
       </c>
       <c r="M46">
-        <v>157.4196624</v>
+        <v>138.1987024</v>
       </c>
       <c r="N46">
-        <v>204.8803376</v>
+        <v>224.1012976</v>
       </c>
       <c r="O46">
-        <v>42.20534954560001</v>
+        <v>46.1648673056</v>
       </c>
       <c r="P46">
-        <v>162.6749880544</v>
+        <v>177.9364302944</v>
       </c>
       <c r="Q46">
-        <v>349.9749880544</v>
+        <v>365.2364302944</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08722076236342902</v>
+        <v>0.0871941324959713</v>
       </c>
       <c r="T46">
         <v>0.9559845842025706</v>
       </c>
       <c r="U46">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V46">
         <v>0.206</v>
       </c>
       <c r="W46">
-        <v>0.06502860000000001</v>
+        <v>0.05708860000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.30149140505335</v>
+        <v>2.621587567091368</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5489,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07759595118644973</v>
+        <v>0.07400807224291048</v>
       </c>
       <c r="C47">
-        <v>1713.890947637233</v>
+        <v>2013.517390196039</v>
       </c>
       <c r="D47">
-        <v>3341.670947637233</v>
+        <v>3641.297390196039</v>
       </c>
       <c r="E47">
         <v>583.48</v>
@@ -5147,45 +5522,45 @@
         <v>362.3</v>
       </c>
       <c r="M47">
-        <v>160.997382</v>
+        <v>141.339582</v>
       </c>
       <c r="N47">
-        <v>201.302618</v>
+        <v>220.960418</v>
       </c>
       <c r="O47">
-        <v>41.46833930800001</v>
+        <v>45.51784610800001</v>
       </c>
       <c r="P47">
-        <v>159.834278692</v>
+        <v>175.442571892</v>
       </c>
       <c r="Q47">
-        <v>347.134278692</v>
+        <v>362.742571892</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08787832942990859</v>
+        <v>0.08785127680529176</v>
       </c>
       <c r="T47">
         <v>0.971161127142997</v>
       </c>
       <c r="U47">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.206</v>
       </c>
       <c r="W47">
-        <v>0.06502860000000001</v>
+        <v>0.05708860000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.25034715160772</v>
+        <v>2.563330065600449</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5571,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.0777356914493792</v>
+        <v>0.07406844628807702</v>
       </c>
       <c r="C48">
-        <v>1659.485778182086</v>
+        <v>1964.324044293494</v>
       </c>
       <c r="D48">
-        <v>3330.949778182086</v>
+        <v>3635.788044293494</v>
       </c>
       <c r="E48">
         <v>627.164</v>
@@ -5229,45 +5604,45 @@
         <v>362.3</v>
       </c>
       <c r="M48">
-        <v>164.5751016</v>
+        <v>144.4804616</v>
       </c>
       <c r="N48">
-        <v>197.7248984</v>
+        <v>217.8195384</v>
       </c>
       <c r="O48">
-        <v>40.73132907040001</v>
+        <v>44.8708249104</v>
       </c>
       <c r="P48">
-        <v>156.9935693296</v>
+        <v>172.9487134896</v>
       </c>
       <c r="Q48">
-        <v>344.2935693296</v>
+        <v>360.2487134896</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08856025083218369</v>
+        <v>0.0885327597927352</v>
       </c>
       <c r="T48">
         <v>0.9868997642664021</v>
       </c>
       <c r="U48">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V48">
         <v>0.206</v>
       </c>
       <c r="W48">
-        <v>0.06502860000000001</v>
+        <v>0.05708860000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.201426561355379</v>
+        <v>2.50760549895696</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5653,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07787543171230868</v>
+        <v>0.07558422233324356</v>
       </c>
       <c r="C49">
-        <v>1605.149182730499</v>
+        <v>1787.58371767394</v>
       </c>
       <c r="D49">
-        <v>3320.297182730499</v>
+        <v>3502.73171767394</v>
       </c>
       <c r="E49">
         <v>670.8480000000002</v>
@@ -5311,37 +5686,37 @@
         <v>362.3</v>
       </c>
       <c r="M49">
-        <v>168.1528212</v>
+        <v>155.6286184</v>
       </c>
       <c r="N49">
-        <v>194.1471788</v>
+        <v>206.6713816</v>
       </c>
       <c r="O49">
-        <v>39.9943188328</v>
+        <v>42.5743046096</v>
       </c>
       <c r="P49">
-        <v>154.1528599672</v>
+        <v>164.0970769904</v>
       </c>
       <c r="Q49">
-        <v>341.4528599672</v>
+        <v>351.3970769904</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.08926790511756354</v>
+        <v>0.08923995911932747</v>
       </c>
       <c r="T49">
         <v>1.003232312224653</v>
       </c>
       <c r="U49">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.206</v>
       </c>
       <c r="W49">
-        <v>0.06502860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5724,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.154587698347817</v>
+        <v>2.327978001249158</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5735,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07801517197523815</v>
+        <v>0.07567556237841011</v>
       </c>
       <c r="C50">
-        <v>1550.880505467354</v>
+        <v>1736.192221022758</v>
       </c>
       <c r="D50">
-        <v>3309.712505467354</v>
+        <v>3495.024221022758</v>
       </c>
       <c r="E50">
         <v>714.5319999999999</v>
@@ -5393,37 +5768,37 @@
         <v>362.3</v>
       </c>
       <c r="M50">
-        <v>171.7305408</v>
+        <v>158.9398656</v>
       </c>
       <c r="N50">
-        <v>190.5694592</v>
+        <v>203.3601344</v>
       </c>
       <c r="O50">
-        <v>39.25730859520001</v>
+        <v>41.89218768640001</v>
       </c>
       <c r="P50">
-        <v>151.3121506048</v>
+        <v>161.4679467136</v>
       </c>
       <c r="Q50">
-        <v>338.6121506048</v>
+        <v>348.7679467136001</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09000277687545796</v>
+        <v>0.08997435842001941</v>
       </c>
       <c r="T50">
         <v>1.020193035104375</v>
       </c>
       <c r="U50">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.206</v>
       </c>
       <c r="W50">
-        <v>0.06502860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5806,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.109700454632238</v>
+        <v>2.279478459556468</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5817,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07815491223816763</v>
+        <v>0.07576690242357664</v>
       </c>
       <c r="C51">
-        <v>1496.679098913573</v>
+        <v>1684.834569426854</v>
       </c>
       <c r="D51">
-        <v>3299.195098913573</v>
+        <v>3487.350569426853</v>
       </c>
       <c r="E51">
         <v>758.2159999999997</v>
@@ -5475,37 +5850,37 @@
         <v>362.3</v>
       </c>
       <c r="M51">
-        <v>175.3082604</v>
+        <v>162.2511128</v>
       </c>
       <c r="N51">
-        <v>186.9917396</v>
+        <v>200.0488872</v>
       </c>
       <c r="O51">
-        <v>38.52029835760001</v>
+        <v>41.21007076320001</v>
       </c>
       <c r="P51">
-        <v>148.4714412424</v>
+        <v>158.8388164368</v>
       </c>
       <c r="Q51">
-        <v>335.7714412424</v>
+        <v>346.1388164368</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09076646713366202</v>
+        <v>0.09073755769328753</v>
       </c>
       <c r="T51">
         <v>1.037818884371537</v>
       </c>
       <c r="U51">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V51">
         <v>0.206</v>
       </c>
       <c r="W51">
-        <v>0.06502860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5888,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.066645343313213</v>
+        <v>2.232958490994091</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5899,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.0782946525010971</v>
+        <v>0.07585824246874319</v>
       </c>
       <c r="C52">
-        <v>1442.54432379409</v>
+        <v>1633.510540444691</v>
       </c>
       <c r="D52">
-        <v>3288.74432379409</v>
+        <v>3479.710540444691</v>
       </c>
       <c r="E52">
         <v>801.8999999999999</v>
@@ -5557,37 +5932,37 @@
         <v>362.3</v>
       </c>
       <c r="M52">
-        <v>178.88598</v>
+        <v>165.56236</v>
       </c>
       <c r="N52">
-        <v>183.41402</v>
+        <v>196.73764</v>
       </c>
       <c r="O52">
-        <v>37.78328812000001</v>
+        <v>40.52795384</v>
       </c>
       <c r="P52">
-        <v>145.63073188</v>
+        <v>156.20968616</v>
       </c>
       <c r="Q52">
-        <v>332.9307318800001</v>
+        <v>343.50968616</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09156070500219421</v>
+        <v>0.09153128493748637</v>
       </c>
       <c r="T52">
         <v>1.056149767609385</v>
       </c>
       <c r="U52">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V52">
         <v>0.206</v>
       </c>
       <c r="W52">
-        <v>0.06502860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5970,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.025312436446948</v>
+        <v>2.188299321174209</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5981,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08503491476402658</v>
+        <v>0.07594958251390974</v>
       </c>
       <c r="C53">
-        <v>962.971687801416</v>
+        <v>1582.219913579762</v>
       </c>
       <c r="D53">
-        <v>2852.855687801416</v>
+        <v>3472.103913579762</v>
       </c>
       <c r="E53">
         <v>845.5840000000001</v>
@@ -5639,45 +6014,45 @@
         <v>362.3</v>
       </c>
       <c r="M53">
-        <v>218.7782088</v>
+        <v>168.8736072</v>
       </c>
       <c r="N53">
-        <v>143.5217912</v>
+        <v>193.4263928</v>
       </c>
       <c r="O53">
-        <v>29.5654889872</v>
+        <v>39.8458369168</v>
       </c>
       <c r="P53">
-        <v>113.9563022128</v>
+        <v>153.5805558832</v>
       </c>
       <c r="Q53">
-        <v>301.2563022128</v>
+        <v>340.8805558832</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09238736074291139</v>
+        <v>0.09235740921206068</v>
       </c>
       <c r="T53">
         <v>1.075228850163064</v>
       </c>
       <c r="U53">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.206</v>
       </c>
       <c r="W53">
-        <v>0.07797080000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.656015020815912</v>
+        <v>2.145391491347263</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +6063,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08530407702695605</v>
+        <v>0.07604092255907627</v>
       </c>
       <c r="C54">
-        <v>904.2676835297048</v>
+        <v>1530.962470259368</v>
       </c>
       <c r="D54">
-        <v>2837.835683529705</v>
+        <v>3464.530470259368</v>
       </c>
       <c r="E54">
         <v>889.2679999999998</v>
@@ -5721,45 +6096,45 @@
         <v>362.3</v>
       </c>
       <c r="M54">
-        <v>223.0679776</v>
+        <v>172.1848544</v>
       </c>
       <c r="N54">
-        <v>139.2320224</v>
+        <v>190.1151456</v>
       </c>
       <c r="O54">
-        <v>28.6817966144</v>
+        <v>39.1637199936</v>
       </c>
       <c r="P54">
-        <v>110.5502257856</v>
+        <v>150.9514256064</v>
       </c>
       <c r="Q54">
-        <v>297.8502257856</v>
+        <v>338.2514256064</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09324846047282512</v>
+        <v>0.09321795533140889</v>
       </c>
       <c r="T54">
         <v>1.095102894489813</v>
       </c>
       <c r="U54">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.206</v>
       </c>
       <c r="W54">
-        <v>0.07797080000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.624168578107914</v>
+        <v>2.104133962667508</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +6145,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08557323928988553</v>
+        <v>0.07613226260424283</v>
       </c>
       <c r="C55">
-        <v>845.7210086212881</v>
+        <v>1479.737993813681</v>
       </c>
       <c r="D55">
-        <v>2822.973008621288</v>
+        <v>3456.989993813681</v>
       </c>
       <c r="E55">
         <v>932.952</v>
@@ -5803,45 +6178,45 @@
         <v>362.3</v>
       </c>
       <c r="M55">
-        <v>227.3577464</v>
+        <v>175.4961016</v>
       </c>
       <c r="N55">
-        <v>134.9422536</v>
+        <v>186.8038984</v>
       </c>
       <c r="O55">
-        <v>27.7981042416</v>
+        <v>38.48160307040001</v>
       </c>
       <c r="P55">
-        <v>107.1441493584</v>
+        <v>148.3222953296</v>
       </c>
       <c r="Q55">
-        <v>294.4441493584</v>
+        <v>335.6222953296</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.0941462027444373</v>
+        <v>0.09411512043455919</v>
       </c>
       <c r="T55">
         <v>1.115822642830466</v>
       </c>
       <c r="U55">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.206</v>
       </c>
       <c r="W55">
-        <v>0.07797080000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.593523887954934</v>
+        <v>2.064433321862461</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +6227,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.085842401552815</v>
+        <v>0.07622360264940936</v>
       </c>
       <c r="C56">
-        <v>787.3292039989497</v>
+        <v>1428.546269455094</v>
       </c>
       <c r="D56">
-        <v>2808.26520399895</v>
+        <v>3449.482269455094</v>
       </c>
       <c r="E56">
         <v>976.6360000000002</v>
@@ -5885,45 +6260,45 @@
         <v>362.3</v>
       </c>
       <c r="M56">
-        <v>231.6475152</v>
+        <v>178.8073488</v>
       </c>
       <c r="N56">
-        <v>130.6524848</v>
+        <v>183.4926512</v>
       </c>
       <c r="O56">
-        <v>26.91441186879999</v>
+        <v>37.7994861472</v>
       </c>
       <c r="P56">
-        <v>103.7380729312</v>
+        <v>145.6931650528</v>
       </c>
       <c r="Q56">
-        <v>291.0380729312</v>
+        <v>332.9931650528</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09508297728872828</v>
+        <v>0.09505129271610729</v>
       </c>
       <c r="T56">
         <v>1.137443249794626</v>
       </c>
       <c r="U56">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V56">
         <v>0.206</v>
       </c>
       <c r="W56">
-        <v>0.07797080000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.564014186326139</v>
+        <v>2.026203075161304</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +6309,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.0861115638157445</v>
+        <v>0.08251608269457589</v>
       </c>
       <c r="C57">
-        <v>729.0898615674246</v>
+        <v>935.9382128713396</v>
       </c>
       <c r="D57">
-        <v>2793.709861567424</v>
+        <v>3000.558212871339</v>
       </c>
       <c r="E57">
         <v>1020.32</v>
@@ -5967,37 +6342,37 @@
         <v>362.3</v>
       </c>
       <c r="M57">
-        <v>235.937284</v>
+        <v>216.2358</v>
       </c>
       <c r="N57">
-        <v>126.362716</v>
+        <v>146.0642</v>
       </c>
       <c r="O57">
-        <v>26.030719496</v>
+        <v>30.08922520000001</v>
       </c>
       <c r="P57">
-        <v>100.331996504</v>
+        <v>115.9749748</v>
       </c>
       <c r="Q57">
-        <v>287.631996504</v>
+        <v>303.2749748</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09606138625720997</v>
+        <v>0.09602907265461311</v>
       </c>
       <c r="T57">
         <v>1.16002477262386</v>
       </c>
       <c r="U57">
-        <v>0.09820000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V57">
         <v>0.206</v>
       </c>
       <c r="W57">
-        <v>0.07797080000000001</v>
+        <v>0.07146</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6380,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.535577564756573</v>
+        <v>1.675485742878839</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6391,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08638072607867396</v>
+        <v>0.08272017073974244</v>
       </c>
       <c r="C58">
-        <v>671.0006228990087</v>
+        <v>879.64211183715</v>
       </c>
       <c r="D58">
-        <v>2779.304622899009</v>
+        <v>2987.94611183715</v>
       </c>
       <c r="E58">
         <v>1064.004</v>
@@ -6049,37 +6424,37 @@
         <v>362.3</v>
       </c>
       <c r="M58">
-        <v>240.2270528</v>
+        <v>220.16736</v>
       </c>
       <c r="N58">
-        <v>122.0729472</v>
+        <v>142.13264</v>
       </c>
       <c r="O58">
-        <v>25.1470271232</v>
+        <v>29.27932384</v>
       </c>
       <c r="P58">
-        <v>96.92592007679998</v>
+        <v>112.85331616</v>
       </c>
       <c r="Q58">
-        <v>284.2259200768</v>
+        <v>300.15331616</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09708426836062264</v>
+        <v>0.09705129713577829</v>
       </c>
       <c r="T58">
         <v>1.183632728308968</v>
       </c>
       <c r="U58">
-        <v>0.09820000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V58">
         <v>0.206</v>
       </c>
       <c r="W58">
-        <v>0.07797080000000001</v>
+        <v>0.07146</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6462,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.508156536814492</v>
+        <v>1.645566354613145</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6473,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1187049203733137</v>
+        <v>0.08292425878490899</v>
       </c>
       <c r="C59">
-        <v>-435.5530932604524</v>
+        <v>823.451590691202</v>
       </c>
       <c r="D59">
-        <v>1716.434906739548</v>
+        <v>2975.439590691202</v>
       </c>
       <c r="E59">
         <v>1107.688</v>
@@ -6131,45 +6506,45 @@
         <v>362.3</v>
       </c>
       <c r="M59">
-        <v>407.3620368000001</v>
+        <v>224.09892</v>
       </c>
       <c r="N59">
-        <v>-45.06203680000004</v>
+        <v>138.20108</v>
       </c>
       <c r="O59">
-        <v>-9.28277958080001</v>
+        <v>28.46942248</v>
       </c>
       <c r="P59">
-        <v>-35.77925721920003</v>
+        <v>109.73165752</v>
       </c>
       <c r="Q59">
-        <v>151.5207427808</v>
+        <v>297.03165752</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09892522905453309</v>
+        <v>0.09812106694164881</v>
       </c>
       <c r="T59">
-        <v>1.226121807289685</v>
+        <v>1.208338728444545</v>
       </c>
       <c r="U59">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V59">
-        <v>0.183212457857585</v>
+        <v>0.206</v>
       </c>
       <c r="W59">
-        <v>0.1336264418944991</v>
+        <v>0.07146</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.8893808633863349</v>
+        <v>1.616696769444494</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6555,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1198829203733137</v>
+        <v>0.08312834683007553</v>
       </c>
       <c r="C60">
-        <v>-502.8298092458783</v>
+        <v>767.3653291955852</v>
       </c>
       <c r="D60">
-        <v>1692.842190754121</v>
+        <v>2963.037329195585</v>
       </c>
       <c r="E60">
         <v>1151.372</v>
@@ -6213,45 +6588,45 @@
         <v>362.3</v>
       </c>
       <c r="M60">
-        <v>414.5087391999999</v>
+        <v>228.03048</v>
       </c>
       <c r="N60">
-        <v>-52.20873919999991</v>
+        <v>134.2695200000001</v>
       </c>
       <c r="O60">
-        <v>-10.75500027519998</v>
+        <v>27.65952112000002</v>
       </c>
       <c r="P60">
-        <v>-41.45373892479993</v>
+        <v>106.60999888</v>
       </c>
       <c r="Q60">
-        <v>145.8462610752001</v>
+        <v>293.90999888</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1001901154605934</v>
+        <v>0.0992417781668465</v>
       </c>
       <c r="T60">
-        <v>1.255315183653724</v>
+        <v>1.234221204777056</v>
       </c>
       <c r="U60">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V60">
-        <v>0.1800536223772819</v>
+        <v>0.206</v>
       </c>
       <c r="W60">
-        <v>0.1341432273790767</v>
+        <v>0.07146</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.8740467105693295</v>
+        <v>1.588822687212692</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6637,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1210609203733137</v>
+        <v>0.08333243487524207</v>
       </c>
       <c r="C61">
-        <v>-569.4667465975651</v>
+        <v>711.3820290331405</v>
       </c>
       <c r="D61">
-        <v>1669.889253402435</v>
+        <v>2950.73802903314</v>
       </c>
       <c r="E61">
         <v>1195.056</v>
@@ -6295,45 +6670,45 @@
         <v>362.3</v>
       </c>
       <c r="M61">
-        <v>421.6554416</v>
+        <v>231.96204</v>
       </c>
       <c r="N61">
-        <v>-59.35544159999995</v>
+        <v>130.33796</v>
       </c>
       <c r="O61">
-        <v>-12.22722096959999</v>
+        <v>26.84961976000001</v>
       </c>
       <c r="P61">
-        <v>-47.12822063039996</v>
+        <v>103.48834024</v>
       </c>
       <c r="Q61">
-        <v>140.1717793696</v>
+        <v>290.78834024</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1015167036425591</v>
+        <v>0.1004171582322977</v>
       </c>
       <c r="T61">
-        <v>1.285932627157474</v>
+        <v>1.261366240930664</v>
       </c>
       <c r="U61">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V61">
-        <v>0.1770018660658025</v>
+        <v>0.206</v>
       </c>
       <c r="W61">
-        <v>0.1346424947116347</v>
+        <v>0.07146</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8592323595427306</v>
+        <v>1.561893489124341</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6719,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1222389203733137</v>
+        <v>0.08353652292040861</v>
       </c>
       <c r="C62">
-        <v>-635.4895811062718</v>
+        <v>655.5004133543903</v>
       </c>
       <c r="D62">
-        <v>1647.550418893728</v>
+        <v>2938.54041335439</v>
       </c>
       <c r="E62">
         <v>1238.74</v>
@@ -6377,45 +6752,45 @@
         <v>362.3</v>
       </c>
       <c r="M62">
-        <v>428.8021439999999</v>
+        <v>235.8935999999999</v>
       </c>
       <c r="N62">
-        <v>-66.50214399999987</v>
+        <v>126.4064000000001</v>
       </c>
       <c r="O62">
-        <v>-13.69944166399998</v>
+        <v>26.03971840000002</v>
       </c>
       <c r="P62">
-        <v>-52.8027023359999</v>
+        <v>100.3666816</v>
       </c>
       <c r="Q62">
-        <v>134.4972976640001</v>
+        <v>287.6666816000001</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.102909621233623</v>
+        <v>0.1016513073010215</v>
       </c>
       <c r="T62">
-        <v>1.318080942836411</v>
+        <v>1.289868528891952</v>
       </c>
       <c r="U62">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V62">
-        <v>0.1740518349647059</v>
+        <v>0.206</v>
       </c>
       <c r="W62">
-        <v>0.1351251197997741</v>
+        <v>0.07146</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.8449118202170186</v>
+        <v>1.535861930972269</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6801,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1234169203733137</v>
+        <v>0.08374061096557515</v>
       </c>
       <c r="C63">
-        <v>-700.9226327945985</v>
+        <v>599.7192263356487</v>
       </c>
       <c r="D63">
-        <v>1625.801367205401</v>
+        <v>2926.443226335648</v>
       </c>
       <c r="E63">
         <v>1282.424</v>
@@ -6459,45 +6834,45 @@
         <v>362.3</v>
       </c>
       <c r="M63">
-        <v>435.9488463999999</v>
+        <v>239.82516</v>
       </c>
       <c r="N63">
-        <v>-73.64884639999991</v>
+        <v>122.4748400000001</v>
       </c>
       <c r="O63">
-        <v>-15.17166235839998</v>
+        <v>25.22981704000001</v>
       </c>
       <c r="P63">
-        <v>-58.47718404159993</v>
+        <v>97.24502296000004</v>
       </c>
       <c r="Q63">
-        <v>128.8228159584001</v>
+        <v>284.54502296</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1043739704960236</v>
+        <v>0.1029487460655773</v>
       </c>
       <c r="T63">
-        <v>1.351877890088627</v>
+        <v>1.319832472646128</v>
       </c>
       <c r="U63">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V63">
-        <v>0.1711985261947926</v>
+        <v>0.206</v>
       </c>
       <c r="W63">
-        <v>0.1355919211145319</v>
+        <v>0.07146</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.8310608067708378</v>
+        <v>1.510683866530101</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6883,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1245949203733137</v>
+        <v>0.1138595817994899</v>
       </c>
       <c r="C64">
-        <v>-765.788954237481</v>
+        <v>-549.9604982932146</v>
       </c>
       <c r="D64">
-        <v>1604.619045762519</v>
+        <v>1820.447501706785</v>
       </c>
       <c r="E64">
         <v>1326.108</v>
@@ -6541,37 +6916,37 @@
         <v>362.3</v>
       </c>
       <c r="M64">
-        <v>443.0955488</v>
+        <v>397.5942944</v>
       </c>
       <c r="N64">
-        <v>-80.79554879999995</v>
+        <v>-35.29429440000001</v>
       </c>
       <c r="O64">
-        <v>-16.64388305279999</v>
+        <v>-7.270624646400003</v>
       </c>
       <c r="P64">
-        <v>-64.15166574719996</v>
+        <v>-28.02366975360001</v>
       </c>
       <c r="Q64">
-        <v>123.1483342528001</v>
+        <v>159.2763302464</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1059153907722348</v>
+        <v>0.1050750261042774</v>
       </c>
       <c r="T64">
-        <v>1.387453624038327</v>
+        <v>1.368938247211948</v>
       </c>
       <c r="U64">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1684372596432637</v>
+        <v>0.1877134582945363</v>
       </c>
       <c r="W64">
-        <v>0.1360436643223621</v>
+        <v>0.1192436643223621</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6954,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8176566002100178</v>
+        <v>0.9112303800705647</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6965,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1257729203733137</v>
+        <v>0.1148695817994899</v>
       </c>
       <c r="C65">
-        <v>-830.1104120671989</v>
+        <v>-616.4271006168256</v>
       </c>
       <c r="D65">
-        <v>1583.981587932801</v>
+        <v>1797.664899383174</v>
       </c>
       <c r="E65">
         <v>1369.792</v>
@@ -6623,37 +6998,37 @@
         <v>362.3</v>
       </c>
       <c r="M65">
-        <v>450.2422511999999</v>
+        <v>404.0071056</v>
       </c>
       <c r="N65">
-        <v>-87.94225119999993</v>
+        <v>-41.70710559999998</v>
       </c>
       <c r="O65">
-        <v>-18.11610374719999</v>
+        <v>-8.591663753599995</v>
       </c>
       <c r="P65">
-        <v>-69.82614745279994</v>
+        <v>-33.11544184639998</v>
       </c>
       <c r="Q65">
-        <v>117.4738525472001</v>
+        <v>154.1845581536</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1075401310633763</v>
+        <v>0.1066770538368254</v>
       </c>
       <c r="T65">
-        <v>1.424952370633958</v>
+        <v>1.405936578217676</v>
       </c>
       <c r="U65">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1657636523473389</v>
+        <v>0.1847338795914485</v>
       </c>
       <c r="W65">
-        <v>0.1364810664759754</v>
+        <v>0.1196810664759754</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +7036,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8046779240162081</v>
+        <v>0.8967664057837303</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +7047,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1610032664481668</v>
+        <v>0.1158795817994899</v>
       </c>
       <c r="C66">
-        <v>-1313.810680477877</v>
+        <v>-682.330510132876</v>
       </c>
       <c r="D66">
-        <v>1143.965319522123</v>
+        <v>1775.445489867124</v>
       </c>
       <c r="E66">
         <v>1413.476</v>
@@ -6705,45 +7080,45 @@
         <v>362.3</v>
       </c>
       <c r="M66">
-        <v>603.3284608</v>
+        <v>410.4199168</v>
       </c>
       <c r="N66">
-        <v>-241.0284608</v>
+        <v>-48.1199168</v>
       </c>
       <c r="O66">
-        <v>-49.65186292480001</v>
+        <v>-9.9127028608</v>
       </c>
       <c r="P66">
-        <v>-191.3765978752</v>
+        <v>-38.2072139392</v>
       </c>
       <c r="Q66">
-        <v>-4.07659787519998</v>
+        <v>149.0927860608</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1110449849119507</v>
+        <v>0.1083680831100705</v>
       </c>
       <c r="T66">
-        <v>1.505843838051238</v>
+        <v>1.444990372057056</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1237034299708608</v>
+        <v>0.1818474127228321</v>
       </c>
       <c r="W66">
-        <v>0.1891047998122883</v>
+        <v>0.1201047998122883</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.600502087237188</v>
+        <v>0.8827544306933596</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +7129,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1627032664481668</v>
+        <v>0.1168895817994899</v>
       </c>
       <c r="C67">
-        <v>-1372.626133949478</v>
+        <v>-747.6913553146687</v>
       </c>
       <c r="D67">
-        <v>1128.833866050522</v>
+        <v>1753.768644685332</v>
       </c>
       <c r="E67">
         <v>1457.16</v>
@@ -6787,45 +7162,45 @@
         <v>362.3</v>
       </c>
       <c r="M67">
-        <v>612.7554680000001</v>
+        <v>416.832728</v>
       </c>
       <c r="N67">
-        <v>-250.4554680000001</v>
+        <v>-54.53272800000002</v>
       </c>
       <c r="O67">
-        <v>-51.59382640800001</v>
+        <v>-11.23374196800001</v>
       </c>
       <c r="P67">
-        <v>-198.861641592</v>
+        <v>-43.29898603200002</v>
       </c>
       <c r="Q67">
-        <v>-11.56164159200003</v>
+        <v>144.001013968</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1129091273380065</v>
+        <v>0.1101557426275011</v>
       </c>
       <c r="T67">
-        <v>1.548867947709845</v>
+        <v>1.486275811258687</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1218003002790014</v>
+        <v>0.1790497602194039</v>
       </c>
       <c r="W67">
-        <v>0.1895154951997915</v>
+        <v>0.1205154951997915</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5912635935873851</v>
+        <v>0.8691735932980771</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +7211,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1644032664481667</v>
+        <v>0.1178995817994899</v>
       </c>
       <c r="C68">
-        <v>-1431.046519658838</v>
+        <v>-812.5292693549659</v>
       </c>
       <c r="D68">
-        <v>1114.097480341162</v>
+        <v>1732.614730645034</v>
       </c>
       <c r="E68">
         <v>1500.844</v>
@@ -6869,45 +7244,45 @@
         <v>362.3</v>
       </c>
       <c r="M68">
-        <v>622.1824752</v>
+        <v>423.2455392</v>
       </c>
       <c r="N68">
-        <v>-259.8824752</v>
+        <v>-60.94553919999998</v>
       </c>
       <c r="O68">
-        <v>-53.5357898912</v>
+        <v>-12.5547810752</v>
       </c>
       <c r="P68">
-        <v>-206.3466853088</v>
+        <v>-48.39075812479999</v>
       </c>
       <c r="Q68">
-        <v>-19.04668530879997</v>
+        <v>138.9092418752</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.114882925200889</v>
+        <v>0.1120485585871335</v>
       </c>
       <c r="T68">
-        <v>1.59442288734837</v>
+        <v>1.529989805707472</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.119954841183865</v>
+        <v>0.1763368850645645</v>
       </c>
       <c r="W68">
-        <v>0.1899137452725219</v>
+        <v>0.120913745272522</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.5823050542906066</v>
+        <v>0.8560042964299245</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +7293,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1661032664481668</v>
+        <v>0.1189095817994899</v>
       </c>
       <c r="C69">
-        <v>-1489.087110487314</v>
+        <v>-876.8629494758475</v>
       </c>
       <c r="D69">
-        <v>1099.740889512686</v>
+        <v>1711.965050524153</v>
       </c>
       <c r="E69">
         <v>1544.528</v>
@@ -6951,45 +7326,45 @@
         <v>362.3</v>
       </c>
       <c r="M69">
-        <v>631.6094824</v>
+        <v>429.6583504</v>
       </c>
       <c r="N69">
-        <v>-269.3094824</v>
+        <v>-67.35835040000001</v>
       </c>
       <c r="O69">
-        <v>-55.47775337440001</v>
+        <v>-13.8758201824</v>
       </c>
       <c r="P69">
-        <v>-213.8317290256</v>
+        <v>-53.4825302176</v>
       </c>
       <c r="Q69">
-        <v>-26.53172902560001</v>
+        <v>133.8174697824</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1169763471766735</v>
+        <v>0.1140560906655315</v>
       </c>
       <c r="T69">
-        <v>1.642738732419533</v>
+        <v>1.576353133153153</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1181644704199267</v>
+        <v>0.1737049912576306</v>
       </c>
       <c r="W69">
-        <v>0.1903001072833798</v>
+        <v>0.1213001072833798</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5736139340773139</v>
+        <v>0.8432281129011195</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7375,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1678032664481668</v>
+        <v>0.1199195817994899</v>
       </c>
       <c r="C70">
-        <v>-1546.762402088321</v>
+        <v>-940.7102120472982</v>
       </c>
       <c r="D70">
-        <v>1085.749597911679</v>
+        <v>1691.801787952702</v>
       </c>
       <c r="E70">
         <v>1588.212</v>
@@ -7033,45 +7408,45 @@
         <v>362.3</v>
       </c>
       <c r="M70">
-        <v>641.0364896000001</v>
+        <v>436.0711616</v>
       </c>
       <c r="N70">
-        <v>-278.7364896000001</v>
+        <v>-73.77116160000003</v>
       </c>
       <c r="O70">
-        <v>-57.41971685760002</v>
+        <v>-15.19685928960001</v>
       </c>
       <c r="P70">
-        <v>-221.3167727424001</v>
+        <v>-58.57430231040002</v>
       </c>
       <c r="Q70">
-        <v>-34.01677274240006</v>
+        <v>128.7256976896</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1192006080259446</v>
+        <v>0.1161890934988294</v>
       </c>
       <c r="T70">
-        <v>1.694074317807643</v>
+        <v>1.625614168564189</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1164267576196336</v>
+        <v>0.1711505060920772</v>
       </c>
       <c r="W70">
-        <v>0.1906751057056831</v>
+        <v>0.1216751057056831</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.5651784350467652</v>
+        <v>0.830827699476103</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7457,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1695032664481668</v>
+        <v>0.1209295817994899</v>
       </c>
       <c r="C71">
-        <v>-1604.086161707072</v>
+        <v>-1004.088043856083</v>
       </c>
       <c r="D71">
-        <v>1072.109838292928</v>
+        <v>1672.107956143917</v>
       </c>
       <c r="E71">
         <v>1631.896</v>
@@ -7115,45 +7490,45 @@
         <v>362.3</v>
       </c>
       <c r="M71">
-        <v>650.4634968</v>
+        <v>442.4839728</v>
       </c>
       <c r="N71">
-        <v>-288.1634968</v>
+        <v>-80.18397279999999</v>
       </c>
       <c r="O71">
-        <v>-59.36168034080001</v>
+        <v>-16.5178983968</v>
       </c>
       <c r="P71">
-        <v>-228.8018164592</v>
+        <v>-63.66607440319999</v>
       </c>
       <c r="Q71">
-        <v>-41.5018164592</v>
+        <v>123.6339255968</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1215683695751686</v>
+        <v>0.1184597094181464</v>
       </c>
       <c r="T71">
-        <v>1.7487218764466</v>
+        <v>1.678053335292066</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1147394133063056</v>
+        <v>0.1686700639748008</v>
       </c>
       <c r="W71">
-        <v>0.1910392346084993</v>
+        <v>0.1220392346084993</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.5569874432344932</v>
+        <v>0.8187867183242755</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7539,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1712032664481667</v>
+        <v>0.1219395817994899</v>
       </c>
       <c r="C72">
-        <v>-1661.071473366176</v>
+        <v>-1067.012649834974</v>
       </c>
       <c r="D72">
-        <v>1058.808526633824</v>
+        <v>1652.867350165026</v>
       </c>
       <c r="E72">
         <v>1675.58</v>
@@ -7197,45 +7572,45 @@
         <v>362.3</v>
       </c>
       <c r="M72">
-        <v>659.8905040000001</v>
+        <v>448.8967840000001</v>
       </c>
       <c r="N72">
-        <v>-297.5905040000001</v>
+        <v>-86.59678400000007</v>
       </c>
       <c r="O72">
-        <v>-61.30364382400002</v>
+        <v>-17.83893750400001</v>
       </c>
       <c r="P72">
-        <v>-236.2868601760001</v>
+        <v>-68.75784649600006</v>
       </c>
       <c r="Q72">
-        <v>-48.98686017600005</v>
+        <v>118.542153504</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1240939818943409</v>
+        <v>0.1208816997320847</v>
       </c>
       <c r="T72">
-        <v>1.807012605661486</v>
+        <v>1.733988446468468</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1131002788305012</v>
+        <v>0.1662604916323036</v>
       </c>
       <c r="W72">
-        <v>0.1913929598283778</v>
+        <v>0.1223929598283778</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.5490304797597148</v>
+        <v>0.8070897652053572</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7621,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1729032664481668</v>
+        <v>0.1620874076745033</v>
       </c>
       <c r="C73">
-        <v>-1717.730779728833</v>
+        <v>-1629.442531849422</v>
       </c>
       <c r="D73">
-        <v>1045.833220271166</v>
+        <v>1134.121468150577</v>
       </c>
       <c r="E73">
         <v>1719.263999999999</v>
@@ -7279,37 +7654,37 @@
         <v>362.3</v>
       </c>
       <c r="M73">
-        <v>669.3175111999999</v>
+        <v>622.7940511999999</v>
       </c>
       <c r="N73">
-        <v>-307.0175111999999</v>
+        <v>-260.4940511999999</v>
       </c>
       <c r="O73">
-        <v>-63.24560730719998</v>
+        <v>-53.66177454719998</v>
       </c>
       <c r="P73">
-        <v>-243.7719038927999</v>
+        <v>-206.8322766527999</v>
       </c>
       <c r="Q73">
-        <v>-56.4719038927999</v>
+        <v>-19.53227665279991</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1267937743734561</v>
+        <v>0.12622184756772</v>
       </c>
       <c r="T73">
-        <v>1.869323385167054</v>
+        <v>1.857317495790302</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1115073171568322</v>
+        <v>0.1198370470241255</v>
       </c>
       <c r="W73">
-        <v>0.1917367209575556</v>
+        <v>0.1767367209575556</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7692,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5412976561011273</v>
+        <v>0.5817332379811917</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7703,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1746032664481668</v>
+        <v>0.1636374076745033</v>
       </c>
       <c r="C74">
-        <v>-1774.075920921199</v>
+        <v>-1686.703890321481</v>
       </c>
       <c r="D74">
-        <v>1033.1720790788</v>
+        <v>1120.544109678519</v>
       </c>
       <c r="E74">
         <v>1762.948</v>
@@ -7361,37 +7736,37 @@
         <v>362.3</v>
       </c>
       <c r="M74">
-        <v>678.7445183999999</v>
+        <v>631.5657983999999</v>
       </c>
       <c r="N74">
-        <v>-316.4445183999999</v>
+        <v>-269.2657983999999</v>
       </c>
       <c r="O74">
-        <v>-65.18757079039999</v>
+        <v>-55.46875447039999</v>
       </c>
       <c r="P74">
-        <v>-251.2569476095999</v>
+        <v>-213.7970439295999</v>
       </c>
       <c r="Q74">
-        <v>-63.95694760959992</v>
+        <v>-26.49704392959993</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1296864091725081</v>
+        <v>0.1290940564094243</v>
       </c>
       <c r="T74">
-        <v>1.936084934637306</v>
+        <v>1.923650263497098</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1099586044185429</v>
+        <v>0.1181726435932349</v>
       </c>
       <c r="W74">
-        <v>0.1920709331664785</v>
+        <v>0.1770709331664785</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7774,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5337796330997228</v>
+        <v>0.5736536096758973</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7785,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1763032664481668</v>
+        <v>0.1651874076745033</v>
       </c>
       <c r="C75">
-        <v>-1830.118170568501</v>
+        <v>-1743.644006567264</v>
       </c>
       <c r="D75">
-        <v>1020.813829431499</v>
+        <v>1107.287993432736</v>
       </c>
       <c r="E75">
         <v>1806.632</v>
@@ -7443,37 +7818,37 @@
         <v>362.3</v>
       </c>
       <c r="M75">
-        <v>688.1715256</v>
+        <v>640.3375456</v>
       </c>
       <c r="N75">
-        <v>-325.8715256</v>
+        <v>-278.0375456</v>
       </c>
       <c r="O75">
-        <v>-67.1295342736</v>
+        <v>-57.2757343936</v>
       </c>
       <c r="P75">
-        <v>-258.7419913264</v>
+        <v>-220.7618112064</v>
       </c>
       <c r="Q75">
-        <v>-71.4419913264</v>
+        <v>-33.46181120639997</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1327933132159343</v>
+        <v>0.1321790214616252</v>
       </c>
       <c r="T75">
-        <v>2.007791784068317</v>
+        <v>1.994896569552546</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1084523221662341</v>
+        <v>0.1165538402563412</v>
       </c>
       <c r="W75">
-        <v>0.1923959888765267</v>
+        <v>0.1773959888765267</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7856,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5264675833312333</v>
+        <v>0.5657953410502</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7867,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1780032664481667</v>
+        <v>0.1667374076745033</v>
       </c>
       <c r="C76">
-        <v>-1885.868269275463</v>
+        <v>-1800.274148244504</v>
       </c>
       <c r="D76">
-        <v>1008.747730724536</v>
+        <v>1094.341851755495</v>
       </c>
       <c r="E76">
         <v>1850.316</v>
@@ -7525,37 +7900,37 @@
         <v>362.3</v>
       </c>
       <c r="M76">
-        <v>697.5985327999999</v>
+        <v>649.1092927999999</v>
       </c>
       <c r="N76">
-        <v>-335.2985327999999</v>
+        <v>-286.8092927999999</v>
       </c>
       <c r="O76">
-        <v>-69.07149775679999</v>
+        <v>-59.08271431679999</v>
       </c>
       <c r="P76">
-        <v>-266.2270350431999</v>
+        <v>-227.7265784831999</v>
       </c>
       <c r="Q76">
-        <v>-78.92703504319991</v>
+        <v>-40.42657848319993</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1361392098780856</v>
+        <v>0.1355012915178416</v>
       </c>
       <c r="T76">
-        <v>2.085014544994022</v>
+        <v>2.071623360689182</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1069867502450688</v>
+        <v>0.1149787883609853</v>
       </c>
       <c r="W76">
-        <v>0.1927122592971142</v>
+        <v>0.1777122592971142</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7938,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.51935315652946</v>
+        <v>0.5581494580630353</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7949,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1797032664481668</v>
+        <v>0.1682874076745033</v>
       </c>
       <c r="C77">
-        <v>-1941.336455760027</v>
+        <v>-1856.605062145919</v>
       </c>
       <c r="D77">
-        <v>996.9635442399726</v>
+        <v>1081.694937854081</v>
       </c>
       <c r="E77">
         <v>1894</v>
@@ -7607,37 +7982,37 @@
         <v>362.3</v>
       </c>
       <c r="M77">
-        <v>707.02554</v>
+        <v>657.88104</v>
       </c>
       <c r="N77">
-        <v>-344.72554</v>
+        <v>-295.58104</v>
       </c>
       <c r="O77">
-        <v>-71.01346124</v>
+        <v>-60.88969424</v>
       </c>
       <c r="P77">
-        <v>-273.7120787599999</v>
+        <v>-234.69134576</v>
       </c>
       <c r="Q77">
-        <v>-86.41207875999993</v>
+        <v>-47.39134575999998</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1397527782732091</v>
+        <v>0.1390893431785553</v>
       </c>
       <c r="T77">
-        <v>2.168415126793783</v>
+        <v>2.15448829511675</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1055602602418012</v>
+        <v>0.1134457378495055</v>
       </c>
       <c r="W77">
-        <v>0.1930200958398193</v>
+        <v>0.1780200958398193</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +8020,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5124284477757339</v>
+        <v>0.5507074652888614</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +8031,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1814032664481668</v>
+        <v>0.1698374076745033</v>
       </c>
       <c r="C78">
-        <v>-1996.532495830038</v>
+        <v>-1912.647003952599</v>
       </c>
       <c r="D78">
-        <v>985.4515041699623</v>
+        <v>1069.336996047401</v>
       </c>
       <c r="E78">
         <v>1937.684</v>
@@ -7689,37 +8064,37 @@
         <v>362.3</v>
       </c>
       <c r="M78">
-        <v>716.4525472</v>
+        <v>666.6527872</v>
       </c>
       <c r="N78">
-        <v>-354.1525472</v>
+        <v>-304.3527872</v>
       </c>
       <c r="O78">
-        <v>-72.95542472320001</v>
+        <v>-62.69667416320001</v>
       </c>
       <c r="P78">
-        <v>-281.1971224768</v>
+        <v>-241.6561130368</v>
       </c>
       <c r="Q78">
-        <v>-93.89712247680001</v>
+        <v>-54.3561130368</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1436674773679261</v>
+        <v>0.1429763991443284</v>
       </c>
       <c r="T78">
-        <v>2.258765757076858</v>
+        <v>2.244258640746615</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1041713094491459</v>
+        <v>0.1119530307725383</v>
       </c>
       <c r="W78">
-        <v>0.1933198314208743</v>
+        <v>0.1783198314208743</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +8102,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5056859681997373</v>
+        <v>0.5434613144297974</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +8113,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2064497405880757</v>
+        <v>0.1713874076745033</v>
       </c>
       <c r="C79">
-        <v>-2183.49245296252</v>
+        <v>-1968.409765970922</v>
       </c>
       <c r="D79">
-        <v>842.1755470374801</v>
+        <v>1057.258234029078</v>
       </c>
       <c r="E79">
         <v>1981.368</v>
@@ -7771,45 +8146,45 @@
         <v>362.3</v>
       </c>
       <c r="M79">
-        <v>826.7895943999999</v>
+        <v>675.4245344</v>
       </c>
       <c r="N79">
-        <v>-464.4895943999999</v>
+        <v>-313.1245344</v>
       </c>
       <c r="O79">
-        <v>-95.68485644639999</v>
+        <v>-64.50365408639999</v>
       </c>
       <c r="P79">
-        <v>-368.8047379536</v>
+        <v>-248.6208803136</v>
       </c>
       <c r="Q79">
-        <v>-181.5047379535999</v>
+        <v>-61.32088031359996</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1489942117748316</v>
+        <v>0.1472014599766905</v>
       </c>
       <c r="T79">
-        <v>2.381705936991052</v>
+        <v>2.341835103387772</v>
       </c>
       <c r="U79">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.09026939925890293</v>
+        <v>0.1104990953079599</v>
       </c>
       <c r="W79">
-        <v>0.2236117816621617</v>
+        <v>0.1786117816621617</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.4382009672762278</v>
+        <v>0.5364033752813585</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +8195,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2084497405880757</v>
+        <v>0.1729374076745033</v>
       </c>
       <c r="C80">
-        <v>-2236.841658557528</v>
+        <v>-2023.902703010633</v>
       </c>
       <c r="D80">
-        <v>832.5103414424723</v>
+        <v>1045.449296989367</v>
       </c>
       <c r="E80">
         <v>2025.052</v>
@@ -7853,45 +8228,45 @@
         <v>362.3</v>
       </c>
       <c r="M80">
-        <v>837.5271216</v>
+        <v>684.1962816</v>
       </c>
       <c r="N80">
-        <v>-475.2271216</v>
+        <v>-321.8962816</v>
       </c>
       <c r="O80">
-        <v>-97.89678704960001</v>
+        <v>-66.31063400960001</v>
       </c>
       <c r="P80">
-        <v>-377.3303345504</v>
+        <v>-255.5856475904</v>
       </c>
       <c r="Q80">
-        <v>-190.0303345504</v>
+        <v>-68.2856475904</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1536848577645966</v>
+        <v>0.1518106172483583</v>
       </c>
       <c r="T80">
-        <v>2.489965297763372</v>
+        <v>2.448282153541761</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.08911209926840417</v>
+        <v>0.1090824402399091</v>
       </c>
       <c r="W80">
-        <v>0.2238962459998263</v>
+        <v>0.1788962459998263</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.4325830061573017</v>
+        <v>0.5295264089315974</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +8277,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2104497405880758</v>
+        <v>0.1744874076745033</v>
       </c>
       <c r="C81">
-        <v>-2289.971536305388</v>
+        <v>-2079.134756547826</v>
       </c>
       <c r="D81">
-        <v>823.0644636946122</v>
+        <v>1033.901243452174</v>
       </c>
       <c r="E81">
         <v>2068.736</v>
@@ -7935,45 +8310,45 @@
         <v>362.3</v>
       </c>
       <c r="M81">
-        <v>848.2646488</v>
+        <v>692.9680288000001</v>
       </c>
       <c r="N81">
-        <v>-485.9646488</v>
+        <v>-330.6680288000001</v>
       </c>
       <c r="O81">
-        <v>-100.1087176528</v>
+        <v>-68.11761393280001</v>
       </c>
       <c r="P81">
-        <v>-385.8559311472</v>
+        <v>-262.5504148672001</v>
       </c>
       <c r="Q81">
-        <v>-198.5559311472</v>
+        <v>-75.25041486720005</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1588222319438632</v>
+        <v>0.1568587418792325</v>
       </c>
       <c r="T81">
-        <v>2.608535073847343</v>
+        <v>2.564867017996131</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.08798409801184209</v>
+        <v>0.1077016498571254</v>
       </c>
       <c r="W81">
-        <v>0.2241735087086892</v>
+        <v>0.1791735087086892</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.427107271902146</v>
+        <v>0.5228235429957544</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +8359,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2124497405880758</v>
+        <v>0.1760374076745033</v>
       </c>
       <c r="C82">
-        <v>-2342.889468100729</v>
+        <v>-2134.114477303993</v>
       </c>
       <c r="D82">
-        <v>813.8305318992707</v>
+        <v>1022.605522696007</v>
       </c>
       <c r="E82">
         <v>2112.42</v>
@@ -8017,45 +8392,45 @@
         <v>362.3</v>
       </c>
       <c r="M82">
-        <v>859.002176</v>
+        <v>701.739776</v>
       </c>
       <c r="N82">
-        <v>-496.702176</v>
+        <v>-339.439776</v>
       </c>
       <c r="O82">
-        <v>-102.320648256</v>
+        <v>-69.924593856</v>
       </c>
       <c r="P82">
-        <v>-394.381527744</v>
+        <v>-269.515182144</v>
       </c>
       <c r="Q82">
-        <v>-207.081527744</v>
+        <v>-82.21518214399998</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1644733435410563</v>
+        <v>0.1624116789731941</v>
       </c>
       <c r="T82">
-        <v>2.73896182753971</v>
+        <v>2.693110368895938</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.08688429678669407</v>
+        <v>0.1063553792339113</v>
       </c>
       <c r="W82">
-        <v>0.2244438398498306</v>
+        <v>0.1794438398498306</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.4217684310033692</v>
+        <v>0.5162882487083076</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8441,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2144497405880758</v>
+        <v>0.1775874076745033</v>
       </c>
       <c r="C83">
-        <v>-2395.60250824456</v>
+        <v>-2188.850046360967</v>
       </c>
       <c r="D83">
-        <v>804.8014917554399</v>
+        <v>1011.553953639033</v>
       </c>
       <c r="E83">
         <v>2156.104</v>
@@ -8099,45 +8474,45 @@
         <v>362.3</v>
       </c>
       <c r="M83">
-        <v>869.7397032</v>
+        <v>710.5115232000001</v>
       </c>
       <c r="N83">
-        <v>-507.4397032</v>
+        <v>-348.2115232</v>
       </c>
       <c r="O83">
-        <v>-104.5325788592</v>
+        <v>-71.73157377920002</v>
       </c>
       <c r="P83">
-        <v>-402.9071243408</v>
+        <v>-276.4799494208</v>
       </c>
       <c r="Q83">
-        <v>-215.6071243408</v>
+        <v>-89.17994942080003</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1707193089905856</v>
+        <v>0.1685491357612569</v>
       </c>
       <c r="T83">
-        <v>2.883117713199695</v>
+        <v>2.834853019890461</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.08581165114735216</v>
+        <v>0.1050423498606532</v>
       </c>
       <c r="W83">
-        <v>0.2247074961479809</v>
+        <v>0.1797074961479808</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.416561413336661</v>
+        <v>0.5099143197119087</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8523,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2164497405880758</v>
+        <v>0.1791374076745033</v>
       </c>
       <c r="C84">
-        <v>-2448.117401417295</v>
+        <v>-2243.349294921336</v>
       </c>
       <c r="D84">
-        <v>795.9705985827056</v>
+        <v>1000.738705078664</v>
       </c>
       <c r="E84">
         <v>2199.788</v>
@@ -8181,45 +8556,45 @@
         <v>362.3</v>
       </c>
       <c r="M84">
-        <v>880.4772304000002</v>
+        <v>719.2832704000001</v>
       </c>
       <c r="N84">
-        <v>-518.1772304000001</v>
+        <v>-356.9832704000001</v>
       </c>
       <c r="O84">
-        <v>-106.7445094624</v>
+        <v>-73.53855370240002</v>
       </c>
       <c r="P84">
-        <v>-411.4327209376</v>
+        <v>-283.4447166976001</v>
       </c>
       <c r="Q84">
-        <v>-224.1327209376</v>
+        <v>-96.14471669760007</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1776592706011737</v>
+        <v>0.1753685321924379</v>
       </c>
       <c r="T84">
-        <v>3.043290919488567</v>
+        <v>2.99234485432882</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.08476516759677469</v>
+        <v>0.1037613455940598</v>
       </c>
       <c r="W84">
-        <v>0.2249647218047128</v>
+        <v>0.1799647218047128</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.411481396100848</v>
+        <v>0.5036958523983488</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8605,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2184497405880758</v>
+        <v>0.2100593400517391</v>
       </c>
       <c r="C85">
-        <v>-2500.440599481346</v>
+        <v>-2462.961864005984</v>
       </c>
       <c r="D85">
-        <v>787.3314005186538</v>
+        <v>824.8101359940156</v>
       </c>
       <c r="E85">
         <v>2243.472</v>
@@ -8263,37 +8638,37 @@
         <v>362.3</v>
       </c>
       <c r="M85">
-        <v>891.2147576000001</v>
+        <v>854.9570376</v>
       </c>
       <c r="N85">
-        <v>-528.9147576</v>
+        <v>-492.6570376</v>
       </c>
       <c r="O85">
-        <v>-108.9564400656</v>
+        <v>-101.4873497456</v>
       </c>
       <c r="P85">
-        <v>-419.9583175344</v>
+        <v>-391.1696878544</v>
       </c>
       <c r="Q85">
-        <v>-232.6583175344</v>
+        <v>-203.8696878544</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1854156982835957</v>
+        <v>0.1848839304227919</v>
       </c>
       <c r="T85">
-        <v>3.222308032399659</v>
+        <v>3.212100009764248</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08374390051729548</v>
+        <v>0.08729538060708748</v>
       </c>
       <c r="W85">
-        <v>0.2252157492528488</v>
+        <v>0.2152157492528488</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8676,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4065237889189101</v>
+        <v>0.4237639835295509</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8687,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2204497405880758</v>
+        <v>0.2119593400517391</v>
       </c>
       <c r="C86">
-        <v>-2552.578277201248</v>
+        <v>-2515.460219480058</v>
       </c>
       <c r="D86">
-        <v>778.8777227987515</v>
+        <v>815.9957805199421</v>
       </c>
       <c r="E86">
         <v>2287.156</v>
@@ -8345,37 +8720,37 @@
         <v>362.3</v>
       </c>
       <c r="M86">
-        <v>901.9522848</v>
+        <v>865.2577248</v>
       </c>
       <c r="N86">
-        <v>-539.6522848</v>
+        <v>-502.9577248</v>
       </c>
       <c r="O86">
-        <v>-111.1683706688</v>
+        <v>-103.6092913088</v>
       </c>
       <c r="P86">
-        <v>-428.4839141312</v>
+        <v>-399.3484334912</v>
       </c>
       <c r="Q86">
-        <v>-241.1839141312</v>
+        <v>-212.0484334912</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1941416794263204</v>
+        <v>0.1935766760742163</v>
       </c>
       <c r="T86">
-        <v>3.423702284424636</v>
+        <v>3.412856260374512</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08274694932066101</v>
+        <v>0.08625614988557455</v>
       </c>
       <c r="W86">
-        <v>0.2254607998569816</v>
+        <v>0.2154607998569815</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8758,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4016842200032088</v>
+        <v>0.4187191742018181</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8769,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2224497405880758</v>
+        <v>0.2138593400517391</v>
       </c>
       <c r="C87">
-        <v>-2604.5363469618</v>
+        <v>-2567.772177209778</v>
       </c>
       <c r="D87">
-        <v>770.6036530381999</v>
+        <v>807.367822790221</v>
       </c>
       <c r="E87">
         <v>2330.839999999999</v>
@@ -8427,37 +8802,37 @@
         <v>362.3</v>
       </c>
       <c r="M87">
-        <v>912.689812</v>
+        <v>875.5584119999999</v>
       </c>
       <c r="N87">
-        <v>-550.3898119999999</v>
+        <v>-513.2584119999999</v>
       </c>
       <c r="O87">
-        <v>-113.380301272</v>
+        <v>-105.731232872</v>
       </c>
       <c r="P87">
-        <v>-437.0095107279999</v>
+        <v>-407.5271791279999</v>
       </c>
       <c r="Q87">
-        <v>-249.7095107279999</v>
+        <v>-220.2271791279999</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2040311247214084</v>
+        <v>0.2034284544791641</v>
       </c>
       <c r="T87">
-        <v>3.651949103386279</v>
+        <v>3.640380011066146</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08177345579924147</v>
+        <v>0.08524137165162662</v>
       </c>
       <c r="W87">
-        <v>0.2257000845645465</v>
+        <v>0.2157000845645465</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8840,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3969585232972888</v>
+        <v>0.413793066270032</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8851,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2244497405880757</v>
+        <v>0.2157593400517391</v>
       </c>
       <c r="C88">
-        <v>-2656.320472557961</v>
+        <v>-2619.903587979395</v>
       </c>
       <c r="D88">
-        <v>762.5035274420383</v>
+        <v>798.9204120206052</v>
       </c>
       <c r="E88">
         <v>2374.523999999999</v>
@@ -8509,37 +8884,37 @@
         <v>362.3</v>
       </c>
       <c r="M88">
-        <v>923.4273392</v>
+        <v>885.8590991999999</v>
       </c>
       <c r="N88">
-        <v>-561.1273392000001</v>
+        <v>-523.5590992</v>
       </c>
       <c r="O88">
-        <v>-115.5922318752</v>
+        <v>-107.8531744352</v>
       </c>
       <c r="P88">
-        <v>-445.5351073248</v>
+        <v>-415.7059247648</v>
       </c>
       <c r="Q88">
-        <v>-258.2351073248</v>
+        <v>-228.4059247648</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2153333479157947</v>
+        <v>0.2146876297991044</v>
       </c>
       <c r="T88">
-        <v>3.912802610771013</v>
+        <v>3.900407154713728</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08082260166204099</v>
+        <v>0.08425019291149141</v>
       </c>
       <c r="W88">
-        <v>0.2259338045114703</v>
+        <v>0.2159338045114703</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8922,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.392342726514762</v>
+        <v>0.4089815189878223</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8933,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2264497405880757</v>
+        <v>0.2176593400517391</v>
       </c>
       <c r="C89">
-        <v>-2707.93608212409</v>
+        <v>-2671.86006024388</v>
       </c>
       <c r="D89">
-        <v>754.5719178759094</v>
+        <v>790.6479397561195</v>
       </c>
       <c r="E89">
         <v>2418.208</v>
@@ -8591,37 +8966,37 @@
         <v>362.3</v>
       </c>
       <c r="M89">
-        <v>934.1648664000001</v>
+        <v>896.1597864</v>
       </c>
       <c r="N89">
-        <v>-571.8648664</v>
+        <v>-533.8597864000001</v>
       </c>
       <c r="O89">
-        <v>-117.8041624784</v>
+        <v>-109.9751159984</v>
       </c>
       <c r="P89">
-        <v>-454.0607039216</v>
+        <v>-423.8846704016</v>
       </c>
       <c r="Q89">
-        <v>-266.7607039215999</v>
+        <v>-236.5846704016</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2283743746785481</v>
+        <v>0.2276789859374971</v>
       </c>
       <c r="T89">
-        <v>4.213787426984167</v>
+        <v>4.200438474307092</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07989360624063821</v>
+        <v>0.08328179988952024</v>
       </c>
       <c r="W89">
-        <v>0.2261621515860511</v>
+        <v>0.2161621515860511</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +9004,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3878330400030982</v>
+        <v>0.4042805819879622</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +9015,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2284497405880757</v>
+        <v>0.2195593400517391</v>
       </c>
       <c r="C90">
-        <v>-2759.388380264539</v>
+        <v>-2723.646972546431</v>
       </c>
       <c r="D90">
-        <v>746.8036197354609</v>
+        <v>782.5450274535687</v>
       </c>
       <c r="E90">
         <v>2461.892</v>
@@ -8673,37 +9048,37 @@
         <v>362.3</v>
       </c>
       <c r="M90">
-        <v>944.9023936</v>
+        <v>906.4604735999999</v>
       </c>
       <c r="N90">
-        <v>-582.6023935999999</v>
+        <v>-544.1604735999999</v>
       </c>
       <c r="O90">
-        <v>-120.0160930816</v>
+        <v>-112.0970575616</v>
       </c>
       <c r="P90">
-        <v>-462.5863005183999</v>
+        <v>-432.0634160384</v>
       </c>
       <c r="Q90">
-        <v>-275.2863005183999</v>
+        <v>-244.7634160384</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2435889059017605</v>
+        <v>0.2428355680989552</v>
       </c>
       <c r="T90">
-        <v>4.564936379232849</v>
+        <v>4.550475013832684</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07898572435154007</v>
+        <v>0.08233541579986663</v>
       </c>
       <c r="W90">
-        <v>0.2263853089543915</v>
+        <v>0.2163853089543915</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +9086,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3834258463666993</v>
+        <v>0.3996864844653718</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +9097,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2304497405880758</v>
+        <v>0.2214593400517391</v>
       </c>
       <c r="C91">
-        <v>-2810.682359442584</v>
+        <v>-2775.26948518014</v>
       </c>
       <c r="D91">
-        <v>739.1936405574154</v>
+        <v>774.6065148198597</v>
       </c>
       <c r="E91">
         <v>2505.576</v>
@@ -8755,37 +9130,37 @@
         <v>362.3</v>
       </c>
       <c r="M91">
-        <v>955.6399208</v>
+        <v>916.7611608</v>
       </c>
       <c r="N91">
-        <v>-593.3399208000001</v>
+        <v>-554.4611608</v>
       </c>
       <c r="O91">
-        <v>-122.2280236848</v>
+        <v>-114.2189991248</v>
       </c>
       <c r="P91">
-        <v>-471.1118971152001</v>
+        <v>-440.2421616752</v>
       </c>
       <c r="Q91">
-        <v>-283.8118971152001</v>
+        <v>-252.9421616752</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2615697155291933</v>
+        <v>0.2607478924715875</v>
       </c>
       <c r="T91">
-        <v>4.979930595526744</v>
+        <v>4.964154560544746</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07809824430264635</v>
+        <v>0.08141029876840744</v>
       </c>
       <c r="W91">
-        <v>0.2266034515504095</v>
+        <v>0.2166034515504095</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +9168,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3791176907895453</v>
+        <v>0.3951956250893564</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +9179,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2324497405880757</v>
+        <v>0.2233593400517391</v>
       </c>
       <c r="C92">
-        <v>-2861.822810680058</v>
+        <v>-2826.732551146994</v>
       </c>
       <c r="D92">
-        <v>731.737189319942</v>
+        <v>766.8274488530061</v>
       </c>
       <c r="E92">
         <v>2549.26</v>
@@ -8837,37 +9212,37 @@
         <v>362.3</v>
       </c>
       <c r="M92">
-        <v>966.3774480000001</v>
+        <v>927.0618480000001</v>
       </c>
       <c r="N92">
-        <v>-604.077448</v>
+        <v>-564.7618480000001</v>
       </c>
       <c r="O92">
-        <v>-124.439954288</v>
+        <v>-116.340940688</v>
       </c>
       <c r="P92">
-        <v>-479.637493712</v>
+        <v>-448.4209073120001</v>
       </c>
       <c r="Q92">
-        <v>-292.337493712</v>
+        <v>-261.120907312</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2831466870821127</v>
+        <v>0.2822426817187462</v>
       </c>
       <c r="T92">
-        <v>5.47792365507942</v>
+        <v>5.460570016599221</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07723048603261694</v>
+        <v>0.08050573989320289</v>
       </c>
       <c r="W92">
-        <v>0.2268167465331828</v>
+        <v>0.2168167465331828</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +9250,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3749052720029948</v>
+        <v>0.3908045625883635</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +9261,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2344497405880757</v>
+        <v>0.2252593400517391</v>
       </c>
       <c r="C93">
-        <v>-2912.81433361586</v>
+        <v>-2878.040926463092</v>
       </c>
       <c r="D93">
-        <v>724.4296663841394</v>
+        <v>759.2030735369079</v>
       </c>
       <c r="E93">
         <v>2592.944</v>
@@ -8919,37 +9294,37 @@
         <v>362.3</v>
       </c>
       <c r="M93">
-        <v>977.1149752</v>
+        <v>937.3625351999999</v>
       </c>
       <c r="N93">
-        <v>-614.8149751999999</v>
+        <v>-575.0625352</v>
       </c>
       <c r="O93">
-        <v>-126.6518848912</v>
+        <v>-118.4628822512</v>
       </c>
       <c r="P93">
-        <v>-488.1630903088</v>
+        <v>-456.5996529488</v>
       </c>
       <c r="Q93">
-        <v>-300.8630903087999</v>
+        <v>-269.2996529488</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3095185412023475</v>
+        <v>0.3085140907986069</v>
       </c>
       <c r="T93">
-        <v>6.086581838977134</v>
+        <v>6.067300018443579</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07638179937291785</v>
+        <v>0.07962106143283805</v>
       </c>
       <c r="W93">
-        <v>0.2270253537141368</v>
+        <v>0.2170253537141368</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +9332,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3707854338491159</v>
+        <v>0.3865100069555244</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +9343,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2364497405880757</v>
+        <v>0.2271593400517391</v>
       </c>
       <c r="C94">
-        <v>-2963.661345967738</v>
+        <v>-2929.199179855149</v>
       </c>
       <c r="D94">
-        <v>717.266654032262</v>
+        <v>751.7288201448506</v>
       </c>
       <c r="E94">
         <v>2636.628</v>
@@ -9001,37 +9376,37 @@
         <v>362.3</v>
       </c>
       <c r="M94">
-        <v>987.8525024</v>
+        <v>947.6632224</v>
       </c>
       <c r="N94">
-        <v>-625.5525024000001</v>
+        <v>-585.3632224</v>
       </c>
       <c r="O94">
-        <v>-128.8638154944</v>
+        <v>-120.5848238144</v>
       </c>
       <c r="P94">
-        <v>-496.6886869056001</v>
+        <v>-464.7783985856</v>
       </c>
       <c r="Q94">
-        <v>-309.3886869056001</v>
+        <v>-277.4783985856</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3424833588526409</v>
+        <v>0.3413533521484329</v>
       </c>
       <c r="T94">
-        <v>6.847404568849277</v>
+        <v>6.825712520749029</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07555156242321223</v>
+        <v>0.07875561511291589</v>
       </c>
       <c r="W94">
-        <v>0.2272294259563744</v>
+        <v>0.2172294259563745</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9414,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.366755157394234</v>
+        <v>0.382308811227747</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9425,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2384497405880758</v>
+        <v>0.2290593400517391</v>
       </c>
       <c r="C95">
-        <v>-3014.36809243822</v>
+        <v>-2980.211701889812</v>
       </c>
       <c r="D95">
-        <v>710.2439075617805</v>
+        <v>744.4002981101885</v>
       </c>
       <c r="E95">
         <v>2680.312</v>
@@ -9083,37 +9458,37 @@
         <v>362.3</v>
       </c>
       <c r="M95">
-        <v>998.5900296000001</v>
+        <v>957.9639096000001</v>
       </c>
       <c r="N95">
-        <v>-636.2900296</v>
+        <v>-595.6639096000001</v>
       </c>
       <c r="O95">
-        <v>-131.0757460976</v>
+        <v>-122.7067653776</v>
       </c>
       <c r="P95">
-        <v>-505.2142835024</v>
+        <v>-472.9571442224001</v>
       </c>
       <c r="Q95">
-        <v>-317.9142835024</v>
+        <v>-285.6571442224001</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3848666958315897</v>
+        <v>0.383575259598209</v>
       </c>
       <c r="T95">
-        <v>7.825605221542031</v>
+        <v>7.800814309427462</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07473918003156478</v>
+        <v>0.07790878054180926</v>
       </c>
       <c r="W95">
-        <v>0.2274291095482414</v>
+        <v>0.2174291095482414</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9496,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3628115535512854</v>
+        <v>0.3781979637951904</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9507,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2404497405880758</v>
+        <v>0.2309593400517391</v>
       </c>
       <c r="C96">
-        <v>-3064.938653102435</v>
+        <v>-3031.082713574127</v>
       </c>
       <c r="D96">
-        <v>703.3573468975655</v>
+        <v>737.213286425873</v>
       </c>
       <c r="E96">
         <v>2723.996</v>
@@ -9165,37 +9540,37 @@
         <v>362.3</v>
       </c>
       <c r="M96">
-        <v>1009.3275568</v>
+        <v>968.2645968</v>
       </c>
       <c r="N96">
-        <v>-647.0275568000002</v>
+        <v>-605.9645968</v>
       </c>
       <c r="O96">
-        <v>-133.2876767008001</v>
+        <v>-124.8287069408</v>
       </c>
       <c r="P96">
-        <v>-513.7398800992001</v>
+        <v>-481.1358898592</v>
       </c>
       <c r="Q96">
-        <v>-326.4398800992001</v>
+        <v>-293.8358898592</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4413778118035214</v>
+        <v>0.4398711361979107</v>
       </c>
       <c r="T96">
-        <v>9.129872758465707</v>
+        <v>9.100950027665375</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07394408237165451</v>
+        <v>0.07707996372753469</v>
       </c>
       <c r="W96">
-        <v>0.2276245445530473</v>
+        <v>0.2176245445530473</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9578,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3589518561730801</v>
+        <v>0.3741745812016247</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9589,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2424497405880758</v>
+        <v>0.2328593400517391</v>
       </c>
       <c r="C97">
-        <v>-3115.376951312652</v>
+        <v>-3081.816274462567</v>
       </c>
       <c r="D97">
-        <v>696.6030486873481</v>
+        <v>730.1637255374332</v>
       </c>
       <c r="E97">
         <v>2767.679999999999</v>
@@ -9247,37 +9622,37 @@
         <v>362.3</v>
       </c>
       <c r="M97">
-        <v>1020.065084</v>
+        <v>978.5652839999999</v>
       </c>
       <c r="N97">
-        <v>-657.7650839999999</v>
+        <v>-616.2652839999998</v>
       </c>
       <c r="O97">
-        <v>-135.499607304</v>
+        <v>-126.950648504</v>
       </c>
       <c r="P97">
-        <v>-522.265476696</v>
+        <v>-489.3146354959999</v>
       </c>
       <c r="Q97">
-        <v>-334.9654766959999</v>
+        <v>-302.0146354959999</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5204933741642258</v>
+        <v>0.5186853634374929</v>
       </c>
       <c r="T97">
-        <v>10.95584731015885</v>
+        <v>10.92114003319845</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07316572360984763</v>
+        <v>0.0762685956882975</v>
       </c>
       <c r="W97">
-        <v>0.2278158651366995</v>
+        <v>0.2178158651366995</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9660,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3551734155817846</v>
+        <v>0.3702359013995025</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9671,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2444497405880757</v>
+        <v>0.2347593400517391</v>
       </c>
       <c r="C98">
-        <v>-3165.686761151705</v>
+        <v>-3132.416290303316</v>
       </c>
       <c r="D98">
-        <v>689.977238848295</v>
+        <v>723.2477096966842</v>
       </c>
       <c r="E98">
         <v>2811.364</v>
@@ -9329,37 +9704,37 @@
         <v>362.3</v>
       </c>
       <c r="M98">
-        <v>1030.8026112</v>
+        <v>988.8659712</v>
       </c>
       <c r="N98">
-        <v>-668.5026112</v>
+        <v>-626.5659711999999</v>
       </c>
       <c r="O98">
-        <v>-137.7115379072</v>
+        <v>-129.0725900672</v>
       </c>
       <c r="P98">
-        <v>-530.7910732928001</v>
+        <v>-497.4933811327999</v>
       </c>
       <c r="Q98">
-        <v>-343.4910732928001</v>
+        <v>-310.1933811327999</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6391667177052811</v>
+        <v>0.6369067042968649</v>
       </c>
       <c r="T98">
-        <v>13.69480913769854</v>
+        <v>13.65142504149804</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07240358065557839</v>
+        <v>0.07547413114987772</v>
       </c>
       <c r="W98">
-        <v>0.2280031998748588</v>
+        <v>0.2180031998748589</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9742,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3514736925028076</v>
+        <v>0.3663792774265909</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9753,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2464497405880758</v>
+        <v>0.2366593400517391</v>
       </c>
       <c r="C99">
-        <v>-3215.871714465059</v>
+        <v>-3182.886520254086</v>
       </c>
       <c r="D99">
-        <v>683.4762855349408</v>
+        <v>716.4614797459133</v>
       </c>
       <c r="E99">
         <v>2855.048</v>
@@ -9411,37 +9786,37 @@
         <v>362.3</v>
       </c>
       <c r="M99">
-        <v>1041.5401384</v>
+        <v>999.1666584000001</v>
       </c>
       <c r="N99">
-        <v>-679.2401384000002</v>
+        <v>-636.8666584</v>
       </c>
       <c r="O99">
-        <v>-139.9234685104001</v>
+        <v>-131.1945316304</v>
       </c>
       <c r="P99">
-        <v>-539.3166698896001</v>
+        <v>-505.6721267696</v>
       </c>
       <c r="Q99">
-        <v>-352.0166698896001</v>
+        <v>-318.3721267696</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8369556236070415</v>
+        <v>0.8339422723958199</v>
       </c>
       <c r="T99">
-        <v>18.25974551693138</v>
+        <v>18.20190005533072</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07165715198902602</v>
+        <v>0.07469604732359032</v>
       </c>
       <c r="W99">
-        <v>0.2281866720410974</v>
+        <v>0.2181866720410974</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9824,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3478502523739126</v>
+        <v>0.3626021714737394</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9835,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2484497405880758</v>
+        <v>0.2385593400517391</v>
       </c>
       <c r="C100">
-        <v>-3265.935307499059</v>
+        <v>-3233.230583695484</v>
       </c>
       <c r="D100">
-        <v>677.0966925009404</v>
+        <v>709.8014163045151</v>
       </c>
       <c r="E100">
         <v>2898.731999999999</v>
@@ -9493,37 +9868,37 @@
         <v>362.3</v>
       </c>
       <c r="M100">
-        <v>1052.2776656</v>
+        <v>1009.4673456</v>
       </c>
       <c r="N100">
-        <v>-689.9776655999999</v>
+        <v>-647.1673455999999</v>
       </c>
       <c r="O100">
-        <v>-142.1353991136</v>
+        <v>-133.3164731936</v>
       </c>
       <c r="P100">
-        <v>-547.8422664863999</v>
+        <v>-513.8508724063998</v>
       </c>
       <c r="Q100">
-        <v>-360.5422664863999</v>
+        <v>-326.5508724063998</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.232533435410562</v>
+        <v>1.22801340859373</v>
       </c>
       <c r="T100">
-        <v>27.38961827539707</v>
+        <v>27.30285008299608</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07092595656056659</v>
+        <v>0.07393384275906391</v>
       </c>
       <c r="W100">
-        <v>0.2283663998774128</v>
+        <v>0.2183663998774127</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9906,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3443007600027503</v>
+        <v>0.3589021493158441</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9917,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2504497405880757</v>
+        <v>0.2404593400517391</v>
       </c>
       <c r="C101">
-        <v>-3315.88090717084</v>
+        <v>-3283.451966667848</v>
       </c>
       <c r="D101">
-        <v>670.8350928291597</v>
+        <v>703.2640333321515</v>
       </c>
       <c r="E101">
         <v>2942.415999999999</v>
@@ -9575,37 +9950,37 @@
         <v>362.3</v>
       </c>
       <c r="M101">
-        <v>1063.0151928</v>
+        <v>1019.7680328</v>
       </c>
       <c r="N101">
-        <v>-700.7151928000001</v>
+        <v>-657.4680327999999</v>
       </c>
       <c r="O101">
-        <v>-144.3473297168</v>
+        <v>-135.4384147568</v>
       </c>
       <c r="P101">
-        <v>-556.3678630832001</v>
+        <v>-522.0296180431999</v>
       </c>
       <c r="Q101">
-        <v>-369.0678630832001</v>
+        <v>-334.7296180431999</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.419266870821124</v>
+        <v>2.41022681718746</v>
       </c>
       <c r="T101">
-        <v>54.77923655079413</v>
+        <v>54.60570016599215</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.07020953275692449</v>
+        <v>0.0731870362665481</v>
       </c>
       <c r="W101">
-        <v>0.228542496848348</v>
+        <v>0.218542496848348</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9988,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3408229745481771</v>
+        <v>0.3552768750803306</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/sweden/sweden_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_farming_agriculture.xlsx
@@ -1659,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1796,22 +1796,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07129124021041604</v>
+        <v>0.07118011025558257</v>
       </c>
       <c r="C2">
-        <v>4245.763689196644</v>
+        <v>4213.812031294751</v>
       </c>
       <c r="D2">
-        <v>3907.763689196644</v>
+        <v>3919.496031294751</v>
       </c>
       <c r="E2">
-        <v>-1382.3</v>
+        <v>-1338.616</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>43.684</v>
       </c>
       <c r="G2">
         <v>338</v>
@@ -1832,28 +1832,28 @@
         <v>362.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.1973052</v>
       </c>
       <c r="N2">
-        <v>362.3</v>
+        <v>360.1026948</v>
       </c>
       <c r="O2">
-        <v>74.63380000000001</v>
+        <v>74.1811551288</v>
       </c>
       <c r="P2">
-        <v>287.6662</v>
+        <v>285.9215396712</v>
       </c>
       <c r="Q2">
-        <v>474.9662</v>
+        <v>473.2215396712</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07129124021041604</v>
+        <v>0.07149568510664907</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5934338361812719</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>164.8837858300249</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1878,22 +1878,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07118011025558257</v>
+        <v>0.07106898030074911</v>
       </c>
       <c r="C3">
-        <v>4213.812031294751</v>
+        <v>4181.931033938858</v>
       </c>
       <c r="D3">
-        <v>3919.496031294751</v>
+        <v>3931.299033938858</v>
       </c>
       <c r="E3">
-        <v>-1338.616</v>
+        <v>-1294.932</v>
       </c>
       <c r="F3">
-        <v>43.684</v>
+        <v>87.36799999999999</v>
       </c>
       <c r="G3">
         <v>338</v>
@@ -1914,28 +1914,28 @@
         <v>362.3</v>
       </c>
       <c r="M3">
-        <v>2.1973052</v>
+        <v>4.394610399999999</v>
       </c>
       <c r="N3">
-        <v>360.1026948</v>
+        <v>357.9053896</v>
       </c>
       <c r="O3">
-        <v>74.1811551288</v>
+        <v>73.72851025760001</v>
       </c>
       <c r="P3">
-        <v>285.9215396712</v>
+        <v>284.1768793424</v>
       </c>
       <c r="Q3">
-        <v>473.2215396712</v>
+        <v>471.4768793424</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07149568510664907</v>
+        <v>0.07170430234770318</v>
       </c>
       <c r="T3">
-        <v>0.5934338361812719</v>
+        <v>0.5982517863210898</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>164.8837858300249</v>
+        <v>82.44189291501246</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1960,22 +1960,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07106898030074911</v>
+        <v>0.07095785034591566</v>
       </c>
       <c r="C4">
-        <v>4181.931033938858</v>
+        <v>4150.12133740951</v>
       </c>
       <c r="D4">
-        <v>3931.299033938858</v>
+        <v>3943.173337409509</v>
       </c>
       <c r="E4">
-        <v>-1294.932</v>
+        <v>-1251.248</v>
       </c>
       <c r="F4">
-        <v>87.36799999999999</v>
+        <v>131.052</v>
       </c>
       <c r="G4">
         <v>338</v>
@@ -1996,28 +1996,28 @@
         <v>362.3</v>
       </c>
       <c r="M4">
-        <v>4.394610399999999</v>
+        <v>6.591915599999999</v>
       </c>
       <c r="N4">
-        <v>357.9053896</v>
+        <v>355.7080844</v>
       </c>
       <c r="O4">
-        <v>73.72851025760001</v>
+        <v>73.27586538640001</v>
       </c>
       <c r="P4">
-        <v>284.1768793424</v>
+        <v>282.4322190136</v>
       </c>
       <c r="Q4">
-        <v>471.4768793424</v>
+        <v>469.7322190136</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07170430234770318</v>
+        <v>0.07191722097517078</v>
       </c>
       <c r="T4">
-        <v>0.5982517863210898</v>
+        <v>0.6031690756390483</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>82.44189291501246</v>
+        <v>54.96126194334164</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2042,22 +2042,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07095785034591566</v>
+        <v>0.07084672039108221</v>
       </c>
       <c r="C5">
-        <v>4150.12133740951</v>
+        <v>4118.383589746441</v>
       </c>
       <c r="D5">
-        <v>3943.173337409509</v>
+        <v>3955.11958974644</v>
       </c>
       <c r="E5">
-        <v>-1251.248</v>
+        <v>-1207.564</v>
       </c>
       <c r="F5">
-        <v>131.052</v>
+        <v>174.736</v>
       </c>
       <c r="G5">
         <v>338</v>
@@ -2078,28 +2078,28 @@
         <v>362.3</v>
       </c>
       <c r="M5">
-        <v>6.591915599999999</v>
+        <v>8.789220799999999</v>
       </c>
       <c r="N5">
-        <v>355.7080844</v>
+        <v>353.5107792</v>
       </c>
       <c r="O5">
-        <v>73.27586538640001</v>
+        <v>72.82322051520001</v>
       </c>
       <c r="P5">
-        <v>282.4322190136</v>
+        <v>280.6875586848</v>
       </c>
       <c r="Q5">
-        <v>469.7322190136</v>
+        <v>467.9875586848</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07191722097517078</v>
+        <v>0.0721345754073773</v>
       </c>
       <c r="T5">
-        <v>0.6031690756390483</v>
+        <v>0.6081888084844643</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>54.96126194334164</v>
+        <v>41.22094645750623</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2124,22 +2124,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07084672039108221</v>
+        <v>0.07073559043624875</v>
       </c>
       <c r="C6">
-        <v>4118.383589746441</v>
+        <v>4086.718446866464</v>
       </c>
       <c r="D6">
-        <v>3955.11958974644</v>
+        <v>3967.138446866464</v>
       </c>
       <c r="E6">
-        <v>-1207.564</v>
+        <v>-1163.88</v>
       </c>
       <c r="F6">
-        <v>174.736</v>
+        <v>218.42</v>
       </c>
       <c r="G6">
         <v>338</v>
@@ -2160,28 +2160,28 @@
         <v>362.3</v>
       </c>
       <c r="M6">
-        <v>8.789220799999999</v>
+        <v>10.986526</v>
       </c>
       <c r="N6">
-        <v>353.5107792</v>
+        <v>351.313474</v>
       </c>
       <c r="O6">
-        <v>72.82322051520001</v>
+        <v>72.370575644</v>
       </c>
       <c r="P6">
-        <v>280.6875586848</v>
+        <v>278.942898356</v>
       </c>
       <c r="Q6">
-        <v>467.9875586848</v>
+        <v>466.242898356</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0721345754073773</v>
+        <v>0.0723565057223671</v>
       </c>
       <c r="T6">
-        <v>0.6081888084844643</v>
+        <v>0.6133142199160996</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>41.22094645750623</v>
+        <v>32.97675716600497</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2206,22 +2206,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07073559043624875</v>
+        <v>0.07062446048141528</v>
       </c>
       <c r="C7">
-        <v>4086.718446866464</v>
+        <v>4055.126572683519</v>
       </c>
       <c r="D7">
-        <v>3967.138446866464</v>
+        <v>3979.230572683519</v>
       </c>
       <c r="E7">
-        <v>-1163.88</v>
+        <v>-1120.196</v>
       </c>
       <c r="F7">
-        <v>218.42</v>
+        <v>262.104</v>
       </c>
       <c r="G7">
         <v>338</v>
@@ -2242,28 +2242,28 @@
         <v>362.3</v>
       </c>
       <c r="M7">
-        <v>10.986526</v>
+        <v>13.1838312</v>
       </c>
       <c r="N7">
-        <v>351.313474</v>
+        <v>349.1161688</v>
       </c>
       <c r="O7">
-        <v>72.370575644</v>
+        <v>71.91793077280001</v>
       </c>
       <c r="P7">
-        <v>278.942898356</v>
+        <v>277.1982380272</v>
       </c>
       <c r="Q7">
-        <v>466.242898356</v>
+        <v>464.4982380272</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0723565057223671</v>
+        <v>0.07258315795895244</v>
       </c>
       <c r="T7">
-        <v>0.6133142199160996</v>
+        <v>0.6185486826547908</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.97675716600497</v>
+        <v>27.48063097167082</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2288,22 +2288,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07062446048141528</v>
+        <v>0.07051333052658183</v>
       </c>
       <c r="C8">
-        <v>4055.126572683519</v>
+        <v>4023.608639230925</v>
       </c>
       <c r="D8">
-        <v>3979.230572683519</v>
+        <v>3991.396639230925</v>
       </c>
       <c r="E8">
-        <v>-1120.196</v>
+        <v>-1076.512</v>
       </c>
       <c r="F8">
-        <v>262.104</v>
+        <v>305.788</v>
       </c>
       <c r="G8">
         <v>338</v>
@@ -2324,28 +2324,28 @@
         <v>362.3</v>
       </c>
       <c r="M8">
-        <v>13.1838312</v>
+        <v>15.3811364</v>
       </c>
       <c r="N8">
-        <v>349.1161688</v>
+        <v>346.9188636</v>
       </c>
       <c r="O8">
-        <v>71.91793077280001</v>
+        <v>71.46528590160001</v>
       </c>
       <c r="P8">
-        <v>277.1982380272</v>
+        <v>275.4535776984</v>
       </c>
       <c r="Q8">
-        <v>464.4982380272</v>
+        <v>462.7535776984</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07258315795895244</v>
+        <v>0.07281468443718477</v>
       </c>
       <c r="T8">
-        <v>0.6185486826547908</v>
+        <v>0.6238957144846368</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.48063097167082</v>
+        <v>23.55482654714642</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2370,22 +2370,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07051333052658182</v>
+        <v>0.07040220057174838</v>
       </c>
       <c r="C9">
-        <v>4023.608639230927</v>
+        <v>3992.165326785882</v>
       </c>
       <c r="D9">
-        <v>3991.396639230926</v>
+        <v>4003.637326785882</v>
       </c>
       <c r="E9">
-        <v>-1076.512</v>
+        <v>-1032.828</v>
       </c>
       <c r="F9">
-        <v>305.788</v>
+        <v>349.472</v>
       </c>
       <c r="G9">
         <v>338</v>
@@ -2406,28 +2406,28 @@
         <v>362.3</v>
       </c>
       <c r="M9">
-        <v>15.3811364</v>
+        <v>17.5784416</v>
       </c>
       <c r="N9">
-        <v>346.9188636</v>
+        <v>344.7215584</v>
       </c>
       <c r="O9">
-        <v>71.46528590160001</v>
+        <v>71.0126410304</v>
       </c>
       <c r="P9">
-        <v>275.4535776984</v>
+        <v>273.7089173696</v>
       </c>
       <c r="Q9">
-        <v>462.7535776984</v>
+        <v>461.0089173696</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07281468443718477</v>
+        <v>0.07305124409972649</v>
       </c>
       <c r="T9">
-        <v>0.6238957144846368</v>
+        <v>0.6293589861368708</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.55482654714642</v>
+        <v>20.61047322875311</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2452,22 +2452,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07040220057174838</v>
+        <v>0.07029107061691492</v>
       </c>
       <c r="C10">
-        <v>3992.165326785882</v>
+        <v>3960.797323996274</v>
       </c>
       <c r="D10">
-        <v>4003.637326785882</v>
+        <v>4015.953323996274</v>
       </c>
       <c r="E10">
-        <v>-1032.828</v>
+        <v>-989.144</v>
       </c>
       <c r="F10">
-        <v>349.472</v>
+        <v>393.1559999999999</v>
       </c>
       <c r="G10">
         <v>338</v>
@@ -2488,28 +2488,28 @@
         <v>362.3</v>
       </c>
       <c r="M10">
-        <v>17.5784416</v>
+        <v>19.7757468</v>
       </c>
       <c r="N10">
-        <v>344.7215584</v>
+        <v>342.5242532</v>
       </c>
       <c r="O10">
-        <v>71.0126410304</v>
+        <v>70.55999615920001</v>
       </c>
       <c r="P10">
-        <v>273.7089173696</v>
+        <v>271.9642570408</v>
       </c>
       <c r="Q10">
-        <v>461.0089173696</v>
+        <v>459.2642570408</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07305124409972649</v>
+        <v>0.07329300287573068</v>
       </c>
       <c r="T10">
-        <v>0.6293589861368708</v>
+        <v>0.6349423296935494</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.61047322875311</v>
+        <v>18.32042064778055</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2534,22 +2534,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07029107061691492</v>
+        <v>0.07017994066208147</v>
       </c>
       <c r="C11">
-        <v>3960.797323996274</v>
+        <v>3929.505328009805</v>
       </c>
       <c r="D11">
-        <v>4015.953323996274</v>
+        <v>4028.345328009806</v>
       </c>
       <c r="E11">
-        <v>-989.144</v>
+        <v>-945.46</v>
       </c>
       <c r="F11">
-        <v>393.1559999999999</v>
+        <v>436.8399999999999</v>
       </c>
       <c r="G11">
         <v>338</v>
@@ -2570,28 +2570,28 @@
         <v>362.3</v>
       </c>
       <c r="M11">
-        <v>19.7757468</v>
+        <v>21.973052</v>
       </c>
       <c r="N11">
-        <v>342.5242532</v>
+        <v>340.326948</v>
       </c>
       <c r="O11">
-        <v>70.55999615920001</v>
+        <v>70.107351288</v>
       </c>
       <c r="P11">
-        <v>271.9642570408</v>
+        <v>270.219596712</v>
       </c>
       <c r="Q11">
-        <v>459.2642570408</v>
+        <v>457.519596712</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07329300287573068</v>
+        <v>0.07354013406897941</v>
       </c>
       <c r="T11">
-        <v>0.6349423296935494</v>
+        <v>0.6406497475514875</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.32042064778055</v>
+        <v>16.48837858300249</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2616,22 +2616,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07017994066208147</v>
+        <v>0.07006881070724802</v>
       </c>
       <c r="C12">
-        <v>3929.505328009805</v>
+        <v>3898.290044605561</v>
       </c>
       <c r="D12">
-        <v>4028.345328009806</v>
+        <v>4040.814044605561</v>
       </c>
       <c r="E12">
-        <v>-945.46</v>
+        <v>-901.7760000000001</v>
       </c>
       <c r="F12">
-        <v>436.84</v>
+        <v>480.5239999999999</v>
       </c>
       <c r="G12">
         <v>338</v>
@@ -2652,28 +2652,28 @@
         <v>362.3</v>
       </c>
       <c r="M12">
-        <v>21.973052</v>
+        <v>24.17035719999999</v>
       </c>
       <c r="N12">
-        <v>340.326948</v>
+        <v>338.1296428</v>
       </c>
       <c r="O12">
-        <v>70.107351288</v>
+        <v>69.65470641680001</v>
       </c>
       <c r="P12">
-        <v>270.219596712</v>
+        <v>268.4749363832</v>
       </c>
       <c r="Q12">
-        <v>457.519596712</v>
+        <v>455.7749363832</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07354013406897941</v>
+        <v>0.07379281877218878</v>
       </c>
       <c r="T12">
-        <v>0.6406497475514875</v>
+        <v>0.6464854219905031</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.48837858300249</v>
+        <v>14.98943507545681</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2698,22 +2698,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07006881070724802</v>
+        <v>0.06995768075241456</v>
       </c>
       <c r="C13">
-        <v>3898.290044605561</v>
+        <v>3867.15218832799</v>
       </c>
       <c r="D13">
-        <v>4040.814044605561</v>
+        <v>4053.360188327989</v>
       </c>
       <c r="E13">
-        <v>-901.7760000000001</v>
+        <v>-858.092</v>
       </c>
       <c r="F13">
-        <v>480.5239999999999</v>
+        <v>524.208</v>
       </c>
       <c r="G13">
         <v>338</v>
@@ -2734,28 +2734,28 @@
         <v>362.3</v>
       </c>
       <c r="M13">
-        <v>24.17035719999999</v>
+        <v>26.3676624</v>
       </c>
       <c r="N13">
-        <v>338.1296428</v>
+        <v>335.9323376</v>
       </c>
       <c r="O13">
-        <v>69.65470641680001</v>
+        <v>69.20206154560002</v>
       </c>
       <c r="P13">
-        <v>268.4749363832</v>
+        <v>266.7302760544</v>
       </c>
       <c r="Q13">
-        <v>455.7749363832</v>
+        <v>454.0302760544</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07379281877218878</v>
+        <v>0.07405124630956199</v>
       </c>
       <c r="T13">
-        <v>0.6464854219905031</v>
+        <v>0.6524537253940415</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.98943507545681</v>
+        <v>13.74031548583541</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2780,22 +2780,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06995768075241456</v>
+        <v>0.07000138079758109</v>
       </c>
       <c r="C14">
-        <v>3867.15218832799</v>
+        <v>3818.525338483809</v>
       </c>
       <c r="D14">
-        <v>4053.360188327989</v>
+        <v>4048.417338483809</v>
       </c>
       <c r="E14">
-        <v>-858.092</v>
+        <v>-814.408</v>
       </c>
       <c r="F14">
-        <v>524.208</v>
+        <v>567.8919999999999</v>
       </c>
       <c r="G14">
         <v>338</v>
@@ -2816,45 +2816,45 @@
         <v>362.3</v>
       </c>
       <c r="M14">
-        <v>26.3676624</v>
+        <v>29.4168056</v>
       </c>
       <c r="N14">
-        <v>335.9323376</v>
+        <v>332.8831944</v>
       </c>
       <c r="O14">
-        <v>69.20206154560002</v>
+        <v>68.57393804640002</v>
       </c>
       <c r="P14">
-        <v>266.7302760544</v>
+        <v>264.3092563536</v>
       </c>
       <c r="Q14">
-        <v>454.0302760544</v>
+        <v>451.6092563536</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07405124630956199</v>
+        <v>0.07431561470986332</v>
       </c>
       <c r="T14">
-        <v>0.6524537253940415</v>
+        <v>0.6585592311746727</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.206</v>
       </c>
       <c r="W14">
-        <v>0.0399382</v>
+        <v>0.0411292</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.74031548583541</v>
+        <v>12.31608914055577</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2862,22 +2862,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07000138079758109</v>
+        <v>0.06990216084274764</v>
       </c>
       <c r="C15">
-        <v>3818.525338483809</v>
+        <v>3786.081401437429</v>
       </c>
       <c r="D15">
-        <v>4048.417338483809</v>
+        <v>4059.65740143743</v>
       </c>
       <c r="E15">
-        <v>-814.408</v>
+        <v>-770.7239999999999</v>
       </c>
       <c r="F15">
-        <v>567.8919999999999</v>
+        <v>611.576</v>
       </c>
       <c r="G15">
         <v>338</v>
@@ -2898,28 +2898,28 @@
         <v>362.3</v>
       </c>
       <c r="M15">
-        <v>29.4168056</v>
+        <v>31.6796368</v>
       </c>
       <c r="N15">
-        <v>332.8831944</v>
+        <v>330.6203632</v>
       </c>
       <c r="O15">
-        <v>68.57393804640002</v>
+        <v>68.10779481920001</v>
       </c>
       <c r="P15">
-        <v>264.3092563536</v>
+        <v>262.5125683808</v>
       </c>
       <c r="Q15">
-        <v>451.6092563536</v>
+        <v>449.8125683808</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07431561470986332</v>
+        <v>0.07458613121249726</v>
       </c>
       <c r="T15">
-        <v>0.6585592311746727</v>
+        <v>0.6648067254618304</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.31608914055577</v>
+        <v>11.43636848765892</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2944,22 +2944,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06990216084274764</v>
+        <v>0.06980294088791417</v>
       </c>
       <c r="C16">
-        <v>3786.081401437429</v>
+        <v>3753.700052187713</v>
       </c>
       <c r="D16">
-        <v>4059.65740143743</v>
+        <v>4070.960052187713</v>
       </c>
       <c r="E16">
-        <v>-770.7239999999999</v>
+        <v>-727.04</v>
       </c>
       <c r="F16">
-        <v>611.576</v>
+        <v>655.26</v>
       </c>
       <c r="G16">
         <v>338</v>
@@ -2980,28 +2980,28 @@
         <v>362.3</v>
       </c>
       <c r="M16">
-        <v>31.6796368</v>
+        <v>33.942468</v>
       </c>
       <c r="N16">
-        <v>330.6203632</v>
+        <v>328.357532</v>
       </c>
       <c r="O16">
-        <v>68.10779481920001</v>
+        <v>67.641651592</v>
       </c>
       <c r="P16">
-        <v>262.5125683808</v>
+        <v>260.715880408</v>
       </c>
       <c r="Q16">
-        <v>449.8125683808</v>
+        <v>448.015880408</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07458613121249726</v>
+        <v>0.07486301280931079</v>
       </c>
       <c r="T16">
-        <v>0.6648067254618304</v>
+        <v>0.6712012196145682</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.43636848765892</v>
+        <v>10.673943921815</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3026,22 +3026,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06980294088791417</v>
+        <v>0.06970372093308072</v>
       </c>
       <c r="C17">
-        <v>3753.700052187713</v>
+        <v>3721.381814953541</v>
       </c>
       <c r="D17">
-        <v>4070.960052187713</v>
+        <v>4082.325814953542</v>
       </c>
       <c r="E17">
-        <v>-727.0400000000001</v>
+        <v>-683.356</v>
       </c>
       <c r="F17">
-        <v>655.2599999999999</v>
+        <v>698.944</v>
       </c>
       <c r="G17">
         <v>338</v>
@@ -3062,28 +3062,28 @@
         <v>362.3</v>
       </c>
       <c r="M17">
-        <v>33.94246799999999</v>
+        <v>36.2052992</v>
       </c>
       <c r="N17">
-        <v>328.357532</v>
+        <v>326.0947008</v>
       </c>
       <c r="O17">
-        <v>67.641651592</v>
+        <v>67.17550836480001</v>
       </c>
       <c r="P17">
-        <v>260.715880408</v>
+        <v>258.9191924352</v>
       </c>
       <c r="Q17">
-        <v>448.015880408</v>
+        <v>446.2191924352</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07486301280931079</v>
+        <v>0.0751464868250961</v>
       </c>
       <c r="T17">
-        <v>0.6712012196145682</v>
+        <v>0.6777479636280855</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.673943921815</v>
+        <v>10.00682242670156</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3108,22 +3108,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06970372093308072</v>
+        <v>0.06983396697824726</v>
       </c>
       <c r="C18">
-        <v>3721.381814953541</v>
+        <v>3662.790954894001</v>
       </c>
       <c r="D18">
-        <v>4082.325814953542</v>
+        <v>4067.418954894002</v>
       </c>
       <c r="E18">
-        <v>-683.356</v>
+        <v>-639.6719999999999</v>
       </c>
       <c r="F18">
-        <v>698.944</v>
+        <v>742.628</v>
       </c>
       <c r="G18">
         <v>338</v>
@@ -3144,45 +3144,45 @@
         <v>362.3</v>
       </c>
       <c r="M18">
-        <v>36.2052992</v>
+        <v>39.730598</v>
       </c>
       <c r="N18">
-        <v>326.0947008</v>
+        <v>322.569402</v>
       </c>
       <c r="O18">
-        <v>67.17550836480001</v>
+        <v>66.44929681200001</v>
       </c>
       <c r="P18">
-        <v>258.9191924352</v>
+        <v>256.120105188</v>
       </c>
       <c r="Q18">
-        <v>446.2191924352</v>
+        <v>443.420105188</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0751464868250961</v>
+        <v>0.07543679154005695</v>
       </c>
       <c r="T18">
-        <v>0.6777479636280855</v>
+        <v>0.6844524605093985</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.206</v>
       </c>
       <c r="W18">
-        <v>0.0411292</v>
+        <v>0.042479</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.00682242670156</v>
+        <v>9.118916357614351</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3190,22 +3190,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06983396697824726</v>
+        <v>0.0697482450234138</v>
       </c>
       <c r="C19">
-        <v>3662.790954894001</v>
+        <v>3628.905688074599</v>
       </c>
       <c r="D19">
-        <v>4067.418954894002</v>
+        <v>4077.217688074599</v>
       </c>
       <c r="E19">
-        <v>-639.6719999999999</v>
+        <v>-595.9879999999999</v>
       </c>
       <c r="F19">
-        <v>742.628</v>
+        <v>786.312</v>
       </c>
       <c r="G19">
         <v>338</v>
@@ -3226,28 +3226,28 @@
         <v>362.3</v>
       </c>
       <c r="M19">
-        <v>39.730598</v>
+        <v>42.067692</v>
       </c>
       <c r="N19">
-        <v>322.569402</v>
+        <v>320.232308</v>
       </c>
       <c r="O19">
-        <v>66.44929681200001</v>
+        <v>65.96785544800001</v>
       </c>
       <c r="P19">
-        <v>256.120105188</v>
+        <v>254.264452552</v>
       </c>
       <c r="Q19">
-        <v>443.420105188</v>
+        <v>441.564452552</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07543679154005695</v>
+        <v>0.07573417685782172</v>
       </c>
       <c r="T19">
-        <v>0.6844524605093985</v>
+        <v>0.6913204817048897</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.118916357614351</v>
+        <v>8.612309893302442</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3272,22 +3272,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06974824502341381</v>
+        <v>0.06966252306858035</v>
       </c>
       <c r="C20">
-        <v>3628.905688074597</v>
+        <v>3595.067747109611</v>
       </c>
       <c r="D20">
-        <v>4077.217688074597</v>
+        <v>4087.063747109612</v>
       </c>
       <c r="E20">
-        <v>-595.9880000000001</v>
+        <v>-552.304</v>
       </c>
       <c r="F20">
-        <v>786.3119999999999</v>
+        <v>829.996</v>
       </c>
       <c r="G20">
         <v>338</v>
@@ -3308,28 +3308,28 @@
         <v>362.3</v>
       </c>
       <c r="M20">
-        <v>42.06769199999999</v>
+        <v>44.404786</v>
       </c>
       <c r="N20">
-        <v>320.232308</v>
+        <v>317.895214</v>
       </c>
       <c r="O20">
-        <v>65.96785544800001</v>
+        <v>65.486414084</v>
       </c>
       <c r="P20">
-        <v>254.264452552</v>
+        <v>252.408799916</v>
       </c>
       <c r="Q20">
-        <v>441.564452552</v>
+        <v>439.708799916</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07573417685782172</v>
+        <v>0.07603890502293871</v>
       </c>
       <c r="T20">
-        <v>0.6913204817048897</v>
+        <v>0.69835808367064</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.612309893302443</v>
+        <v>8.159030425233894</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3354,22 +3354,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06966252306858035</v>
+        <v>0.06957680111374691</v>
       </c>
       <c r="C21">
-        <v>3595.067747109611</v>
+        <v>3561.27747569015</v>
       </c>
       <c r="D21">
-        <v>4087.063747109612</v>
+        <v>4096.95747569015</v>
       </c>
       <c r="E21">
-        <v>-552.304</v>
+        <v>-508.62</v>
       </c>
       <c r="F21">
-        <v>829.996</v>
+        <v>873.6799999999999</v>
       </c>
       <c r="G21">
         <v>338</v>
@@ -3390,28 +3390,28 @@
         <v>362.3</v>
       </c>
       <c r="M21">
-        <v>44.404786</v>
+        <v>46.74187999999999</v>
       </c>
       <c r="N21">
-        <v>317.895214</v>
+        <v>315.55812</v>
       </c>
       <c r="O21">
-        <v>65.486414084</v>
+        <v>65.00497272000001</v>
       </c>
       <c r="P21">
-        <v>252.408799916</v>
+        <v>250.55314728</v>
       </c>
       <c r="Q21">
-        <v>439.708799916</v>
+        <v>437.85314728</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07603890502293871</v>
+        <v>0.07635125139218363</v>
       </c>
       <c r="T21">
-        <v>0.69835808367064</v>
+        <v>0.7055716256855341</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.159030425233894</v>
+        <v>7.751078903972199</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3436,22 +3436,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06957680111374691</v>
+        <v>0.06962447115891343</v>
       </c>
       <c r="C22">
-        <v>3561.27747569015</v>
+        <v>3512.085661383654</v>
       </c>
       <c r="D22">
-        <v>4096.95747569015</v>
+        <v>4091.449661383654</v>
       </c>
       <c r="E22">
-        <v>-508.62</v>
+        <v>-464.9359999999999</v>
       </c>
       <c r="F22">
-        <v>873.6799999999999</v>
+        <v>917.364</v>
       </c>
       <c r="G22">
         <v>338</v>
@@ -3472,45 +3472,45 @@
         <v>362.3</v>
       </c>
       <c r="M22">
-        <v>46.74187999999999</v>
+        <v>49.8128652</v>
       </c>
       <c r="N22">
-        <v>315.55812</v>
+        <v>312.4871348</v>
       </c>
       <c r="O22">
-        <v>65.00497272000001</v>
+        <v>64.37234976880001</v>
       </c>
       <c r="P22">
-        <v>250.55314728</v>
+        <v>248.1147850312</v>
       </c>
       <c r="Q22">
-        <v>437.85314728</v>
+        <v>435.4147850312</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07635125139218363</v>
+        <v>0.07667150526444738</v>
       </c>
       <c r="T22">
-        <v>0.7055716256855341</v>
+        <v>0.7129677890172609</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.206</v>
       </c>
       <c r="W22">
-        <v>0.042479</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.751078903972199</v>
+        <v>7.273221456853681</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3518,22 +3518,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06962447115891343</v>
+        <v>0.06954510120407999</v>
       </c>
       <c r="C23">
-        <v>3512.085661383654</v>
+        <v>3477.580311372068</v>
       </c>
       <c r="D23">
-        <v>4091.449661383654</v>
+        <v>4100.628311372067</v>
       </c>
       <c r="E23">
-        <v>-464.936</v>
+        <v>-421.2520000000001</v>
       </c>
       <c r="F23">
-        <v>917.3639999999999</v>
+        <v>961.0479999999999</v>
       </c>
       <c r="G23">
         <v>338</v>
@@ -3554,28 +3554,28 @@
         <v>362.3</v>
       </c>
       <c r="M23">
-        <v>49.8128652</v>
+        <v>52.1849064</v>
       </c>
       <c r="N23">
-        <v>312.4871348</v>
+        <v>310.1150936</v>
       </c>
       <c r="O23">
-        <v>64.37234976880001</v>
+        <v>63.88370928160001</v>
       </c>
       <c r="P23">
-        <v>248.1147850312</v>
+        <v>246.2313843184</v>
       </c>
       <c r="Q23">
-        <v>435.4147850312</v>
+        <v>433.5313843184</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07667150526444738</v>
+        <v>0.07699997077446151</v>
       </c>
       <c r="T23">
-        <v>0.7129677890172609</v>
+        <v>0.7205535975626216</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.273221456853681</v>
+        <v>6.942620481542151</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3600,22 +3600,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06954510120407999</v>
+        <v>0.06946573124924653</v>
       </c>
       <c r="C24">
-        <v>3477.580311372068</v>
+        <v>3443.11623623683</v>
       </c>
       <c r="D24">
-        <v>4100.628311372067</v>
+        <v>4109.84823623683</v>
       </c>
       <c r="E24">
-        <v>-421.2520000000001</v>
+        <v>-377.568</v>
       </c>
       <c r="F24">
-        <v>961.0479999999999</v>
+        <v>1004.732</v>
       </c>
       <c r="G24">
         <v>338</v>
@@ -3636,28 +3636,28 @@
         <v>362.3</v>
       </c>
       <c r="M24">
-        <v>52.1849064</v>
+        <v>54.5569476</v>
       </c>
       <c r="N24">
-        <v>310.1150936</v>
+        <v>307.7430524</v>
       </c>
       <c r="O24">
-        <v>63.88370928160001</v>
+        <v>63.3950687944</v>
       </c>
       <c r="P24">
-        <v>246.2313843184</v>
+        <v>244.3479836056</v>
       </c>
       <c r="Q24">
-        <v>433.5313843184</v>
+        <v>431.6479836056</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07699997077446151</v>
+        <v>0.07733696785616431</v>
       </c>
       <c r="T24">
-        <v>0.7205535975626216</v>
+        <v>0.7283364400961737</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.942620481542151</v>
+        <v>6.640767417127273</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3682,22 +3682,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06946573124924653</v>
+        <v>0.06938636129441307</v>
       </c>
       <c r="C25">
-        <v>3443.11623623683</v>
+        <v>3408.69371501481</v>
       </c>
       <c r="D25">
-        <v>4109.84823623683</v>
+        <v>4119.10971501481</v>
       </c>
       <c r="E25">
-        <v>-377.568</v>
+        <v>-333.884</v>
       </c>
       <c r="F25">
-        <v>1004.732</v>
+        <v>1048.416</v>
       </c>
       <c r="G25">
         <v>338</v>
@@ -3718,28 +3718,28 @@
         <v>362.3</v>
       </c>
       <c r="M25">
-        <v>54.5569476</v>
+        <v>56.9289888</v>
       </c>
       <c r="N25">
-        <v>307.7430524</v>
+        <v>305.3710112</v>
       </c>
       <c r="O25">
-        <v>63.3950687944</v>
+        <v>62.9064283072</v>
       </c>
       <c r="P25">
-        <v>244.3479836056</v>
+        <v>242.4645828928</v>
       </c>
       <c r="Q25">
-        <v>431.6479836056</v>
+        <v>429.7645828928</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07733696785616431</v>
+        <v>0.07768283328212246</v>
       </c>
       <c r="T25">
-        <v>0.7283364400961737</v>
+        <v>0.7363240942753455</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.640767417127273</v>
+        <v>6.36406877474697</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3764,22 +3764,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06938636129441307</v>
+        <v>0.06950549133957962</v>
       </c>
       <c r="C26">
-        <v>3408.69371501481</v>
+        <v>3351.124371682802</v>
       </c>
       <c r="D26">
-        <v>4119.10971501481</v>
+        <v>4105.224371682802</v>
       </c>
       <c r="E26">
-        <v>-333.884</v>
+        <v>-290.2</v>
       </c>
       <c r="F26">
-        <v>1048.416</v>
+        <v>1092.1</v>
       </c>
       <c r="G26">
         <v>338</v>
@@ -3800,45 +3800,45 @@
         <v>362.3</v>
       </c>
       <c r="M26">
-        <v>56.9289888</v>
+        <v>60.39313</v>
       </c>
       <c r="N26">
-        <v>305.3710112</v>
+        <v>301.90687</v>
       </c>
       <c r="O26">
-        <v>62.9064283072</v>
+        <v>62.19281522000001</v>
       </c>
       <c r="P26">
-        <v>242.4645828928</v>
+        <v>239.71405478</v>
       </c>
       <c r="Q26">
-        <v>429.7645828928</v>
+        <v>427.01405478</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07768283328212246</v>
+        <v>0.07803792178610615</v>
       </c>
       <c r="T26">
-        <v>0.7363240942753455</v>
+        <v>0.744524752565962</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.206</v>
       </c>
       <c r="W26">
-        <v>0.04311420000000001</v>
+        <v>0.0439082</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.36406877474697</v>
+        <v>5.999026710488429</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3846,22 +3846,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06950549133957962</v>
+        <v>0.06943406138474616</v>
       </c>
       <c r="C27">
-        <v>3351.124371682802</v>
+        <v>3315.754714376753</v>
       </c>
       <c r="D27">
-        <v>4105.224371682802</v>
+        <v>4113.538714376753</v>
       </c>
       <c r="E27">
-        <v>-290.2</v>
+        <v>-246.5160000000001</v>
       </c>
       <c r="F27">
-        <v>1092.1</v>
+        <v>1135.784</v>
       </c>
       <c r="G27">
         <v>338</v>
@@ -3882,28 +3882,28 @@
         <v>362.3</v>
       </c>
       <c r="M27">
-        <v>60.39313</v>
+        <v>62.8088552</v>
       </c>
       <c r="N27">
-        <v>301.90687</v>
+        <v>299.4911448</v>
       </c>
       <c r="O27">
-        <v>62.19281522000001</v>
+        <v>61.69517582880001</v>
       </c>
       <c r="P27">
-        <v>239.71405478</v>
+        <v>237.7959689712</v>
       </c>
       <c r="Q27">
-        <v>427.01405478</v>
+        <v>425.0959689712</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07803792178610615</v>
+        <v>0.07840260727668399</v>
       </c>
       <c r="T27">
-        <v>0.744524752565962</v>
+        <v>0.7529470502698383</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.999026710488429</v>
+        <v>5.768294913931181</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3928,22 +3928,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06943406138474616</v>
+        <v>0.0693626314299127</v>
       </c>
       <c r="C28">
-        <v>3315.754714376753</v>
+        <v>3280.41880362308</v>
       </c>
       <c r="D28">
-        <v>4113.538714376753</v>
+        <v>4121.88680362308</v>
       </c>
       <c r="E28">
-        <v>-246.5160000000001</v>
+        <v>-202.8319999999999</v>
       </c>
       <c r="F28">
-        <v>1135.784</v>
+        <v>1179.468</v>
       </c>
       <c r="G28">
         <v>338</v>
@@ -3964,28 +3964,28 @@
         <v>362.3</v>
       </c>
       <c r="M28">
-        <v>62.8088552</v>
+        <v>65.22458040000001</v>
       </c>
       <c r="N28">
-        <v>299.4911448</v>
+        <v>297.0754196</v>
       </c>
       <c r="O28">
-        <v>61.69517582880001</v>
+        <v>61.19753643760001</v>
       </c>
       <c r="P28">
-        <v>237.7959689712</v>
+        <v>235.8778831624</v>
       </c>
       <c r="Q28">
-        <v>425.0959689712</v>
+        <v>423.1778831624</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07840260727668399</v>
+        <v>0.07877728415056534</v>
       </c>
       <c r="T28">
-        <v>0.7529470502698383</v>
+        <v>0.7616000958560125</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.768294913931181</v>
+        <v>5.554654361563359</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4010,22 +4010,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0693626314299127</v>
+        <v>0.06929120147507925</v>
       </c>
       <c r="C29">
-        <v>3280.41880362308</v>
+        <v>3245.116845297161</v>
       </c>
       <c r="D29">
-        <v>4121.88680362308</v>
+        <v>4130.268845297162</v>
       </c>
       <c r="E29">
-        <v>-202.8319999999999</v>
+        <v>-159.1479999999999</v>
       </c>
       <c r="F29">
-        <v>1179.468</v>
+        <v>1223.152</v>
       </c>
       <c r="G29">
         <v>338</v>
@@ -4046,28 +4046,28 @@
         <v>362.3</v>
       </c>
       <c r="M29">
-        <v>65.22458040000001</v>
+        <v>67.6403056</v>
       </c>
       <c r="N29">
-        <v>297.0754196</v>
+        <v>294.6596944</v>
       </c>
       <c r="O29">
-        <v>61.19753643760001</v>
+        <v>60.69989704640001</v>
       </c>
       <c r="P29">
-        <v>235.8778831624</v>
+        <v>233.9597973536</v>
       </c>
       <c r="Q29">
-        <v>423.1778831624</v>
+        <v>421.2597973536</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07877728415056534</v>
+        <v>0.07916236871538784</v>
       </c>
       <c r="T29">
-        <v>0.7616000958560125</v>
+        <v>0.7704935038195806</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.554654361563359</v>
+        <v>5.356273848650383</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4092,22 +4092,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06929120147507925</v>
+        <v>0.06921977152024578</v>
       </c>
       <c r="C30">
-        <v>3245.116845297161</v>
+        <v>3209.849046952427</v>
       </c>
       <c r="D30">
-        <v>4130.268845297162</v>
+        <v>4138.685046952427</v>
       </c>
       <c r="E30">
-        <v>-159.1479999999999</v>
+        <v>-115.4639999999999</v>
       </c>
       <c r="F30">
-        <v>1223.152</v>
+        <v>1266.836</v>
       </c>
       <c r="G30">
         <v>338</v>
@@ -4128,28 +4128,28 @@
         <v>362.3</v>
       </c>
       <c r="M30">
-        <v>67.6403056</v>
+        <v>70.0560308</v>
       </c>
       <c r="N30">
-        <v>294.6596944</v>
+        <v>292.2439692</v>
       </c>
       <c r="O30">
-        <v>60.69989704640001</v>
+        <v>60.20225765520001</v>
       </c>
       <c r="P30">
-        <v>233.9597973536</v>
+        <v>232.0417115448</v>
       </c>
       <c r="Q30">
-        <v>421.2597973536</v>
+        <v>419.3417115448</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07916236871538784</v>
+        <v>0.07955830073274053</v>
       </c>
       <c r="T30">
-        <v>0.7704935038195806</v>
+        <v>0.7796374303173336</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.356273848650383</v>
+        <v>5.171574750421059</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4174,22 +4174,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06921977152024578</v>
+        <v>0.06914834156541232</v>
       </c>
       <c r="C31">
-        <v>3209.849046952427</v>
+        <v>3174.615617837465</v>
       </c>
       <c r="D31">
-        <v>4138.685046952427</v>
+        <v>4147.135617837464</v>
       </c>
       <c r="E31">
-        <v>-115.4640000000002</v>
+        <v>-71.7800000000002</v>
       </c>
       <c r="F31">
-        <v>1266.836</v>
+        <v>1310.52</v>
       </c>
       <c r="G31">
         <v>338</v>
@@ -4210,28 +4210,28 @@
         <v>362.3</v>
       </c>
       <c r="M31">
-        <v>70.05603079999999</v>
+        <v>72.47175599999998</v>
       </c>
       <c r="N31">
-        <v>292.2439692</v>
+        <v>289.828244</v>
       </c>
       <c r="O31">
-        <v>60.20225765520001</v>
+        <v>59.70461826400001</v>
       </c>
       <c r="P31">
-        <v>232.0417115448</v>
+        <v>230.123625736</v>
       </c>
       <c r="Q31">
-        <v>419.3417115448</v>
+        <v>417.4236257360001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07955830073274053</v>
+        <v>0.07996554509344617</v>
       </c>
       <c r="T31">
-        <v>0.7796374303173336</v>
+        <v>0.7890426118578795</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.17157475042106</v>
+        <v>4.999188925407025</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4256,22 +4256,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06914834156541232</v>
+        <v>0.06907691161057887</v>
       </c>
       <c r="C32">
-        <v>3174.615617837465</v>
+        <v>3139.416768913382</v>
       </c>
       <c r="D32">
-        <v>4147.135617837464</v>
+        <v>4155.620768913382</v>
       </c>
       <c r="E32">
-        <v>-71.7800000000002</v>
+        <v>-28.096</v>
       </c>
       <c r="F32">
-        <v>1310.52</v>
+        <v>1354.204</v>
       </c>
       <c r="G32">
         <v>338</v>
@@ -4292,28 +4292,28 @@
         <v>362.3</v>
       </c>
       <c r="M32">
-        <v>72.47175599999998</v>
+        <v>74.8874812</v>
       </c>
       <c r="N32">
-        <v>289.828244</v>
+        <v>287.4125188</v>
       </c>
       <c r="O32">
-        <v>59.70461826400001</v>
+        <v>59.20697887280001</v>
       </c>
       <c r="P32">
-        <v>230.123625736</v>
+        <v>228.2055399272</v>
       </c>
       <c r="Q32">
-        <v>417.4236257360001</v>
+        <v>415.5055399272001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07996554509344617</v>
+        <v>0.0803845936385201</v>
       </c>
       <c r="T32">
-        <v>0.7890426118578795</v>
+        <v>0.7987204073561225</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.999188925407025</v>
+        <v>4.837924766522926</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4338,22 +4338,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06907691161057887</v>
+        <v>0.06900548165574541</v>
       </c>
       <c r="C33">
-        <v>3139.416768913382</v>
+        <v>3104.252712871356</v>
       </c>
       <c r="D33">
-        <v>4155.620768913382</v>
+        <v>4164.140712871356</v>
       </c>
       <c r="E33">
-        <v>-28.096</v>
+        <v>15.58799999999997</v>
       </c>
       <c r="F33">
-        <v>1354.204</v>
+        <v>1397.888</v>
       </c>
       <c r="G33">
         <v>338</v>
@@ -4374,28 +4374,28 @@
         <v>362.3</v>
       </c>
       <c r="M33">
-        <v>74.8874812</v>
+        <v>77.30320639999999</v>
       </c>
       <c r="N33">
-        <v>287.4125188</v>
+        <v>284.9967936</v>
       </c>
       <c r="O33">
-        <v>59.20697887280001</v>
+        <v>58.70933948160001</v>
       </c>
       <c r="P33">
-        <v>228.2055399272</v>
+        <v>226.2874541184</v>
       </c>
       <c r="Q33">
-        <v>415.5055399272001</v>
+        <v>413.5874541184</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0803845936385201</v>
+        <v>0.08081596714080208</v>
       </c>
       <c r="T33">
-        <v>0.7987204073561225</v>
+        <v>0.8086828438984315</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.837924766522926</v>
+        <v>4.686739617569085</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4420,22 +4420,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06900548165574541</v>
+        <v>0.06893405170091195</v>
       </c>
       <c r="C34">
-        <v>3104.252712871356</v>
+        <v>3069.123664150402</v>
       </c>
       <c r="D34">
-        <v>4164.140712871356</v>
+        <v>4172.695664150402</v>
       </c>
       <c r="E34">
-        <v>15.58799999999997</v>
+        <v>59.27199999999993</v>
       </c>
       <c r="F34">
-        <v>1397.888</v>
+        <v>1441.572</v>
       </c>
       <c r="G34">
         <v>338</v>
@@ -4456,28 +4456,28 @@
         <v>362.3</v>
       </c>
       <c r="M34">
-        <v>77.30320639999999</v>
+        <v>79.71893159999999</v>
       </c>
       <c r="N34">
-        <v>284.9967936</v>
+        <v>282.5810684</v>
       </c>
       <c r="O34">
-        <v>58.70933948160001</v>
+        <v>58.21170009040002</v>
       </c>
       <c r="P34">
-        <v>226.2874541184</v>
+        <v>224.3693683096</v>
       </c>
       <c r="Q34">
-        <v>413.5874541184</v>
+        <v>411.6693683096</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08081596714080208</v>
+        <v>0.08126021746404768</v>
       </c>
       <c r="T34">
-        <v>0.8086828438984315</v>
+        <v>0.8189426666061824</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.686739617569085</v>
+        <v>4.544717204915477</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4502,22 +4502,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06893405170091195</v>
+        <v>0.0695375217460785</v>
       </c>
       <c r="C35">
-        <v>3069.123664150402</v>
+        <v>2954.250983943923</v>
       </c>
       <c r="D35">
-        <v>4172.695664150402</v>
+        <v>4101.506983943923</v>
       </c>
       <c r="E35">
-        <v>59.27199999999993</v>
+        <v>102.9560000000001</v>
       </c>
       <c r="F35">
-        <v>1441.572</v>
+        <v>1485.256</v>
       </c>
       <c r="G35">
         <v>338</v>
@@ -4538,45 +4538,45 @@
         <v>362.3</v>
       </c>
       <c r="M35">
-        <v>79.71893159999999</v>
+        <v>85.84779680000001</v>
       </c>
       <c r="N35">
-        <v>282.5810684</v>
+        <v>276.4522032</v>
       </c>
       <c r="O35">
-        <v>58.21170009040002</v>
+        <v>56.9491538592</v>
       </c>
       <c r="P35">
-        <v>224.3693683096</v>
+        <v>219.5030493408</v>
       </c>
       <c r="Q35">
-        <v>411.6693683096</v>
+        <v>406.8030493408</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08126021746404768</v>
+        <v>0.08171792991830075</v>
       </c>
       <c r="T35">
-        <v>0.8189426666061824</v>
+        <v>0.8295133930323501</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.206</v>
       </c>
       <c r="W35">
-        <v>0.0439082</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.544717204915477</v>
+        <v>4.22025973297896</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4584,22 +4584,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0695375217460785</v>
+        <v>0.06948594179124505</v>
       </c>
       <c r="C36">
-        <v>2954.250983943923</v>
+        <v>2916.556568220581</v>
       </c>
       <c r="D36">
-        <v>4101.506983943923</v>
+        <v>4107.496568220581</v>
       </c>
       <c r="E36">
-        <v>102.9560000000001</v>
+        <v>146.6400000000001</v>
       </c>
       <c r="F36">
-        <v>1485.256</v>
+        <v>1528.94</v>
       </c>
       <c r="G36">
         <v>338</v>
@@ -4620,28 +4620,28 @@
         <v>362.3</v>
       </c>
       <c r="M36">
-        <v>85.84779680000001</v>
+        <v>88.37273200000001</v>
       </c>
       <c r="N36">
-        <v>276.4522032</v>
+        <v>273.927268</v>
       </c>
       <c r="O36">
-        <v>56.9491538592</v>
+        <v>56.42901720800001</v>
       </c>
       <c r="P36">
-        <v>219.5030493408</v>
+        <v>217.498250792</v>
       </c>
       <c r="Q36">
-        <v>406.8030493408</v>
+        <v>404.798250792</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08171792991830075</v>
+        <v>0.08218972583268469</v>
       </c>
       <c r="T36">
-        <v>0.8295133930323501</v>
+        <v>0.840409372579323</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.22025973297896</v>
+        <v>4.099680883465275</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4666,22 +4666,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06948594179124505</v>
+        <v>0.07043480183641158</v>
       </c>
       <c r="C37">
-        <v>2916.556568220581</v>
+        <v>2765.414603801488</v>
       </c>
       <c r="D37">
-        <v>4107.496568220581</v>
+        <v>4000.038603801488</v>
       </c>
       <c r="E37">
-        <v>146.6400000000001</v>
+        <v>190.3240000000001</v>
       </c>
       <c r="F37">
-        <v>1528.94</v>
+        <v>1572.624</v>
       </c>
       <c r="G37">
         <v>338</v>
@@ -4702,45 +4702,45 @@
         <v>362.3</v>
       </c>
       <c r="M37">
-        <v>88.37273200000001</v>
+        <v>96.4018512</v>
       </c>
       <c r="N37">
-        <v>273.927268</v>
+        <v>265.8981488</v>
       </c>
       <c r="O37">
-        <v>56.42901720800001</v>
+        <v>54.77501865280001</v>
       </c>
       <c r="P37">
-        <v>217.498250792</v>
+        <v>211.1231301472</v>
       </c>
       <c r="Q37">
-        <v>404.798250792</v>
+        <v>398.4231301472</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08218972583268469</v>
+        <v>0.0826762653693931</v>
       </c>
       <c r="T37">
-        <v>0.840409372579323</v>
+        <v>0.8516458514871387</v>
       </c>
       <c r="U37">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.206</v>
       </c>
       <c r="W37">
-        <v>0.04589320000000001</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.099680883465275</v>
+        <v>3.758226584760854</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4748,22 +4748,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07043480183641158</v>
+        <v>0.07041101188157814</v>
       </c>
       <c r="C38">
-        <v>2765.414603801488</v>
+        <v>2724.3560431985</v>
       </c>
       <c r="D38">
-        <v>4000.038603801488</v>
+        <v>4002.6640431985</v>
       </c>
       <c r="E38">
-        <v>190.3239999999998</v>
+        <v>234.0079999999998</v>
       </c>
       <c r="F38">
-        <v>1572.624</v>
+        <v>1616.308</v>
       </c>
       <c r="G38">
         <v>338</v>
@@ -4784,28 +4784,28 @@
         <v>362.3</v>
       </c>
       <c r="M38">
-        <v>96.40185119999998</v>
+        <v>99.07968039999999</v>
       </c>
       <c r="N38">
-        <v>265.8981488000001</v>
+        <v>263.2203196</v>
       </c>
       <c r="O38">
-        <v>54.77501865280001</v>
+        <v>54.22338583760001</v>
       </c>
       <c r="P38">
-        <v>211.1231301472</v>
+        <v>208.9969337624</v>
       </c>
       <c r="Q38">
-        <v>398.4231301472</v>
+        <v>396.2969337624</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0826762653693931</v>
+        <v>0.08317825060567957</v>
       </c>
       <c r="T38">
-        <v>0.8516458514871387</v>
+        <v>0.8632390440110755</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.758226584760855</v>
+        <v>3.656652893280831</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4830,22 +4830,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07041101188157814</v>
+        <v>0.07038722192674468</v>
       </c>
       <c r="C39">
-        <v>2724.3560431985</v>
+        <v>2683.300931291829</v>
       </c>
       <c r="D39">
-        <v>4002.6640431985</v>
+        <v>4005.29293129183</v>
       </c>
       <c r="E39">
-        <v>234.0079999999998</v>
+        <v>277.692</v>
       </c>
       <c r="F39">
-        <v>1616.308</v>
+        <v>1659.992</v>
       </c>
       <c r="G39">
         <v>338</v>
@@ -4866,28 +4866,28 @@
         <v>362.3</v>
       </c>
       <c r="M39">
-        <v>99.07968039999999</v>
+        <v>101.7575096</v>
       </c>
       <c r="N39">
-        <v>263.2203196</v>
+        <v>260.5424904</v>
       </c>
       <c r="O39">
-        <v>54.22338583760001</v>
+        <v>53.67175302240001</v>
       </c>
       <c r="P39">
-        <v>208.9969337624</v>
+        <v>206.8707373776</v>
       </c>
       <c r="Q39">
-        <v>396.2969337624</v>
+        <v>394.1707373776</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08317825060567957</v>
+        <v>0.08369642891410431</v>
       </c>
       <c r="T39">
-        <v>0.8632390440110755</v>
+        <v>0.8752062104873976</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.656652893280831</v>
+        <v>3.560425185562914</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4912,22 +4912,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07038722192674468</v>
+        <v>0.07123047997191122</v>
       </c>
       <c r="C40">
-        <v>2683.300931291829</v>
+        <v>2548.493623245473</v>
       </c>
       <c r="D40">
-        <v>4005.29293129183</v>
+        <v>3914.169623245473</v>
       </c>
       <c r="E40">
-        <v>277.692</v>
+        <v>321.376</v>
       </c>
       <c r="F40">
-        <v>1659.992</v>
+        <v>1703.676</v>
       </c>
       <c r="G40">
         <v>338</v>
@@ -4948,45 +4948,45 @@
         <v>362.3</v>
       </c>
       <c r="M40">
-        <v>101.7575096</v>
+        <v>109.2056316</v>
       </c>
       <c r="N40">
-        <v>260.5424904</v>
+        <v>253.0943684</v>
       </c>
       <c r="O40">
-        <v>53.67175302240001</v>
+        <v>52.1374398904</v>
       </c>
       <c r="P40">
-        <v>206.8707373776</v>
+        <v>200.9569285096</v>
       </c>
       <c r="Q40">
-        <v>394.1707373776</v>
+        <v>388.2569285096</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08369642891410431</v>
+        <v>0.08423159667526428</v>
       </c>
       <c r="T40">
-        <v>0.8752062104873976</v>
+        <v>0.8875657430776973</v>
       </c>
       <c r="U40">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.206</v>
       </c>
       <c r="W40">
-        <v>0.04867220000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.560425185562914</v>
+        <v>3.317594474679088</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4994,22 +4994,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07123047997191122</v>
+        <v>0.07122892201707776</v>
       </c>
       <c r="C41">
-        <v>2548.493623245473</v>
+        <v>2504.974154140503</v>
       </c>
       <c r="D41">
-        <v>3914.169623245473</v>
+        <v>3914.334154140503</v>
       </c>
       <c r="E41">
-        <v>321.376</v>
+        <v>365.0599999999999</v>
       </c>
       <c r="F41">
-        <v>1703.676</v>
+        <v>1747.36</v>
       </c>
       <c r="G41">
         <v>338</v>
@@ -5030,28 +5030,28 @@
         <v>362.3</v>
       </c>
       <c r="M41">
-        <v>109.2056316</v>
+        <v>112.005776</v>
       </c>
       <c r="N41">
-        <v>253.0943684</v>
+        <v>250.294224</v>
       </c>
       <c r="O41">
-        <v>52.1374398904</v>
+        <v>51.56061014400001</v>
       </c>
       <c r="P41">
-        <v>200.9569285096</v>
+        <v>198.733613856</v>
       </c>
       <c r="Q41">
-        <v>388.2569285096</v>
+        <v>386.033613856</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08423159667526428</v>
+        <v>0.08478460336179626</v>
       </c>
       <c r="T41">
-        <v>0.8875657430776973</v>
+        <v>0.9003372600876736</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.317594474679088</v>
+        <v>3.234654612812111</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5076,22 +5076,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07122892201707776</v>
+        <v>0.07122736406224431</v>
       </c>
       <c r="C42">
-        <v>2504.974154140503</v>
+        <v>2461.454698868123</v>
       </c>
       <c r="D42">
-        <v>3914.334154140503</v>
+        <v>3914.498698868123</v>
       </c>
       <c r="E42">
-        <v>365.0599999999999</v>
+        <v>408.7440000000001</v>
       </c>
       <c r="F42">
-        <v>1747.36</v>
+        <v>1791.044</v>
       </c>
       <c r="G42">
         <v>338</v>
@@ -5112,28 +5112,28 @@
         <v>362.3</v>
       </c>
       <c r="M42">
-        <v>112.005776</v>
+        <v>114.8059204</v>
       </c>
       <c r="N42">
-        <v>250.294224</v>
+        <v>247.4940796</v>
       </c>
       <c r="O42">
-        <v>51.56061014400001</v>
+        <v>50.9837803976</v>
       </c>
       <c r="P42">
-        <v>198.733613856</v>
+        <v>196.5102992024</v>
       </c>
       <c r="Q42">
-        <v>386.033613856</v>
+        <v>383.8102992024</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08478460336179626</v>
+        <v>0.0853563560377022</v>
       </c>
       <c r="T42">
-        <v>0.9003372600876736</v>
+        <v>0.9135417098776492</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.234654612812111</v>
+        <v>3.155760597865473</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5158,22 +5158,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07122736406224431</v>
+        <v>0.07122580610741085</v>
       </c>
       <c r="C43">
-        <v>2461.454698868123</v>
+        <v>2417.935257430078</v>
       </c>
       <c r="D43">
-        <v>3914.498698868123</v>
+        <v>3914.663257430078</v>
       </c>
       <c r="E43">
-        <v>408.7440000000001</v>
+        <v>452.4280000000001</v>
       </c>
       <c r="F43">
-        <v>1791.044</v>
+        <v>1834.728</v>
       </c>
       <c r="G43">
         <v>338</v>
@@ -5194,28 +5194,28 @@
         <v>362.3</v>
       </c>
       <c r="M43">
-        <v>114.8059204</v>
+        <v>117.6060648</v>
       </c>
       <c r="N43">
-        <v>247.4940796</v>
+        <v>244.6939352</v>
       </c>
       <c r="O43">
-        <v>50.9837803976</v>
+        <v>50.40695065120001</v>
       </c>
       <c r="P43">
-        <v>196.5102992024</v>
+        <v>194.2869845488</v>
       </c>
       <c r="Q43">
-        <v>383.8102992024</v>
+        <v>381.5869845488</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0853563560377022</v>
+        <v>0.08594782432312215</v>
       </c>
       <c r="T43">
-        <v>0.9135417098776492</v>
+        <v>0.9272014855224515</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -5232,7 +5232,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.155760597865473</v>
+        <v>3.080623440773438</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5240,22 +5240,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07122580610741085</v>
+        <v>0.07122424815257739</v>
       </c>
       <c r="C44">
-        <v>2417.935257430078</v>
+        <v>2374.415829828115</v>
       </c>
       <c r="D44">
-        <v>3914.663257430078</v>
+        <v>3914.827829828114</v>
       </c>
       <c r="E44">
-        <v>452.4279999999999</v>
+        <v>496.1119999999999</v>
       </c>
       <c r="F44">
-        <v>1834.728</v>
+        <v>1878.412</v>
       </c>
       <c r="G44">
         <v>338</v>
@@ -5276,28 +5276,28 @@
         <v>362.3</v>
       </c>
       <c r="M44">
-        <v>117.6060648</v>
+        <v>120.4062092</v>
       </c>
       <c r="N44">
-        <v>244.6939352</v>
+        <v>241.8937908</v>
       </c>
       <c r="O44">
-        <v>50.40695065120001</v>
+        <v>49.83012090480001</v>
       </c>
       <c r="P44">
-        <v>194.2869845488</v>
+        <v>192.0636698952</v>
       </c>
       <c r="Q44">
-        <v>381.5869845488</v>
+        <v>379.3636698952</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08594782432312213</v>
+        <v>0.0865600458817147</v>
       </c>
       <c r="T44">
-        <v>0.9272014855224513</v>
+        <v>0.9413405515407555</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.080623440773439</v>
+        <v>3.008981035174057</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5322,22 +5322,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07122424815257739</v>
+        <v>0.07394769819774394</v>
       </c>
       <c r="C45">
-        <v>2374.415829828115</v>
+        <v>2062.727458171347</v>
       </c>
       <c r="D45">
-        <v>3914.827829828114</v>
+        <v>3646.823458171347</v>
       </c>
       <c r="E45">
-        <v>496.1119999999999</v>
+        <v>539.7959999999998</v>
       </c>
       <c r="F45">
-        <v>1878.412</v>
+        <v>1922.096</v>
       </c>
       <c r="G45">
         <v>338</v>
@@ -5358,45 +5358,45 @@
         <v>362.3</v>
       </c>
       <c r="M45">
-        <v>120.4062092</v>
+        <v>138.1987024</v>
       </c>
       <c r="N45">
-        <v>241.8937908</v>
+        <v>224.1012976</v>
       </c>
       <c r="O45">
-        <v>49.83012090480001</v>
+        <v>46.1648673056</v>
       </c>
       <c r="P45">
-        <v>192.0636698952</v>
+        <v>177.9364302944</v>
       </c>
       <c r="Q45">
-        <v>379.3636698952</v>
+        <v>365.2364302944</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.0865600458817147</v>
+        <v>0.0871941324959713</v>
       </c>
       <c r="T45">
-        <v>0.9413405515407555</v>
+        <v>0.9559845842025706</v>
       </c>
       <c r="U45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0.206</v>
       </c>
       <c r="W45">
-        <v>0.05089540000000001</v>
+        <v>0.05708860000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.008981035174057</v>
+        <v>2.621587567091368</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5404,22 +5404,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07394769819774394</v>
+        <v>0.07400807224291048</v>
       </c>
       <c r="C46">
-        <v>2062.727458171347</v>
+        <v>2013.517390196039</v>
       </c>
       <c r="D46">
-        <v>3646.823458171347</v>
+        <v>3641.297390196039</v>
       </c>
       <c r="E46">
-        <v>539.7959999999998</v>
+        <v>583.48</v>
       </c>
       <c r="F46">
-        <v>1922.096</v>
+        <v>1965.78</v>
       </c>
       <c r="G46">
         <v>338</v>
@@ -5440,28 +5440,28 @@
         <v>362.3</v>
       </c>
       <c r="M46">
-        <v>138.1987024</v>
+        <v>141.339582</v>
       </c>
       <c r="N46">
-        <v>224.1012976</v>
+        <v>220.960418</v>
       </c>
       <c r="O46">
-        <v>46.1648673056</v>
+        <v>45.51784610800001</v>
       </c>
       <c r="P46">
-        <v>177.9364302944</v>
+        <v>175.442571892</v>
       </c>
       <c r="Q46">
-        <v>365.2364302944</v>
+        <v>362.742571892</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0871941324959713</v>
+        <v>0.08785127680529176</v>
       </c>
       <c r="T46">
-        <v>0.9559845842025706</v>
+        <v>0.971161127142997</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.621587567091368</v>
+        <v>2.563330065600449</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5486,22 +5486,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07400807224291048</v>
+        <v>0.07406844628807702</v>
       </c>
       <c r="C47">
-        <v>2013.517390196039</v>
+        <v>1964.324044293494</v>
       </c>
       <c r="D47">
-        <v>3641.297390196039</v>
+        <v>3635.788044293494</v>
       </c>
       <c r="E47">
-        <v>583.48</v>
+        <v>627.164</v>
       </c>
       <c r="F47">
-        <v>1965.78</v>
+        <v>2009.464</v>
       </c>
       <c r="G47">
         <v>338</v>
@@ -5522,28 +5522,28 @@
         <v>362.3</v>
       </c>
       <c r="M47">
-        <v>141.339582</v>
+        <v>144.4804616</v>
       </c>
       <c r="N47">
-        <v>220.960418</v>
+        <v>217.8195384</v>
       </c>
       <c r="O47">
-        <v>45.51784610800001</v>
+        <v>44.8708249104</v>
       </c>
       <c r="P47">
-        <v>175.442571892</v>
+        <v>172.9487134896</v>
       </c>
       <c r="Q47">
-        <v>362.742571892</v>
+        <v>360.2487134896</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08785127680529176</v>
+        <v>0.0885327597927352</v>
       </c>
       <c r="T47">
-        <v>0.971161127142997</v>
+        <v>0.9868997642664021</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.563330065600449</v>
+        <v>2.50760549895696</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5568,22 +5568,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07406844628807702</v>
+        <v>0.07558422233324356</v>
       </c>
       <c r="C48">
-        <v>1964.324044293494</v>
+        <v>1787.58371767394</v>
       </c>
       <c r="D48">
-        <v>3635.788044293494</v>
+        <v>3502.73171767394</v>
       </c>
       <c r="E48">
-        <v>627.164</v>
+        <v>670.8480000000002</v>
       </c>
       <c r="F48">
-        <v>2009.464</v>
+        <v>2053.148</v>
       </c>
       <c r="G48">
         <v>338</v>
@@ -5604,45 +5604,45 @@
         <v>362.3</v>
       </c>
       <c r="M48">
-        <v>144.4804616</v>
+        <v>155.6286184</v>
       </c>
       <c r="N48">
-        <v>217.8195384</v>
+        <v>206.6713816</v>
       </c>
       <c r="O48">
-        <v>44.8708249104</v>
+        <v>42.5743046096</v>
       </c>
       <c r="P48">
-        <v>172.9487134896</v>
+        <v>164.0970769904</v>
       </c>
       <c r="Q48">
-        <v>360.2487134896</v>
+        <v>351.3970769904</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0885327597927352</v>
+        <v>0.08923995911932747</v>
       </c>
       <c r="T48">
-        <v>0.9868997642664021</v>
+        <v>1.003232312224653</v>
       </c>
       <c r="U48">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
         <v>0.206</v>
       </c>
       <c r="W48">
-        <v>0.05708860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.50760549895696</v>
+        <v>2.327978001249158</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5650,22 +5650,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07558422233324356</v>
+        <v>0.07567556237841011</v>
       </c>
       <c r="C49">
-        <v>1787.58371767394</v>
+        <v>1736.192221022758</v>
       </c>
       <c r="D49">
-        <v>3502.73171767394</v>
+        <v>3495.024221022758</v>
       </c>
       <c r="E49">
-        <v>670.8480000000002</v>
+        <v>714.5319999999999</v>
       </c>
       <c r="F49">
-        <v>2053.148</v>
+        <v>2096.832</v>
       </c>
       <c r="G49">
         <v>338</v>
@@ -5686,28 +5686,28 @@
         <v>362.3</v>
       </c>
       <c r="M49">
-        <v>155.6286184</v>
+        <v>158.9398656</v>
       </c>
       <c r="N49">
-        <v>206.6713816</v>
+        <v>203.3601344</v>
       </c>
       <c r="O49">
-        <v>42.5743046096</v>
+        <v>41.89218768640001</v>
       </c>
       <c r="P49">
-        <v>164.0970769904</v>
+        <v>161.4679467136</v>
       </c>
       <c r="Q49">
-        <v>351.3970769904</v>
+        <v>348.7679467136001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08923995911932747</v>
+        <v>0.08997435842001943</v>
       </c>
       <c r="T49">
-        <v>1.003232312224653</v>
+        <v>1.020193035104375</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.327978001249158</v>
+        <v>2.279478459556468</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5732,22 +5732,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07567556237841011</v>
+        <v>0.07576690242357664</v>
       </c>
       <c r="C50">
-        <v>1736.192221022758</v>
+        <v>1684.834569426854</v>
       </c>
       <c r="D50">
-        <v>3495.024221022758</v>
+        <v>3487.350569426853</v>
       </c>
       <c r="E50">
-        <v>714.5319999999999</v>
+        <v>758.2159999999997</v>
       </c>
       <c r="F50">
-        <v>2096.832</v>
+        <v>2140.516</v>
       </c>
       <c r="G50">
         <v>338</v>
@@ -5768,28 +5768,28 @@
         <v>362.3</v>
       </c>
       <c r="M50">
-        <v>158.9398656</v>
+        <v>162.2511128</v>
       </c>
       <c r="N50">
-        <v>203.3601344</v>
+        <v>200.0488872</v>
       </c>
       <c r="O50">
-        <v>41.89218768640001</v>
+        <v>41.21007076320001</v>
       </c>
       <c r="P50">
-        <v>161.4679467136</v>
+        <v>158.8388164368</v>
       </c>
       <c r="Q50">
-        <v>348.7679467136001</v>
+        <v>346.1388164368</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08997435842001941</v>
+        <v>0.09073755769328753</v>
       </c>
       <c r="T50">
-        <v>1.020193035104375</v>
+        <v>1.037818884371537</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.279478459556468</v>
+        <v>2.232958490994091</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5814,22 +5814,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07576690242357664</v>
+        <v>0.07585824246874319</v>
       </c>
       <c r="C51">
-        <v>1684.834569426854</v>
+        <v>1633.510540444691</v>
       </c>
       <c r="D51">
-        <v>3487.350569426853</v>
+        <v>3479.710540444691</v>
       </c>
       <c r="E51">
-        <v>758.2159999999997</v>
+        <v>801.8999999999999</v>
       </c>
       <c r="F51">
-        <v>2140.516</v>
+        <v>2184.2</v>
       </c>
       <c r="G51">
         <v>338</v>
@@ -5850,28 +5850,28 @@
         <v>362.3</v>
       </c>
       <c r="M51">
-        <v>162.2511128</v>
+        <v>165.56236</v>
       </c>
       <c r="N51">
-        <v>200.0488872</v>
+        <v>196.73764</v>
       </c>
       <c r="O51">
-        <v>41.21007076320001</v>
+        <v>40.52795384</v>
       </c>
       <c r="P51">
-        <v>158.8388164368</v>
+        <v>156.20968616</v>
       </c>
       <c r="Q51">
-        <v>346.1388164368</v>
+        <v>343.50968616</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09073755769328753</v>
+        <v>0.09153128493748637</v>
       </c>
       <c r="T51">
-        <v>1.037818884371537</v>
+        <v>1.056149767609385</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.232958490994091</v>
+        <v>2.188299321174209</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5896,22 +5896,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07585824246874319</v>
+        <v>0.07594958251390974</v>
       </c>
       <c r="C52">
-        <v>1633.510540444691</v>
+        <v>1582.219913579762</v>
       </c>
       <c r="D52">
-        <v>3479.710540444691</v>
+        <v>3472.103913579762</v>
       </c>
       <c r="E52">
-        <v>801.8999999999999</v>
+        <v>845.5840000000001</v>
       </c>
       <c r="F52">
-        <v>2184.2</v>
+        <v>2227.884</v>
       </c>
       <c r="G52">
         <v>338</v>
@@ -5932,28 +5932,28 @@
         <v>362.3</v>
       </c>
       <c r="M52">
-        <v>165.56236</v>
+        <v>168.8736072</v>
       </c>
       <c r="N52">
-        <v>196.73764</v>
+        <v>193.4263928</v>
       </c>
       <c r="O52">
-        <v>40.52795384</v>
+        <v>39.8458369168</v>
       </c>
       <c r="P52">
-        <v>156.20968616</v>
+        <v>153.5805558832</v>
       </c>
       <c r="Q52">
-        <v>343.50968616</v>
+        <v>340.8805558832</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09153128493748637</v>
+        <v>0.09235740921206068</v>
       </c>
       <c r="T52">
-        <v>1.056149767609385</v>
+        <v>1.075228850163064</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.188299321174209</v>
+        <v>2.145391491347263</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5978,22 +5978,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07594958251390974</v>
+        <v>0.07604092255907627</v>
       </c>
       <c r="C53">
-        <v>1582.219913579762</v>
+        <v>1530.962470259368</v>
       </c>
       <c r="D53">
-        <v>3472.103913579762</v>
+        <v>3464.530470259368</v>
       </c>
       <c r="E53">
-        <v>845.5840000000001</v>
+        <v>889.2679999999998</v>
       </c>
       <c r="F53">
-        <v>2227.884</v>
+        <v>2271.568</v>
       </c>
       <c r="G53">
         <v>338</v>
@@ -6014,28 +6014,28 @@
         <v>362.3</v>
       </c>
       <c r="M53">
-        <v>168.8736072</v>
+        <v>172.1848544</v>
       </c>
       <c r="N53">
-        <v>193.4263928</v>
+        <v>190.1151456</v>
       </c>
       <c r="O53">
-        <v>39.8458369168</v>
+        <v>39.1637199936</v>
       </c>
       <c r="P53">
-        <v>153.5805558832</v>
+        <v>150.9514256064</v>
       </c>
       <c r="Q53">
-        <v>340.8805558832</v>
+        <v>338.2514256064</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09235740921206068</v>
+        <v>0.09321795533140889</v>
       </c>
       <c r="T53">
-        <v>1.075228850163064</v>
+        <v>1.095102894489813</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.145391491347263</v>
+        <v>2.104133962667508</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6060,22 +6060,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07604092255907627</v>
+        <v>0.07613226260424283</v>
       </c>
       <c r="C54">
-        <v>1530.962470259368</v>
+        <v>1479.737993813681</v>
       </c>
       <c r="D54">
-        <v>3464.530470259368</v>
+        <v>3456.989993813681</v>
       </c>
       <c r="E54">
-        <v>889.2679999999998</v>
+        <v>932.952</v>
       </c>
       <c r="F54">
-        <v>2271.568</v>
+        <v>2315.252</v>
       </c>
       <c r="G54">
         <v>338</v>
@@ -6096,28 +6096,28 @@
         <v>362.3</v>
       </c>
       <c r="M54">
-        <v>172.1848544</v>
+        <v>175.4961016</v>
       </c>
       <c r="N54">
-        <v>190.1151456</v>
+        <v>186.8038984</v>
       </c>
       <c r="O54">
-        <v>39.1637199936</v>
+        <v>38.48160307040001</v>
       </c>
       <c r="P54">
-        <v>150.9514256064</v>
+        <v>148.3222953296</v>
       </c>
       <c r="Q54">
-        <v>338.2514256064</v>
+        <v>335.6222953296</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09321795533140889</v>
+        <v>0.09411512043455919</v>
       </c>
       <c r="T54">
-        <v>1.095102894489813</v>
+        <v>1.115822642830466</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.104133962667508</v>
+        <v>2.064433321862461</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6142,22 +6142,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07613226260424283</v>
+        <v>0.07622360264940936</v>
       </c>
       <c r="C55">
-        <v>1479.737993813681</v>
+        <v>1428.546269455094</v>
       </c>
       <c r="D55">
-        <v>3456.989993813681</v>
+        <v>3449.482269455094</v>
       </c>
       <c r="E55">
-        <v>932.952</v>
+        <v>976.6360000000002</v>
       </c>
       <c r="F55">
-        <v>2315.252</v>
+        <v>2358.936</v>
       </c>
       <c r="G55">
         <v>338</v>
@@ -6178,28 +6178,28 @@
         <v>362.3</v>
       </c>
       <c r="M55">
-        <v>175.4961016</v>
+        <v>178.8073488</v>
       </c>
       <c r="N55">
-        <v>186.8038984</v>
+        <v>183.4926512</v>
       </c>
       <c r="O55">
-        <v>38.48160307040001</v>
+        <v>37.7994861472</v>
       </c>
       <c r="P55">
-        <v>148.3222953296</v>
+        <v>145.6931650528</v>
       </c>
       <c r="Q55">
-        <v>335.6222953296</v>
+        <v>332.9931650528</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09411512043455919</v>
+        <v>0.09505129271610729</v>
       </c>
       <c r="T55">
-        <v>1.115822642830466</v>
+        <v>1.137443249794626</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.064433321862461</v>
+        <v>2.026203075161304</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6224,22 +6224,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07622360264940936</v>
+        <v>0.08251608269457589</v>
       </c>
       <c r="C56">
-        <v>1428.546269455094</v>
+        <v>935.9382128713396</v>
       </c>
       <c r="D56">
-        <v>3449.482269455094</v>
+        <v>3000.558212871339</v>
       </c>
       <c r="E56">
-        <v>976.6360000000002</v>
+        <v>1020.32</v>
       </c>
       <c r="F56">
-        <v>2358.936</v>
+        <v>2402.62</v>
       </c>
       <c r="G56">
         <v>338</v>
@@ -6260,45 +6260,45 @@
         <v>362.3</v>
       </c>
       <c r="M56">
-        <v>178.8073488</v>
+        <v>216.2358</v>
       </c>
       <c r="N56">
-        <v>183.4926512</v>
+        <v>146.0642</v>
       </c>
       <c r="O56">
-        <v>37.7994861472</v>
+        <v>30.08922520000001</v>
       </c>
       <c r="P56">
-        <v>145.6931650528</v>
+        <v>115.9749748</v>
       </c>
       <c r="Q56">
-        <v>332.9931650528</v>
+        <v>303.2749748</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09505129271610729</v>
+        <v>0.09602907265461311</v>
       </c>
       <c r="T56">
-        <v>1.137443249794626</v>
+        <v>1.16002477262386</v>
       </c>
       <c r="U56">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V56">
         <v>0.206</v>
       </c>
       <c r="W56">
-        <v>0.06018520000000001</v>
+        <v>0.07146</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.026203075161304</v>
+        <v>1.675485742878839</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6306,22 +6306,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08251608269457589</v>
+        <v>0.08272017073974244</v>
       </c>
       <c r="C57">
-        <v>935.9382128713396</v>
+        <v>879.64211183715</v>
       </c>
       <c r="D57">
-        <v>3000.558212871339</v>
+        <v>2987.94611183715</v>
       </c>
       <c r="E57">
-        <v>1020.32</v>
+        <v>1064.004</v>
       </c>
       <c r="F57">
-        <v>2402.62</v>
+        <v>2446.304</v>
       </c>
       <c r="G57">
         <v>338</v>
@@ -6342,28 +6342,28 @@
         <v>362.3</v>
       </c>
       <c r="M57">
-        <v>216.2358</v>
+        <v>220.16736</v>
       </c>
       <c r="N57">
-        <v>146.0642</v>
+        <v>142.13264</v>
       </c>
       <c r="O57">
-        <v>30.08922520000001</v>
+        <v>29.27932384</v>
       </c>
       <c r="P57">
-        <v>115.9749748</v>
+        <v>112.85331616</v>
       </c>
       <c r="Q57">
-        <v>303.2749748</v>
+        <v>300.15331616</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09602907265461311</v>
+        <v>0.09705129713577829</v>
       </c>
       <c r="T57">
-        <v>1.16002477262386</v>
+        <v>1.183632728308968</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.675485742878839</v>
+        <v>1.645566354613145</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6388,22 +6388,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08272017073974244</v>
+        <v>0.08292425878490899</v>
       </c>
       <c r="C58">
-        <v>879.64211183715</v>
+        <v>823.451590691202</v>
       </c>
       <c r="D58">
-        <v>2987.94611183715</v>
+        <v>2975.439590691202</v>
       </c>
       <c r="E58">
-        <v>1064.004</v>
+        <v>1107.688</v>
       </c>
       <c r="F58">
-        <v>2446.304</v>
+        <v>2489.988</v>
       </c>
       <c r="G58">
         <v>338</v>
@@ -6424,28 +6424,28 @@
         <v>362.3</v>
       </c>
       <c r="M58">
-        <v>220.16736</v>
+        <v>224.09892</v>
       </c>
       <c r="N58">
-        <v>142.13264</v>
+        <v>138.20108</v>
       </c>
       <c r="O58">
-        <v>29.27932384</v>
+        <v>28.46942248</v>
       </c>
       <c r="P58">
-        <v>112.85331616</v>
+        <v>109.73165752</v>
       </c>
       <c r="Q58">
-        <v>300.15331616</v>
+        <v>297.03165752</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09705129713577829</v>
+        <v>0.09812106694164881</v>
       </c>
       <c r="T58">
-        <v>1.183632728308968</v>
+        <v>1.208338728444545</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.645566354613145</v>
+        <v>1.616696769444494</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6470,22 +6470,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08292425878490899</v>
+        <v>0.08312834683007553</v>
       </c>
       <c r="C59">
-        <v>823.451590691202</v>
+        <v>767.3653291955848</v>
       </c>
       <c r="D59">
-        <v>2975.439590691202</v>
+        <v>2963.037329195585</v>
       </c>
       <c r="E59">
-        <v>1107.688</v>
+        <v>1151.372</v>
       </c>
       <c r="F59">
-        <v>2489.988</v>
+        <v>2533.672</v>
       </c>
       <c r="G59">
         <v>338</v>
@@ -6506,28 +6506,28 @@
         <v>362.3</v>
       </c>
       <c r="M59">
-        <v>224.09892</v>
+        <v>228.03048</v>
       </c>
       <c r="N59">
-        <v>138.20108</v>
+        <v>134.26952</v>
       </c>
       <c r="O59">
-        <v>28.46942248</v>
+        <v>27.65952112000001</v>
       </c>
       <c r="P59">
-        <v>109.73165752</v>
+        <v>106.60999888</v>
       </c>
       <c r="Q59">
-        <v>297.03165752</v>
+        <v>293.90999888</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09812106694164881</v>
+        <v>0.09924177816684651</v>
       </c>
       <c r="T59">
-        <v>1.208338728444545</v>
+        <v>1.234221204777056</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6544,7 +6544,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.616696769444494</v>
+        <v>1.588822687212692</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6552,22 +6552,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08312834683007553</v>
+        <v>0.08333243487524207</v>
       </c>
       <c r="C60">
-        <v>767.3653291955852</v>
+        <v>711.3820290331405</v>
       </c>
       <c r="D60">
-        <v>2963.037329195585</v>
+        <v>2950.73802903314</v>
       </c>
       <c r="E60">
-        <v>1151.372</v>
+        <v>1195.056</v>
       </c>
       <c r="F60">
-        <v>2533.672</v>
+        <v>2577.356</v>
       </c>
       <c r="G60">
         <v>338</v>
@@ -6588,28 +6588,28 @@
         <v>362.3</v>
       </c>
       <c r="M60">
-        <v>228.03048</v>
+        <v>231.96204</v>
       </c>
       <c r="N60">
-        <v>134.2695200000001</v>
+        <v>130.33796</v>
       </c>
       <c r="O60">
-        <v>27.65952112000002</v>
+        <v>26.84961976000001</v>
       </c>
       <c r="P60">
-        <v>106.60999888</v>
+        <v>103.48834024</v>
       </c>
       <c r="Q60">
-        <v>293.90999888</v>
+        <v>290.78834024</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.0992417781668465</v>
+        <v>0.1004171582322977</v>
       </c>
       <c r="T60">
-        <v>1.234221204777056</v>
+        <v>1.261366240930664</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.588822687212692</v>
+        <v>1.561893489124341</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6634,22 +6634,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08333243487524207</v>
+        <v>0.08353652292040861</v>
       </c>
       <c r="C61">
-        <v>711.3820290331405</v>
+        <v>655.5004133543903</v>
       </c>
       <c r="D61">
-        <v>2950.73802903314</v>
+        <v>2938.54041335439</v>
       </c>
       <c r="E61">
-        <v>1195.056</v>
+        <v>1238.74</v>
       </c>
       <c r="F61">
-        <v>2577.356</v>
+        <v>2621.04</v>
       </c>
       <c r="G61">
         <v>338</v>
@@ -6670,28 +6670,28 @@
         <v>362.3</v>
       </c>
       <c r="M61">
-        <v>231.96204</v>
+        <v>235.8935999999999</v>
       </c>
       <c r="N61">
-        <v>130.33796</v>
+        <v>126.4064000000001</v>
       </c>
       <c r="O61">
-        <v>26.84961976000001</v>
+        <v>26.03971840000002</v>
       </c>
       <c r="P61">
-        <v>103.48834024</v>
+        <v>100.3666816</v>
       </c>
       <c r="Q61">
-        <v>290.78834024</v>
+        <v>287.6666816000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1004171582322977</v>
+        <v>0.1016513073010215</v>
       </c>
       <c r="T61">
-        <v>1.261366240930664</v>
+        <v>1.289868528891952</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.561893489124341</v>
+        <v>1.535861930972269</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6716,22 +6716,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08353652292040861</v>
+        <v>0.08374061096557515</v>
       </c>
       <c r="C62">
-        <v>655.5004133543903</v>
+        <v>599.7192263356487</v>
       </c>
       <c r="D62">
-        <v>2938.54041335439</v>
+        <v>2926.443226335648</v>
       </c>
       <c r="E62">
-        <v>1238.74</v>
+        <v>1282.424</v>
       </c>
       <c r="F62">
-        <v>2621.04</v>
+        <v>2664.724</v>
       </c>
       <c r="G62">
         <v>338</v>
@@ -6752,28 +6752,28 @@
         <v>362.3</v>
       </c>
       <c r="M62">
-        <v>235.8935999999999</v>
+        <v>239.82516</v>
       </c>
       <c r="N62">
-        <v>126.4064000000001</v>
+        <v>122.4748400000001</v>
       </c>
       <c r="O62">
-        <v>26.03971840000002</v>
+        <v>25.22981704000001</v>
       </c>
       <c r="P62">
-        <v>100.3666816</v>
+        <v>97.24502296000004</v>
       </c>
       <c r="Q62">
-        <v>287.6666816000001</v>
+        <v>284.54502296</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1016513073010215</v>
+        <v>0.1029487460655773</v>
       </c>
       <c r="T62">
-        <v>1.289868528891952</v>
+        <v>1.319832472646128</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.535861930972269</v>
+        <v>1.510683866530101</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6798,22 +6798,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08374061096557515</v>
+        <v>0.1138595817994899</v>
       </c>
       <c r="C63">
-        <v>599.7192263356487</v>
+        <v>-549.9604982932146</v>
       </c>
       <c r="D63">
-        <v>2926.443226335648</v>
+        <v>1820.447501706785</v>
       </c>
       <c r="E63">
-        <v>1282.424</v>
+        <v>1326.108</v>
       </c>
       <c r="F63">
-        <v>2664.724</v>
+        <v>2708.408</v>
       </c>
       <c r="G63">
         <v>338</v>
@@ -6834,45 +6834,45 @@
         <v>362.3</v>
       </c>
       <c r="M63">
-        <v>239.82516</v>
+        <v>397.5942944</v>
       </c>
       <c r="N63">
-        <v>122.4748400000001</v>
+        <v>-35.29429440000001</v>
       </c>
       <c r="O63">
-        <v>25.22981704000001</v>
+        <v>-7.270624646400003</v>
       </c>
       <c r="P63">
-        <v>97.24502296000004</v>
+        <v>-28.02366975360001</v>
       </c>
       <c r="Q63">
-        <v>284.54502296</v>
+        <v>159.2763302464</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1029487460655773</v>
+        <v>0.1050750261042774</v>
       </c>
       <c r="T63">
-        <v>1.319832472646128</v>
+        <v>1.368938247211948</v>
       </c>
       <c r="U63">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.206</v>
+        <v>0.1877134582945363</v>
       </c>
       <c r="W63">
-        <v>0.07146</v>
+        <v>0.1192436643223621</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.510683866530101</v>
+        <v>0.9112303800705647</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6880,22 +6880,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1138595817994899</v>
+        <v>0.1148695817994899</v>
       </c>
       <c r="C64">
-        <v>-549.9604982932146</v>
+        <v>-616.4271006168256</v>
       </c>
       <c r="D64">
-        <v>1820.447501706785</v>
+        <v>1797.664899383174</v>
       </c>
       <c r="E64">
-        <v>1326.108</v>
+        <v>1369.792</v>
       </c>
       <c r="F64">
-        <v>2708.408</v>
+        <v>2752.092</v>
       </c>
       <c r="G64">
         <v>338</v>
@@ -6916,37 +6916,37 @@
         <v>362.3</v>
       </c>
       <c r="M64">
-        <v>397.5942944</v>
+        <v>404.0071056</v>
       </c>
       <c r="N64">
-        <v>-35.29429440000001</v>
+        <v>-41.70710559999998</v>
       </c>
       <c r="O64">
-        <v>-7.270624646400003</v>
+        <v>-8.591663753599995</v>
       </c>
       <c r="P64">
-        <v>-28.02366975360001</v>
+        <v>-33.11544184639998</v>
       </c>
       <c r="Q64">
-        <v>159.2763302464</v>
+        <v>154.1845581536</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1050750261042774</v>
+        <v>0.1066770538368254</v>
       </c>
       <c r="T64">
-        <v>1.368938247211948</v>
+        <v>1.405936578217676</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1877134582945363</v>
+        <v>0.1847338795914485</v>
       </c>
       <c r="W64">
-        <v>0.1192436643223621</v>
+        <v>0.1196810664759754</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.9112303800705647</v>
+        <v>0.8967664057837303</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6962,22 +6962,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1148695817994899</v>
+        <v>0.1158795817994899</v>
       </c>
       <c r="C65">
-        <v>-616.4271006168256</v>
+        <v>-682.330510132876</v>
       </c>
       <c r="D65">
-        <v>1797.664899383174</v>
+        <v>1775.445489867124</v>
       </c>
       <c r="E65">
-        <v>1369.792</v>
+        <v>1413.476</v>
       </c>
       <c r="F65">
-        <v>2752.092</v>
+        <v>2795.776</v>
       </c>
       <c r="G65">
         <v>338</v>
@@ -6998,37 +6998,37 @@
         <v>362.3</v>
       </c>
       <c r="M65">
-        <v>404.0071056</v>
+        <v>410.4199168</v>
       </c>
       <c r="N65">
-        <v>-41.70710559999998</v>
+        <v>-48.1199168</v>
       </c>
       <c r="O65">
-        <v>-8.591663753599995</v>
+        <v>-9.9127028608</v>
       </c>
       <c r="P65">
-        <v>-33.11544184639998</v>
+        <v>-38.2072139392</v>
       </c>
       <c r="Q65">
-        <v>154.1845581536</v>
+        <v>149.0927860608</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1066770538368254</v>
+        <v>0.1083680831100705</v>
       </c>
       <c r="T65">
-        <v>1.405936578217676</v>
+        <v>1.444990372057056</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1847338795914485</v>
+        <v>0.1818474127228321</v>
       </c>
       <c r="W65">
-        <v>0.1196810664759754</v>
+        <v>0.1201047998122883</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8967664057837303</v>
+        <v>0.8827544306933596</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7044,22 +7044,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1158795817994899</v>
+        <v>0.1168895817994899</v>
       </c>
       <c r="C66">
-        <v>-682.330510132876</v>
+        <v>-747.6913553146687</v>
       </c>
       <c r="D66">
-        <v>1775.445489867124</v>
+        <v>1753.768644685332</v>
       </c>
       <c r="E66">
-        <v>1413.476</v>
+        <v>1457.16</v>
       </c>
       <c r="F66">
-        <v>2795.776</v>
+        <v>2839.46</v>
       </c>
       <c r="G66">
         <v>338</v>
@@ -7080,37 +7080,37 @@
         <v>362.3</v>
       </c>
       <c r="M66">
-        <v>410.4199168</v>
+        <v>416.832728</v>
       </c>
       <c r="N66">
-        <v>-48.1199168</v>
+        <v>-54.53272800000002</v>
       </c>
       <c r="O66">
-        <v>-9.9127028608</v>
+        <v>-11.23374196800001</v>
       </c>
       <c r="P66">
-        <v>-38.2072139392</v>
+        <v>-43.29898603200002</v>
       </c>
       <c r="Q66">
-        <v>149.0927860608</v>
+        <v>144.001013968</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1083680831100705</v>
+        <v>0.1101557426275011</v>
       </c>
       <c r="T66">
-        <v>1.444990372057056</v>
+        <v>1.486275811258687</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1818474127228321</v>
+        <v>0.1790497602194039</v>
       </c>
       <c r="W66">
-        <v>0.1201047998122883</v>
+        <v>0.1205154951997915</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8827544306933596</v>
+        <v>0.8691735932980771</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7126,22 +7126,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1168895817994899</v>
+        <v>0.1178995817994899</v>
       </c>
       <c r="C67">
-        <v>-747.6913553146687</v>
+        <v>-812.5292693549659</v>
       </c>
       <c r="D67">
-        <v>1753.768644685332</v>
+        <v>1732.614730645034</v>
       </c>
       <c r="E67">
-        <v>1457.16</v>
+        <v>1500.844</v>
       </c>
       <c r="F67">
-        <v>2839.46</v>
+        <v>2883.144</v>
       </c>
       <c r="G67">
         <v>338</v>
@@ -7162,37 +7162,37 @@
         <v>362.3</v>
       </c>
       <c r="M67">
-        <v>416.832728</v>
+        <v>423.2455392</v>
       </c>
       <c r="N67">
-        <v>-54.53272800000002</v>
+        <v>-60.94553919999998</v>
       </c>
       <c r="O67">
-        <v>-11.23374196800001</v>
+        <v>-12.5547810752</v>
       </c>
       <c r="P67">
-        <v>-43.29898603200002</v>
+        <v>-48.39075812479999</v>
       </c>
       <c r="Q67">
-        <v>144.001013968</v>
+        <v>138.9092418752</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1101557426275011</v>
+        <v>0.1120485585871335</v>
       </c>
       <c r="T67">
-        <v>1.486275811258687</v>
+        <v>1.529989805707472</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1790497602194039</v>
+        <v>0.1763368850645645</v>
       </c>
       <c r="W67">
-        <v>0.1205154951997915</v>
+        <v>0.120913745272522</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8691735932980771</v>
+        <v>0.8560042964299245</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7208,22 +7208,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1178995817994899</v>
+        <v>0.1189095817994899</v>
       </c>
       <c r="C68">
-        <v>-812.5292693549659</v>
+        <v>-876.8629494758475</v>
       </c>
       <c r="D68">
-        <v>1732.614730645034</v>
+        <v>1711.965050524153</v>
       </c>
       <c r="E68">
-        <v>1500.844</v>
+        <v>1544.528</v>
       </c>
       <c r="F68">
-        <v>2883.144</v>
+        <v>2926.828</v>
       </c>
       <c r="G68">
         <v>338</v>
@@ -7244,37 +7244,37 @@
         <v>362.3</v>
       </c>
       <c r="M68">
-        <v>423.2455392</v>
+        <v>429.6583504</v>
       </c>
       <c r="N68">
-        <v>-60.94553919999998</v>
+        <v>-67.35835040000001</v>
       </c>
       <c r="O68">
-        <v>-12.5547810752</v>
+        <v>-13.8758201824</v>
       </c>
       <c r="P68">
-        <v>-48.39075812479999</v>
+        <v>-53.4825302176</v>
       </c>
       <c r="Q68">
-        <v>138.9092418752</v>
+        <v>133.8174697824</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1120485585871335</v>
+        <v>0.1140560906655315</v>
       </c>
       <c r="T68">
-        <v>1.529989805707472</v>
+        <v>1.576353133153153</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1763368850645645</v>
+        <v>0.1737049912576306</v>
       </c>
       <c r="W68">
-        <v>0.120913745272522</v>
+        <v>0.1213001072833798</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8560042964299245</v>
+        <v>0.8432281129011195</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7290,22 +7290,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1189095817994899</v>
+        <v>0.1199195817994899</v>
       </c>
       <c r="C69">
-        <v>-876.8629494758475</v>
+        <v>-940.7102120472982</v>
       </c>
       <c r="D69">
-        <v>1711.965050524153</v>
+        <v>1691.801787952702</v>
       </c>
       <c r="E69">
-        <v>1544.528</v>
+        <v>1588.212</v>
       </c>
       <c r="F69">
-        <v>2926.828</v>
+        <v>2970.512</v>
       </c>
       <c r="G69">
         <v>338</v>
@@ -7326,37 +7326,37 @@
         <v>362.3</v>
       </c>
       <c r="M69">
-        <v>429.6583504</v>
+        <v>436.0711616</v>
       </c>
       <c r="N69">
-        <v>-67.35835040000001</v>
+        <v>-73.77116160000003</v>
       </c>
       <c r="O69">
-        <v>-13.8758201824</v>
+        <v>-15.19685928960001</v>
       </c>
       <c r="P69">
-        <v>-53.4825302176</v>
+        <v>-58.57430231040002</v>
       </c>
       <c r="Q69">
-        <v>133.8174697824</v>
+        <v>128.7256976896</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1140560906655315</v>
+        <v>0.1161890934988294</v>
       </c>
       <c r="T69">
-        <v>1.576353133153153</v>
+        <v>1.625614168564189</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1737049912576306</v>
+        <v>0.1711505060920772</v>
       </c>
       <c r="W69">
-        <v>0.1213001072833798</v>
+        <v>0.1216751057056831</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8432281129011195</v>
+        <v>0.830827699476103</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7372,22 +7372,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1199195817994899</v>
+        <v>0.1209295817994899</v>
       </c>
       <c r="C70">
-        <v>-940.7102120472982</v>
+        <v>-1004.088043856083</v>
       </c>
       <c r="D70">
-        <v>1691.801787952702</v>
+        <v>1672.107956143917</v>
       </c>
       <c r="E70">
-        <v>1588.212</v>
+        <v>1631.896</v>
       </c>
       <c r="F70">
-        <v>2970.512</v>
+        <v>3014.196</v>
       </c>
       <c r="G70">
         <v>338</v>
@@ -7408,37 +7408,37 @@
         <v>362.3</v>
       </c>
       <c r="M70">
-        <v>436.0711616</v>
+        <v>442.4839728</v>
       </c>
       <c r="N70">
-        <v>-73.77116160000003</v>
+        <v>-80.18397279999999</v>
       </c>
       <c r="O70">
-        <v>-15.19685928960001</v>
+        <v>-16.5178983968</v>
       </c>
       <c r="P70">
-        <v>-58.57430231040002</v>
+        <v>-63.66607440319999</v>
       </c>
       <c r="Q70">
-        <v>128.7256976896</v>
+        <v>123.6339255968</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1161890934988294</v>
+        <v>0.1184597094181464</v>
       </c>
       <c r="T70">
-        <v>1.625614168564189</v>
+        <v>1.678053335292066</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1711505060920772</v>
+        <v>0.1686700639748008</v>
       </c>
       <c r="W70">
-        <v>0.1216751057056831</v>
+        <v>0.1220392346084993</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.830827699476103</v>
+        <v>0.8187867183242755</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7454,22 +7454,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1209295817994899</v>
+        <v>0.1219395817994899</v>
       </c>
       <c r="C71">
-        <v>-1004.088043856083</v>
+        <v>-1067.012649834974</v>
       </c>
       <c r="D71">
-        <v>1672.107956143917</v>
+        <v>1652.867350165026</v>
       </c>
       <c r="E71">
-        <v>1631.896</v>
+        <v>1675.58</v>
       </c>
       <c r="F71">
-        <v>3014.196</v>
+        <v>3057.88</v>
       </c>
       <c r="G71">
         <v>338</v>
@@ -7490,37 +7490,37 @@
         <v>362.3</v>
       </c>
       <c r="M71">
-        <v>442.4839728</v>
+        <v>448.8967840000001</v>
       </c>
       <c r="N71">
-        <v>-80.18397279999999</v>
+        <v>-86.59678400000007</v>
       </c>
       <c r="O71">
-        <v>-16.5178983968</v>
+        <v>-17.83893750400001</v>
       </c>
       <c r="P71">
-        <v>-63.66607440319999</v>
+        <v>-68.75784649600006</v>
       </c>
       <c r="Q71">
-        <v>123.6339255968</v>
+        <v>118.542153504</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1184597094181464</v>
+        <v>0.1208816997320847</v>
       </c>
       <c r="T71">
-        <v>1.678053335292066</v>
+        <v>1.733988446468468</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1686700639748008</v>
+        <v>0.1662604916323036</v>
       </c>
       <c r="W71">
-        <v>0.1220392346084993</v>
+        <v>0.1223929598283778</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8187867183242755</v>
+        <v>0.8070897652053572</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7536,22 +7536,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1219395817994899</v>
+        <v>0.1620874076745033</v>
       </c>
       <c r="C72">
-        <v>-1067.012649834974</v>
+        <v>-1629.442531849423</v>
       </c>
       <c r="D72">
-        <v>1652.867350165026</v>
+        <v>1134.121468150577</v>
       </c>
       <c r="E72">
-        <v>1675.58</v>
+        <v>1719.264</v>
       </c>
       <c r="F72">
-        <v>3057.88</v>
+        <v>3101.564</v>
       </c>
       <c r="G72">
         <v>338</v>
@@ -7572,45 +7572,45 @@
         <v>362.3</v>
       </c>
       <c r="M72">
-        <v>448.8967840000001</v>
+        <v>622.7940512</v>
       </c>
       <c r="N72">
-        <v>-86.59678400000007</v>
+        <v>-260.4940512</v>
       </c>
       <c r="O72">
-        <v>-17.83893750400001</v>
+        <v>-53.6617745472</v>
       </c>
       <c r="P72">
-        <v>-68.75784649600006</v>
+        <v>-206.8322766528</v>
       </c>
       <c r="Q72">
-        <v>118.542153504</v>
+        <v>-19.53227665279999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1208816997320847</v>
+        <v>0.1262218475677201</v>
       </c>
       <c r="T72">
-        <v>1.733988446468468</v>
+        <v>1.857317495790302</v>
       </c>
       <c r="U72">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1662604916323036</v>
+        <v>0.1198370470241255</v>
       </c>
       <c r="W72">
-        <v>0.1223929598283778</v>
+        <v>0.1767367209575556</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.8070897652053572</v>
+        <v>0.5817332379811916</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7618,22 +7618,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1620874076745033</v>
+        <v>0.1636374076745033</v>
       </c>
       <c r="C73">
-        <v>-1629.442531849422</v>
+        <v>-1686.703890321481</v>
       </c>
       <c r="D73">
-        <v>1134.121468150577</v>
+        <v>1120.544109678519</v>
       </c>
       <c r="E73">
-        <v>1719.263999999999</v>
+        <v>1762.948</v>
       </c>
       <c r="F73">
-        <v>3101.563999999999</v>
+        <v>3145.248</v>
       </c>
       <c r="G73">
         <v>338</v>
@@ -7654,37 +7654,37 @@
         <v>362.3</v>
       </c>
       <c r="M73">
-        <v>622.7940511999999</v>
+        <v>631.5657983999999</v>
       </c>
       <c r="N73">
-        <v>-260.4940511999999</v>
+        <v>-269.2657983999999</v>
       </c>
       <c r="O73">
-        <v>-53.66177454719998</v>
+        <v>-55.46875447039999</v>
       </c>
       <c r="P73">
-        <v>-206.8322766527999</v>
+        <v>-213.7970439295999</v>
       </c>
       <c r="Q73">
-        <v>-19.53227665279991</v>
+        <v>-26.49704392959993</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.12622184756772</v>
+        <v>0.1290940564094243</v>
       </c>
       <c r="T73">
-        <v>1.857317495790302</v>
+        <v>1.923650263497098</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1198370470241255</v>
+        <v>0.1181726435932349</v>
       </c>
       <c r="W73">
-        <v>0.1767367209575556</v>
+        <v>0.1770709331664785</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5817332379811917</v>
+        <v>0.5736536096758973</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7700,22 +7700,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1636374076745033</v>
+        <v>0.1651874076745033</v>
       </c>
       <c r="C74">
-        <v>-1686.703890321481</v>
+        <v>-1743.644006567264</v>
       </c>
       <c r="D74">
-        <v>1120.544109678519</v>
+        <v>1107.287993432736</v>
       </c>
       <c r="E74">
-        <v>1762.948</v>
+        <v>1806.632</v>
       </c>
       <c r="F74">
-        <v>3145.248</v>
+        <v>3188.932</v>
       </c>
       <c r="G74">
         <v>338</v>
@@ -7736,37 +7736,37 @@
         <v>362.3</v>
       </c>
       <c r="M74">
-        <v>631.5657983999999</v>
+        <v>640.3375456</v>
       </c>
       <c r="N74">
-        <v>-269.2657983999999</v>
+        <v>-278.0375456</v>
       </c>
       <c r="O74">
-        <v>-55.46875447039999</v>
+        <v>-57.2757343936</v>
       </c>
       <c r="P74">
-        <v>-213.7970439295999</v>
+        <v>-220.7618112064</v>
       </c>
       <c r="Q74">
-        <v>-26.49704392959993</v>
+        <v>-33.46181120639997</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1290940564094243</v>
+        <v>0.1321790214616252</v>
       </c>
       <c r="T74">
-        <v>1.923650263497098</v>
+        <v>1.994896569552546</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1181726435932349</v>
+        <v>0.1165538402563412</v>
       </c>
       <c r="W74">
-        <v>0.1770709331664785</v>
+        <v>0.1773959888765267</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5736536096758973</v>
+        <v>0.5657953410502</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7782,22 +7782,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1651874076745033</v>
+        <v>0.1667374076745033</v>
       </c>
       <c r="C75">
-        <v>-1743.644006567264</v>
+        <v>-1800.274148244504</v>
       </c>
       <c r="D75">
-        <v>1107.287993432736</v>
+        <v>1094.341851755495</v>
       </c>
       <c r="E75">
-        <v>1806.632</v>
+        <v>1850.316</v>
       </c>
       <c r="F75">
-        <v>3188.932</v>
+        <v>3232.616</v>
       </c>
       <c r="G75">
         <v>338</v>
@@ -7818,37 +7818,37 @@
         <v>362.3</v>
       </c>
       <c r="M75">
-        <v>640.3375456</v>
+        <v>649.1092927999999</v>
       </c>
       <c r="N75">
-        <v>-278.0375456</v>
+        <v>-286.8092927999999</v>
       </c>
       <c r="O75">
-        <v>-57.2757343936</v>
+        <v>-59.08271431679999</v>
       </c>
       <c r="P75">
-        <v>-220.7618112064</v>
+        <v>-227.7265784831999</v>
       </c>
       <c r="Q75">
-        <v>-33.46181120639997</v>
+        <v>-40.42657848319993</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1321790214616252</v>
+        <v>0.1355012915178416</v>
       </c>
       <c r="T75">
-        <v>1.994896569552546</v>
+        <v>2.071623360689182</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1165538402563412</v>
+        <v>0.1149787883609853</v>
       </c>
       <c r="W75">
-        <v>0.1773959888765267</v>
+        <v>0.1777122592971142</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5657953410502</v>
+        <v>0.5581494580630353</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7864,22 +7864,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1667374076745033</v>
+        <v>0.1682874076745033</v>
       </c>
       <c r="C76">
-        <v>-1800.274148244504</v>
+        <v>-1856.605062145919</v>
       </c>
       <c r="D76">
-        <v>1094.341851755495</v>
+        <v>1081.694937854081</v>
       </c>
       <c r="E76">
-        <v>1850.316</v>
+        <v>1894</v>
       </c>
       <c r="F76">
-        <v>3232.616</v>
+        <v>3276.3</v>
       </c>
       <c r="G76">
         <v>338</v>
@@ -7900,37 +7900,37 @@
         <v>362.3</v>
       </c>
       <c r="M76">
-        <v>649.1092927999999</v>
+        <v>657.88104</v>
       </c>
       <c r="N76">
-        <v>-286.8092927999999</v>
+        <v>-295.58104</v>
       </c>
       <c r="O76">
-        <v>-59.08271431679999</v>
+        <v>-60.88969424</v>
       </c>
       <c r="P76">
-        <v>-227.7265784831999</v>
+        <v>-234.69134576</v>
       </c>
       <c r="Q76">
-        <v>-40.42657848319993</v>
+        <v>-47.39134575999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1355012915178416</v>
+        <v>0.1390893431785553</v>
       </c>
       <c r="T76">
-        <v>2.071623360689182</v>
+        <v>2.15448829511675</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1149787883609853</v>
+        <v>0.1134457378495055</v>
       </c>
       <c r="W76">
-        <v>0.1777122592971142</v>
+        <v>0.1780200958398193</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5581494580630353</v>
+        <v>0.5507074652888614</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7946,22 +7946,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1682874076745033</v>
+        <v>0.1698374076745033</v>
       </c>
       <c r="C77">
-        <v>-1856.605062145919</v>
+        <v>-1912.647003952599</v>
       </c>
       <c r="D77">
-        <v>1081.694937854081</v>
+        <v>1069.336996047401</v>
       </c>
       <c r="E77">
-        <v>1894</v>
+        <v>1937.684</v>
       </c>
       <c r="F77">
-        <v>3276.3</v>
+        <v>3319.984</v>
       </c>
       <c r="G77">
         <v>338</v>
@@ -7982,37 +7982,37 @@
         <v>362.3</v>
       </c>
       <c r="M77">
-        <v>657.88104</v>
+        <v>666.6527872</v>
       </c>
       <c r="N77">
-        <v>-295.58104</v>
+        <v>-304.3527872</v>
       </c>
       <c r="O77">
-        <v>-60.88969424</v>
+        <v>-62.69667416320001</v>
       </c>
       <c r="P77">
-        <v>-234.69134576</v>
+        <v>-241.6561130368</v>
       </c>
       <c r="Q77">
-        <v>-47.39134575999998</v>
+        <v>-54.3561130368</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1390893431785553</v>
+        <v>0.1429763991443284</v>
       </c>
       <c r="T77">
-        <v>2.15448829511675</v>
+        <v>2.244258640746615</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1134457378495055</v>
+        <v>0.1119530307725383</v>
       </c>
       <c r="W77">
-        <v>0.1780200958398193</v>
+        <v>0.1783198314208743</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5507074652888614</v>
+        <v>0.5434613144297974</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8028,22 +8028,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1698374076745033</v>
+        <v>0.1713874076745033</v>
       </c>
       <c r="C78">
-        <v>-1912.647003952599</v>
+        <v>-1968.409765970922</v>
       </c>
       <c r="D78">
-        <v>1069.336996047401</v>
+        <v>1057.258234029078</v>
       </c>
       <c r="E78">
-        <v>1937.684</v>
+        <v>1981.368</v>
       </c>
       <c r="F78">
-        <v>3319.984</v>
+        <v>3363.668</v>
       </c>
       <c r="G78">
         <v>338</v>
@@ -8064,37 +8064,37 @@
         <v>362.3</v>
       </c>
       <c r="M78">
-        <v>666.6527872</v>
+        <v>675.4245344</v>
       </c>
       <c r="N78">
-        <v>-304.3527872</v>
+        <v>-313.1245344</v>
       </c>
       <c r="O78">
-        <v>-62.69667416320001</v>
+        <v>-64.50365408639999</v>
       </c>
       <c r="P78">
-        <v>-241.6561130368</v>
+        <v>-248.6208803136</v>
       </c>
       <c r="Q78">
-        <v>-54.3561130368</v>
+        <v>-61.32088031359996</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1429763991443284</v>
+        <v>0.1472014599766905</v>
       </c>
       <c r="T78">
-        <v>2.244258640746615</v>
+        <v>2.341835103387772</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1119530307725383</v>
+        <v>0.1104990953079599</v>
       </c>
       <c r="W78">
-        <v>0.1783198314208743</v>
+        <v>0.1786117816621617</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5434613144297974</v>
+        <v>0.5364033752813585</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8110,22 +8110,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1713874076745033</v>
+        <v>0.1729374076745033</v>
       </c>
       <c r="C79">
-        <v>-1968.409765970922</v>
+        <v>-2023.902703010633</v>
       </c>
       <c r="D79">
-        <v>1057.258234029078</v>
+        <v>1045.449296989367</v>
       </c>
       <c r="E79">
-        <v>1981.368</v>
+        <v>2025.052</v>
       </c>
       <c r="F79">
-        <v>3363.668</v>
+        <v>3407.352</v>
       </c>
       <c r="G79">
         <v>338</v>
@@ -8146,37 +8146,37 @@
         <v>362.3</v>
       </c>
       <c r="M79">
-        <v>675.4245344</v>
+        <v>684.1962816</v>
       </c>
       <c r="N79">
-        <v>-313.1245344</v>
+        <v>-321.8962816</v>
       </c>
       <c r="O79">
-        <v>-64.50365408639999</v>
+        <v>-66.31063400960001</v>
       </c>
       <c r="P79">
-        <v>-248.6208803136</v>
+        <v>-255.5856475904</v>
       </c>
       <c r="Q79">
-        <v>-61.32088031359996</v>
+        <v>-68.2856475904</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1472014599766905</v>
+        <v>0.1518106172483583</v>
       </c>
       <c r="T79">
-        <v>2.341835103387772</v>
+        <v>2.448282153541761</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1104990953079599</v>
+        <v>0.1090824402399091</v>
       </c>
       <c r="W79">
-        <v>0.1786117816621617</v>
+        <v>0.1788962459998263</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5364033752813585</v>
+        <v>0.5295264089315974</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8192,22 +8192,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1729374076745033</v>
+        <v>0.1744874076745033</v>
       </c>
       <c r="C80">
-        <v>-2023.902703010633</v>
+        <v>-2079.134756547826</v>
       </c>
       <c r="D80">
-        <v>1045.449296989367</v>
+        <v>1033.901243452174</v>
       </c>
       <c r="E80">
-        <v>2025.052</v>
+        <v>2068.736</v>
       </c>
       <c r="F80">
-        <v>3407.352</v>
+        <v>3451.036</v>
       </c>
       <c r="G80">
         <v>338</v>
@@ -8228,37 +8228,37 @@
         <v>362.3</v>
       </c>
       <c r="M80">
-        <v>684.1962816</v>
+        <v>692.9680288000001</v>
       </c>
       <c r="N80">
-        <v>-321.8962816</v>
+        <v>-330.6680288000001</v>
       </c>
       <c r="O80">
-        <v>-66.31063400960001</v>
+        <v>-68.11761393280001</v>
       </c>
       <c r="P80">
-        <v>-255.5856475904</v>
+        <v>-262.5504148672001</v>
       </c>
       <c r="Q80">
-        <v>-68.2856475904</v>
+        <v>-75.25041486720005</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1518106172483583</v>
+        <v>0.1568587418792325</v>
       </c>
       <c r="T80">
-        <v>2.448282153541761</v>
+        <v>2.564867017996131</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1090824402399091</v>
+        <v>0.1077016498571254</v>
       </c>
       <c r="W80">
-        <v>0.1788962459998263</v>
+        <v>0.1791735087086892</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5295264089315974</v>
+        <v>0.5228235429957544</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8274,22 +8274,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1744874076745033</v>
+        <v>0.1760374076745033</v>
       </c>
       <c r="C81">
-        <v>-2079.134756547826</v>
+        <v>-2134.114477303993</v>
       </c>
       <c r="D81">
-        <v>1033.901243452174</v>
+        <v>1022.605522696007</v>
       </c>
       <c r="E81">
-        <v>2068.736</v>
+        <v>2112.42</v>
       </c>
       <c r="F81">
-        <v>3451.036</v>
+        <v>3494.72</v>
       </c>
       <c r="G81">
         <v>338</v>
@@ -8310,37 +8310,37 @@
         <v>362.3</v>
       </c>
       <c r="M81">
-        <v>692.9680288000001</v>
+        <v>701.739776</v>
       </c>
       <c r="N81">
-        <v>-330.6680288000001</v>
+        <v>-339.439776</v>
       </c>
       <c r="O81">
-        <v>-68.11761393280001</v>
+        <v>-69.924593856</v>
       </c>
       <c r="P81">
-        <v>-262.5504148672001</v>
+        <v>-269.515182144</v>
       </c>
       <c r="Q81">
-        <v>-75.25041486720005</v>
+        <v>-82.21518214399998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1568587418792325</v>
+        <v>0.1624116789731941</v>
       </c>
       <c r="T81">
-        <v>2.564867017996131</v>
+        <v>2.693110368895938</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1077016498571254</v>
+        <v>0.1063553792339113</v>
       </c>
       <c r="W81">
-        <v>0.1791735087086892</v>
+        <v>0.1794438398498306</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5228235429957544</v>
+        <v>0.5162882487083076</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8356,22 +8356,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1760374076745033</v>
+        <v>0.1775874076745033</v>
       </c>
       <c r="C82">
-        <v>-2134.114477303993</v>
+        <v>-2188.850046360967</v>
       </c>
       <c r="D82">
-        <v>1022.605522696007</v>
+        <v>1011.553953639033</v>
       </c>
       <c r="E82">
-        <v>2112.42</v>
+        <v>2156.104</v>
       </c>
       <c r="F82">
-        <v>3494.72</v>
+        <v>3538.404</v>
       </c>
       <c r="G82">
         <v>338</v>
@@ -8392,37 +8392,37 @@
         <v>362.3</v>
       </c>
       <c r="M82">
-        <v>701.739776</v>
+        <v>710.5115232000001</v>
       </c>
       <c r="N82">
-        <v>-339.439776</v>
+        <v>-348.2115232</v>
       </c>
       <c r="O82">
-        <v>-69.924593856</v>
+        <v>-71.73157377920002</v>
       </c>
       <c r="P82">
-        <v>-269.515182144</v>
+        <v>-276.4799494208</v>
       </c>
       <c r="Q82">
-        <v>-82.21518214399998</v>
+        <v>-89.17994942080003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1624116789731941</v>
+        <v>0.1685491357612569</v>
       </c>
       <c r="T82">
-        <v>2.693110368895938</v>
+        <v>2.834853019890461</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1063553792339113</v>
+        <v>0.1050423498606532</v>
       </c>
       <c r="W82">
-        <v>0.1794438398498306</v>
+        <v>0.1797074961479808</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5162882487083076</v>
+        <v>0.5099143197119087</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8438,22 +8438,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1775874076745033</v>
+        <v>0.1791374076745033</v>
       </c>
       <c r="C83">
-        <v>-2188.850046360967</v>
+        <v>-2243.349294921336</v>
       </c>
       <c r="D83">
-        <v>1011.553953639033</v>
+        <v>1000.738705078664</v>
       </c>
       <c r="E83">
-        <v>2156.104</v>
+        <v>2199.788</v>
       </c>
       <c r="F83">
-        <v>3538.404</v>
+        <v>3582.088</v>
       </c>
       <c r="G83">
         <v>338</v>
@@ -8474,37 +8474,37 @@
         <v>362.3</v>
       </c>
       <c r="M83">
-        <v>710.5115232000001</v>
+        <v>719.2832704000001</v>
       </c>
       <c r="N83">
-        <v>-348.2115232</v>
+        <v>-356.9832704000001</v>
       </c>
       <c r="O83">
-        <v>-71.73157377920002</v>
+        <v>-73.53855370240002</v>
       </c>
       <c r="P83">
-        <v>-276.4799494208</v>
+        <v>-283.4447166976001</v>
       </c>
       <c r="Q83">
-        <v>-89.17994942080003</v>
+        <v>-96.14471669760007</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1685491357612569</v>
+        <v>0.1753685321924379</v>
       </c>
       <c r="T83">
-        <v>2.834853019890461</v>
+        <v>2.99234485432882</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1050423498606532</v>
+        <v>0.1037613455940598</v>
       </c>
       <c r="W83">
-        <v>0.1797074961479808</v>
+        <v>0.1799647218047128</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5099143197119087</v>
+        <v>0.5036958523983488</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8520,22 +8520,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1791374076745033</v>
+        <v>0.2100593400517391</v>
       </c>
       <c r="C84">
-        <v>-2243.349294921336</v>
+        <v>-2462.961864005984</v>
       </c>
       <c r="D84">
-        <v>1000.738705078664</v>
+        <v>824.8101359940156</v>
       </c>
       <c r="E84">
-        <v>2199.788</v>
+        <v>2243.472</v>
       </c>
       <c r="F84">
-        <v>3582.088</v>
+        <v>3625.772</v>
       </c>
       <c r="G84">
         <v>338</v>
@@ -8556,45 +8556,45 @@
         <v>362.3</v>
       </c>
       <c r="M84">
-        <v>719.2832704000001</v>
+        <v>854.9570376</v>
       </c>
       <c r="N84">
-        <v>-356.9832704000001</v>
+        <v>-492.6570376</v>
       </c>
       <c r="O84">
-        <v>-73.53855370240002</v>
+        <v>-101.4873497456</v>
       </c>
       <c r="P84">
-        <v>-283.4447166976001</v>
+        <v>-391.1696878544</v>
       </c>
       <c r="Q84">
-        <v>-96.14471669760007</v>
+        <v>-203.8696878544</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1753685321924379</v>
+        <v>0.1848839304227919</v>
       </c>
       <c r="T84">
-        <v>2.99234485432882</v>
+        <v>3.212100009764248</v>
       </c>
       <c r="U84">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1037613455940598</v>
+        <v>0.08729538060708748</v>
       </c>
       <c r="W84">
-        <v>0.1799647218047128</v>
+        <v>0.2152157492528488</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.5036958523983488</v>
+        <v>0.4237639835295509</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8602,22 +8602,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2100593400517391</v>
+        <v>0.2119593400517391</v>
       </c>
       <c r="C85">
-        <v>-2462.961864005984</v>
+        <v>-2515.460219480059</v>
       </c>
       <c r="D85">
-        <v>824.8101359940156</v>
+        <v>815.9957805199416</v>
       </c>
       <c r="E85">
-        <v>2243.472</v>
+        <v>2287.156</v>
       </c>
       <c r="F85">
-        <v>3625.772</v>
+        <v>3669.456</v>
       </c>
       <c r="G85">
         <v>338</v>
@@ -8638,37 +8638,37 @@
         <v>362.3</v>
       </c>
       <c r="M85">
-        <v>854.9570376</v>
+        <v>865.2577248000001</v>
       </c>
       <c r="N85">
-        <v>-492.6570376</v>
+        <v>-502.9577248000001</v>
       </c>
       <c r="O85">
-        <v>-101.4873497456</v>
+        <v>-103.6092913088</v>
       </c>
       <c r="P85">
-        <v>-391.1696878544</v>
+        <v>-399.3484334912001</v>
       </c>
       <c r="Q85">
-        <v>-203.8696878544</v>
+        <v>-212.0484334912001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1848839304227919</v>
+        <v>0.1935766760742165</v>
       </c>
       <c r="T85">
-        <v>3.212100009764248</v>
+        <v>3.412856260374515</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08729538060708748</v>
+        <v>0.08625614988557453</v>
       </c>
       <c r="W85">
-        <v>0.2152157492528488</v>
+        <v>0.2154607998569815</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4237639835295509</v>
+        <v>0.418719174201818</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8684,22 +8684,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2119593400517391</v>
+        <v>0.2138593400517391</v>
       </c>
       <c r="C86">
-        <v>-2515.460219480058</v>
+        <v>-2567.772177209778</v>
       </c>
       <c r="D86">
-        <v>815.9957805199421</v>
+        <v>807.367822790221</v>
       </c>
       <c r="E86">
-        <v>2287.156</v>
+        <v>2330.839999999999</v>
       </c>
       <c r="F86">
-        <v>3669.456</v>
+        <v>3713.139999999999</v>
       </c>
       <c r="G86">
         <v>338</v>
@@ -8720,37 +8720,37 @@
         <v>362.3</v>
       </c>
       <c r="M86">
-        <v>865.2577248</v>
+        <v>875.5584119999999</v>
       </c>
       <c r="N86">
-        <v>-502.9577248</v>
+        <v>-513.2584119999999</v>
       </c>
       <c r="O86">
-        <v>-103.6092913088</v>
+        <v>-105.731232872</v>
       </c>
       <c r="P86">
-        <v>-399.3484334912</v>
+        <v>-407.5271791279999</v>
       </c>
       <c r="Q86">
-        <v>-212.0484334912</v>
+        <v>-220.2271791279999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1935766760742163</v>
+        <v>0.2034284544791641</v>
       </c>
       <c r="T86">
-        <v>3.412856260374512</v>
+        <v>3.640380011066146</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08625614988557455</v>
+        <v>0.08524137165162662</v>
       </c>
       <c r="W86">
-        <v>0.2154607998569815</v>
+        <v>0.2157000845645465</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4187191742018181</v>
+        <v>0.413793066270032</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8766,22 +8766,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2138593400517391</v>
+        <v>0.2157593400517391</v>
       </c>
       <c r="C87">
-        <v>-2567.772177209778</v>
+        <v>-2619.903587979395</v>
       </c>
       <c r="D87">
-        <v>807.367822790221</v>
+        <v>798.9204120206052</v>
       </c>
       <c r="E87">
-        <v>2330.839999999999</v>
+        <v>2374.523999999999</v>
       </c>
       <c r="F87">
-        <v>3713.139999999999</v>
+        <v>3756.824</v>
       </c>
       <c r="G87">
         <v>338</v>
@@ -8802,37 +8802,37 @@
         <v>362.3</v>
       </c>
       <c r="M87">
-        <v>875.5584119999999</v>
+        <v>885.8590991999999</v>
       </c>
       <c r="N87">
-        <v>-513.2584119999999</v>
+        <v>-523.5590992</v>
       </c>
       <c r="O87">
-        <v>-105.731232872</v>
+        <v>-107.8531744352</v>
       </c>
       <c r="P87">
-        <v>-407.5271791279999</v>
+        <v>-415.7059247648</v>
       </c>
       <c r="Q87">
-        <v>-220.2271791279999</v>
+        <v>-228.4059247648</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2034284544791641</v>
+        <v>0.2146876297991044</v>
       </c>
       <c r="T87">
-        <v>3.640380011066146</v>
+        <v>3.900407154713728</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08524137165162662</v>
+        <v>0.08425019291149141</v>
       </c>
       <c r="W87">
-        <v>0.2157000845645465</v>
+        <v>0.2159338045114703</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.413793066270032</v>
+        <v>0.4089815189878223</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8848,22 +8848,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2157593400517391</v>
+        <v>0.2176593400517391</v>
       </c>
       <c r="C88">
-        <v>-2619.903587979395</v>
+        <v>-2671.86006024388</v>
       </c>
       <c r="D88">
-        <v>798.9204120206052</v>
+        <v>790.6479397561195</v>
       </c>
       <c r="E88">
-        <v>2374.523999999999</v>
+        <v>2418.208</v>
       </c>
       <c r="F88">
-        <v>3756.824</v>
+        <v>3800.508</v>
       </c>
       <c r="G88">
         <v>338</v>
@@ -8884,37 +8884,37 @@
         <v>362.3</v>
       </c>
       <c r="M88">
-        <v>885.8590991999999</v>
+        <v>896.1597864</v>
       </c>
       <c r="N88">
-        <v>-523.5590992</v>
+        <v>-533.8597864000001</v>
       </c>
       <c r="O88">
-        <v>-107.8531744352</v>
+        <v>-109.9751159984</v>
       </c>
       <c r="P88">
-        <v>-415.7059247648</v>
+        <v>-423.8846704016</v>
       </c>
       <c r="Q88">
-        <v>-228.4059247648</v>
+        <v>-236.5846704016</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2146876297991044</v>
+        <v>0.2276789859374971</v>
       </c>
       <c r="T88">
-        <v>3.900407154713728</v>
+        <v>4.200438474307092</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08425019291149141</v>
+        <v>0.08328179988952024</v>
       </c>
       <c r="W88">
-        <v>0.2159338045114703</v>
+        <v>0.2161621515860511</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4089815189878223</v>
+        <v>0.4042805819879622</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8930,22 +8930,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2176593400517391</v>
+        <v>0.2195593400517391</v>
       </c>
       <c r="C89">
-        <v>-2671.86006024388</v>
+        <v>-2723.646972546431</v>
       </c>
       <c r="D89">
-        <v>790.6479397561195</v>
+        <v>782.5450274535687</v>
       </c>
       <c r="E89">
-        <v>2418.208</v>
+        <v>2461.892</v>
       </c>
       <c r="F89">
-        <v>3800.508</v>
+        <v>3844.192</v>
       </c>
       <c r="G89">
         <v>338</v>
@@ -8966,37 +8966,37 @@
         <v>362.3</v>
       </c>
       <c r="M89">
-        <v>896.1597864</v>
+        <v>906.4604735999999</v>
       </c>
       <c r="N89">
-        <v>-533.8597864000001</v>
+        <v>-544.1604735999999</v>
       </c>
       <c r="O89">
-        <v>-109.9751159984</v>
+        <v>-112.0970575616</v>
       </c>
       <c r="P89">
-        <v>-423.8846704016</v>
+        <v>-432.0634160384</v>
       </c>
       <c r="Q89">
-        <v>-236.5846704016</v>
+        <v>-244.7634160384</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2276789859374971</v>
+        <v>0.2428355680989552</v>
       </c>
       <c r="T89">
-        <v>4.200438474307092</v>
+        <v>4.550475013832684</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08328179988952024</v>
+        <v>0.08233541579986663</v>
       </c>
       <c r="W89">
-        <v>0.2161621515860511</v>
+        <v>0.2163853089543915</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4042805819879622</v>
+        <v>0.3996864844653718</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9012,22 +9012,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2195593400517391</v>
+        <v>0.2214593400517391</v>
       </c>
       <c r="C90">
-        <v>-2723.646972546431</v>
+        <v>-2775.26948518014</v>
       </c>
       <c r="D90">
-        <v>782.5450274535687</v>
+        <v>774.6065148198597</v>
       </c>
       <c r="E90">
-        <v>2461.892</v>
+        <v>2505.576</v>
       </c>
       <c r="F90">
-        <v>3844.192</v>
+        <v>3887.876</v>
       </c>
       <c r="G90">
         <v>338</v>
@@ -9048,37 +9048,37 @@
         <v>362.3</v>
       </c>
       <c r="M90">
-        <v>906.4604735999999</v>
+        <v>916.7611608</v>
       </c>
       <c r="N90">
-        <v>-544.1604735999999</v>
+        <v>-554.4611608</v>
       </c>
       <c r="O90">
-        <v>-112.0970575616</v>
+        <v>-114.2189991248</v>
       </c>
       <c r="P90">
-        <v>-432.0634160384</v>
+        <v>-440.2421616752</v>
       </c>
       <c r="Q90">
-        <v>-244.7634160384</v>
+        <v>-252.9421616752</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2428355680989552</v>
+        <v>0.2607478924715875</v>
       </c>
       <c r="T90">
-        <v>4.550475013832684</v>
+        <v>4.964154560544746</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08233541579986663</v>
+        <v>0.08141029876840744</v>
       </c>
       <c r="W90">
-        <v>0.2163853089543915</v>
+        <v>0.2166034515504095</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3996864844653718</v>
+        <v>0.3951956250893564</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9094,22 +9094,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2214593400517391</v>
+        <v>0.2233593400517391</v>
       </c>
       <c r="C91">
-        <v>-2775.26948518014</v>
+        <v>-2826.732551146994</v>
       </c>
       <c r="D91">
-        <v>774.6065148198597</v>
+        <v>766.8274488530061</v>
       </c>
       <c r="E91">
-        <v>2505.576</v>
+        <v>2549.26</v>
       </c>
       <c r="F91">
-        <v>3887.876</v>
+        <v>3931.56</v>
       </c>
       <c r="G91">
         <v>338</v>
@@ -9130,37 +9130,37 @@
         <v>362.3</v>
       </c>
       <c r="M91">
-        <v>916.7611608</v>
+        <v>927.0618480000001</v>
       </c>
       <c r="N91">
-        <v>-554.4611608</v>
+        <v>-564.7618480000001</v>
       </c>
       <c r="O91">
-        <v>-114.2189991248</v>
+        <v>-116.340940688</v>
       </c>
       <c r="P91">
-        <v>-440.2421616752</v>
+        <v>-448.4209073120001</v>
       </c>
       <c r="Q91">
-        <v>-252.9421616752</v>
+        <v>-261.120907312</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2607478924715875</v>
+        <v>0.2822426817187462</v>
       </c>
       <c r="T91">
-        <v>4.964154560544746</v>
+        <v>5.460570016599221</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08141029876840744</v>
+        <v>0.08050573989320289</v>
       </c>
       <c r="W91">
-        <v>0.2166034515504095</v>
+        <v>0.2168167465331828</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3951956250893564</v>
+        <v>0.3908045625883635</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9176,22 +9176,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2233593400517391</v>
+        <v>0.2252593400517391</v>
       </c>
       <c r="C92">
-        <v>-2826.732551146994</v>
+        <v>-2878.040926463092</v>
       </c>
       <c r="D92">
-        <v>766.8274488530061</v>
+        <v>759.2030735369079</v>
       </c>
       <c r="E92">
-        <v>2549.26</v>
+        <v>2592.944</v>
       </c>
       <c r="F92">
-        <v>3931.56</v>
+        <v>3975.244</v>
       </c>
       <c r="G92">
         <v>338</v>
@@ -9212,37 +9212,37 @@
         <v>362.3</v>
       </c>
       <c r="M92">
-        <v>927.0618480000001</v>
+        <v>937.3625351999999</v>
       </c>
       <c r="N92">
-        <v>-564.7618480000001</v>
+        <v>-575.0625352</v>
       </c>
       <c r="O92">
-        <v>-116.340940688</v>
+        <v>-118.4628822512</v>
       </c>
       <c r="P92">
-        <v>-448.4209073120001</v>
+        <v>-456.5996529488</v>
       </c>
       <c r="Q92">
-        <v>-261.120907312</v>
+        <v>-269.2996529488</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2822426817187462</v>
+        <v>0.3085140907986069</v>
       </c>
       <c r="T92">
-        <v>5.460570016599221</v>
+        <v>6.067300018443579</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08050573989320289</v>
+        <v>0.07962106143283805</v>
       </c>
       <c r="W92">
-        <v>0.2168167465331828</v>
+        <v>0.2170253537141368</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3908045625883635</v>
+        <v>0.3865100069555244</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9258,22 +9258,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2252593400517391</v>
+        <v>0.2271593400517391</v>
       </c>
       <c r="C93">
-        <v>-2878.040926463092</v>
+        <v>-2929.199179855149</v>
       </c>
       <c r="D93">
-        <v>759.2030735369079</v>
+        <v>751.7288201448506</v>
       </c>
       <c r="E93">
-        <v>2592.944</v>
+        <v>2636.628</v>
       </c>
       <c r="F93">
-        <v>3975.244</v>
+        <v>4018.928</v>
       </c>
       <c r="G93">
         <v>338</v>
@@ -9294,37 +9294,37 @@
         <v>362.3</v>
       </c>
       <c r="M93">
-        <v>937.3625351999999</v>
+        <v>947.6632224</v>
       </c>
       <c r="N93">
-        <v>-575.0625352</v>
+        <v>-585.3632224</v>
       </c>
       <c r="O93">
-        <v>-118.4628822512</v>
+        <v>-120.5848238144</v>
       </c>
       <c r="P93">
-        <v>-456.5996529488</v>
+        <v>-464.7783985856</v>
       </c>
       <c r="Q93">
-        <v>-269.2996529488</v>
+        <v>-277.4783985856</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3085140907986069</v>
+        <v>0.3413533521484329</v>
       </c>
       <c r="T93">
-        <v>6.067300018443579</v>
+        <v>6.825712520749029</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07962106143283805</v>
+        <v>0.07875561511291589</v>
       </c>
       <c r="W93">
-        <v>0.2170253537141368</v>
+        <v>0.2172294259563745</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3865100069555244</v>
+        <v>0.382308811227747</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9340,22 +9340,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2271593400517391</v>
+        <v>0.2290593400517391</v>
       </c>
       <c r="C94">
-        <v>-2929.199179855149</v>
+        <v>-2980.211701889812</v>
       </c>
       <c r="D94">
-        <v>751.7288201448506</v>
+        <v>744.4002981101885</v>
       </c>
       <c r="E94">
-        <v>2636.628</v>
+        <v>2680.312</v>
       </c>
       <c r="F94">
-        <v>4018.928</v>
+        <v>4062.612</v>
       </c>
       <c r="G94">
         <v>338</v>
@@ -9376,37 +9376,37 @@
         <v>362.3</v>
       </c>
       <c r="M94">
-        <v>947.6632224</v>
+        <v>957.9639096000001</v>
       </c>
       <c r="N94">
-        <v>-585.3632224</v>
+        <v>-595.6639096000001</v>
       </c>
       <c r="O94">
-        <v>-120.5848238144</v>
+        <v>-122.7067653776</v>
       </c>
       <c r="P94">
-        <v>-464.7783985856</v>
+        <v>-472.9571442224001</v>
       </c>
       <c r="Q94">
-        <v>-277.4783985856</v>
+        <v>-285.6571442224001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3413533521484329</v>
+        <v>0.383575259598209</v>
       </c>
       <c r="T94">
-        <v>6.825712520749029</v>
+        <v>7.800814309427462</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07875561511291589</v>
+        <v>0.07790878054180926</v>
       </c>
       <c r="W94">
-        <v>0.2172294259563745</v>
+        <v>0.2174291095482414</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.382308811227747</v>
+        <v>0.3781979637951904</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9422,22 +9422,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2290593400517391</v>
+        <v>0.2309593400517391</v>
       </c>
       <c r="C95">
-        <v>-2980.211701889812</v>
+        <v>-3031.082713574127</v>
       </c>
       <c r="D95">
-        <v>744.4002981101885</v>
+        <v>737.213286425873</v>
       </c>
       <c r="E95">
-        <v>2680.312</v>
+        <v>2723.996</v>
       </c>
       <c r="F95">
-        <v>4062.612</v>
+        <v>4106.296</v>
       </c>
       <c r="G95">
         <v>338</v>
@@ -9458,37 +9458,37 @@
         <v>362.3</v>
       </c>
       <c r="M95">
-        <v>957.9639096000001</v>
+        <v>968.2645968</v>
       </c>
       <c r="N95">
-        <v>-595.6639096000001</v>
+        <v>-605.9645968</v>
       </c>
       <c r="O95">
-        <v>-122.7067653776</v>
+        <v>-124.8287069408</v>
       </c>
       <c r="P95">
-        <v>-472.9571442224001</v>
+        <v>-481.1358898592</v>
       </c>
       <c r="Q95">
-        <v>-285.6571442224001</v>
+        <v>-293.8358898592</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.383575259598209</v>
+        <v>0.4398711361979107</v>
       </c>
       <c r="T95">
-        <v>7.800814309427462</v>
+        <v>9.100950027665375</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07790878054180926</v>
+        <v>0.07707996372753469</v>
       </c>
       <c r="W95">
-        <v>0.2174291095482414</v>
+        <v>0.2176245445530473</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3781979637951904</v>
+        <v>0.3741745812016247</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9504,22 +9504,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2309593400517391</v>
+        <v>0.2328593400517391</v>
       </c>
       <c r="C96">
-        <v>-3031.082713574127</v>
+        <v>-3081.816274462567</v>
       </c>
       <c r="D96">
-        <v>737.213286425873</v>
+        <v>730.1637255374332</v>
       </c>
       <c r="E96">
-        <v>2723.996</v>
+        <v>2767.679999999999</v>
       </c>
       <c r="F96">
-        <v>4106.296</v>
+        <v>4149.98</v>
       </c>
       <c r="G96">
         <v>338</v>
@@ -9540,37 +9540,37 @@
         <v>362.3</v>
       </c>
       <c r="M96">
-        <v>968.2645968</v>
+        <v>978.5652839999999</v>
       </c>
       <c r="N96">
-        <v>-605.9645968</v>
+        <v>-616.2652839999998</v>
       </c>
       <c r="O96">
-        <v>-124.8287069408</v>
+        <v>-126.950648504</v>
       </c>
       <c r="P96">
-        <v>-481.1358898592</v>
+        <v>-489.3146354959999</v>
       </c>
       <c r="Q96">
-        <v>-293.8358898592</v>
+        <v>-302.0146354959999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4398711361979107</v>
+        <v>0.5186853634374929</v>
       </c>
       <c r="T96">
-        <v>9.100950027665375</v>
+        <v>10.92114003319845</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07707996372753469</v>
+        <v>0.0762685956882975</v>
       </c>
       <c r="W96">
-        <v>0.2176245445530473</v>
+        <v>0.2178158651366995</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3741745812016247</v>
+        <v>0.3702359013995025</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9586,22 +9586,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2328593400517391</v>
+        <v>0.2347593400517392</v>
       </c>
       <c r="C97">
-        <v>-3081.816274462567</v>
+        <v>-3132.416290303316</v>
       </c>
       <c r="D97">
-        <v>730.1637255374332</v>
+        <v>723.2477096966842</v>
       </c>
       <c r="E97">
-        <v>2767.679999999999</v>
+        <v>2811.364</v>
       </c>
       <c r="F97">
-        <v>4149.98</v>
+        <v>4193.664</v>
       </c>
       <c r="G97">
         <v>338</v>
@@ -9622,37 +9622,37 @@
         <v>362.3</v>
       </c>
       <c r="M97">
-        <v>978.5652839999999</v>
+        <v>988.8659712</v>
       </c>
       <c r="N97">
-        <v>-616.2652839999998</v>
+        <v>-626.5659711999999</v>
       </c>
       <c r="O97">
-        <v>-126.950648504</v>
+        <v>-129.0725900672</v>
       </c>
       <c r="P97">
-        <v>-489.3146354959999</v>
+        <v>-497.4933811327999</v>
       </c>
       <c r="Q97">
-        <v>-302.0146354959999</v>
+        <v>-310.1933811327999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5186853634374929</v>
+        <v>0.6369067042968666</v>
       </c>
       <c r="T97">
-        <v>10.92114003319845</v>
+        <v>13.65142504149808</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0762685956882975</v>
+        <v>0.07547413114987772</v>
       </c>
       <c r="W97">
-        <v>0.2178158651366995</v>
+        <v>0.2180031998748589</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3702359013995025</v>
+        <v>0.3663792774265909</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9668,22 +9668,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2347593400517391</v>
+        <v>0.2366593400517391</v>
       </c>
       <c r="C98">
-        <v>-3132.416290303316</v>
+        <v>-3182.886520254086</v>
       </c>
       <c r="D98">
-        <v>723.2477096966842</v>
+        <v>716.4614797459133</v>
       </c>
       <c r="E98">
-        <v>2811.364</v>
+        <v>2855.048</v>
       </c>
       <c r="F98">
-        <v>4193.664</v>
+        <v>4237.348</v>
       </c>
       <c r="G98">
         <v>338</v>
@@ -9704,37 +9704,37 @@
         <v>362.3</v>
       </c>
       <c r="M98">
-        <v>988.8659712</v>
+        <v>999.1666584000001</v>
       </c>
       <c r="N98">
-        <v>-626.5659711999999</v>
+        <v>-636.8666584</v>
       </c>
       <c r="O98">
-        <v>-129.0725900672</v>
+        <v>-131.1945316304</v>
       </c>
       <c r="P98">
-        <v>-497.4933811327999</v>
+        <v>-505.6721267696</v>
       </c>
       <c r="Q98">
-        <v>-310.1933811327999</v>
+        <v>-318.3721267696</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6369067042968649</v>
+        <v>0.8339422723958199</v>
       </c>
       <c r="T98">
-        <v>13.65142504149804</v>
+        <v>18.20190005533072</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07547413114987772</v>
+        <v>0.07469604732359032</v>
       </c>
       <c r="W98">
-        <v>0.2180031998748589</v>
+        <v>0.2181866720410974</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3663792774265909</v>
+        <v>0.3626021714737394</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9750,22 +9750,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2366593400517391</v>
+        <v>0.2385593400517391</v>
       </c>
       <c r="C99">
-        <v>-3182.886520254086</v>
+        <v>-3233.230583695484</v>
       </c>
       <c r="D99">
-        <v>716.4614797459133</v>
+        <v>709.8014163045151</v>
       </c>
       <c r="E99">
-        <v>2855.048</v>
+        <v>2898.731999999999</v>
       </c>
       <c r="F99">
-        <v>4237.348</v>
+        <v>4281.031999999999</v>
       </c>
       <c r="G99">
         <v>338</v>
@@ -9786,37 +9786,37 @@
         <v>362.3</v>
       </c>
       <c r="M99">
-        <v>999.1666584000001</v>
+        <v>1009.4673456</v>
       </c>
       <c r="N99">
-        <v>-636.8666584</v>
+        <v>-647.1673455999999</v>
       </c>
       <c r="O99">
-        <v>-131.1945316304</v>
+        <v>-133.3164731936</v>
       </c>
       <c r="P99">
-        <v>-505.6721267696</v>
+        <v>-513.8508724063998</v>
       </c>
       <c r="Q99">
-        <v>-318.3721267696</v>
+        <v>-326.5508724063998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8339422723958199</v>
+        <v>1.22801340859373</v>
       </c>
       <c r="T99">
-        <v>18.20190005533072</v>
+        <v>27.30285008299608</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07469604732359032</v>
+        <v>0.07393384275906391</v>
       </c>
       <c r="W99">
-        <v>0.2181866720410974</v>
+        <v>0.2183663998774127</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3626021714737394</v>
+        <v>0.3589021493158441</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9832,22 +9832,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2385593400517391</v>
+        <v>0.2404593400517391</v>
       </c>
       <c r="C100">
-        <v>-3233.230583695484</v>
+        <v>-3283.451966667848</v>
       </c>
       <c r="D100">
-        <v>709.8014163045151</v>
+        <v>703.2640333321515</v>
       </c>
       <c r="E100">
-        <v>2898.731999999999</v>
+        <v>2942.415999999999</v>
       </c>
       <c r="F100">
-        <v>4281.031999999999</v>
+        <v>4324.715999999999</v>
       </c>
       <c r="G100">
         <v>338</v>
@@ -9868,37 +9868,37 @@
         <v>362.3</v>
       </c>
       <c r="M100">
-        <v>1009.4673456</v>
+        <v>1019.7680328</v>
       </c>
       <c r="N100">
-        <v>-647.1673455999999</v>
+        <v>-657.4680327999999</v>
       </c>
       <c r="O100">
-        <v>-133.3164731936</v>
+        <v>-135.4384147568</v>
       </c>
       <c r="P100">
-        <v>-513.8508724063998</v>
+        <v>-522.0296180431999</v>
       </c>
       <c r="Q100">
-        <v>-326.5508724063998</v>
+        <v>-334.7296180431999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.22801340859373</v>
+        <v>2.41022681718746</v>
       </c>
       <c r="T100">
-        <v>27.30285008299608</v>
+        <v>54.60570016599215</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07393384275906391</v>
+        <v>0.0731870362665481</v>
       </c>
       <c r="W100">
-        <v>0.2183663998774127</v>
+        <v>0.218542496848348</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9906,91 +9906,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3589021493158441</v>
+        <v>0.3552768750803306</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2404593400517391</v>
-      </c>
-      <c r="C101">
-        <v>-3283.451966667848</v>
-      </c>
-      <c r="D101">
-        <v>703.2640333321515</v>
-      </c>
-      <c r="E101">
-        <v>2942.415999999999</v>
-      </c>
-      <c r="F101">
-        <v>4324.715999999999</v>
-      </c>
-      <c r="G101">
-        <v>338</v>
-      </c>
-      <c r="H101">
-        <v>2986.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>549.6</v>
-      </c>
-      <c r="K101">
-        <v>187.3</v>
-      </c>
-      <c r="L101">
-        <v>362.3</v>
-      </c>
-      <c r="M101">
-        <v>1019.7680328</v>
-      </c>
-      <c r="N101">
-        <v>-657.4680327999999</v>
-      </c>
-      <c r="O101">
-        <v>-135.4384147568</v>
-      </c>
-      <c r="P101">
-        <v>-522.0296180431999</v>
-      </c>
-      <c r="Q101">
-        <v>-334.7296180431999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.41022681718746</v>
-      </c>
-      <c r="T101">
-        <v>54.60570016599215</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0731870362665481</v>
-      </c>
-      <c r="W101">
-        <v>0.218542496848348</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3552768750803306</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
